--- a/docs/examples/demo-control-3_FERG.xlsx
+++ b/docs/examples/demo-control-3_FERG.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C440"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -517,7 +517,7 @@
         <v>[R_01_闪光]</v>
       </c>
       <c r="C11" t="str">
-        <v>白色光: 0.01 cd·s/m²</v>
+        <v>b白色光:0.01cd.m-2,5ms</v>
       </c>
     </row>
     <row r="12">
@@ -528,7 +528,7 @@
         <v>[R_01_闪光背景]</v>
       </c>
       <c r="C12" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="13">
@@ -539,7 +539,7 @@
         <v>[R_01_采样]</v>
       </c>
       <c r="C13" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="14">
@@ -550,7 +550,7 @@
         <v>[R_01_分析时间]</v>
       </c>
       <c r="C14" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="15">
@@ -572,7 +572,7 @@
         <v>[R_01_详细数据(uv)]</v>
       </c>
       <c r="C16" t="str">
-        <v>1.57,-2.68,2.99,-2.41,1.12,0.5,-1.98,2.87,-2.91,2.08,-0.64,-0.99,2.33,-2.97,2.74,-1.69,0.14,1.45,-2.61,3,-2.5,1.25,0.36,-1.87,2.82,-2.94,2.18,-0.79,-0.86,2.22,-2.96,2.78,-1.83,0.26,1.29,-2.58,2.95,-2.63,1.31,0.13,-1.86,2.63,-3.13,2.08,-1.16,-1,1.8,-3.33,2.36,-2.49,-0.24,0.41,-3.38,1.92,-3.9,0.05,-1.61,-3.58,0.47,-5.56,-0.58,-4.42,-4.4,-2.31,-7.8,-2.66,-8.27,-6.44,-6.78,-11.12,-6.75,-13.51,-10.32,-13.25,-16.01,-13.25,-20.38,-16.51,-21.81,-22.8,-22.25,-28.91,-25.09,-32.15,-31.37,-33.25,-38.58,-35.46,-43.33,-40.93,-44.98,-48.2,-46.21,-53.67,-49.92,-55.42,-55.91,-55.14,-60.91,-56.1,-62,-59.39,-59.64,-62.53,-57.01,-62.06,-56.34,-57.16,-56.33,-50.46,-53.47,-45.01,-45.82,-40.9,-35.05,-35.1,-24.63,-24.8,-16,-10.5,-7.06,4.45,5.5,17.45,22.39,29.44,40.91,43.67,57.71,62.05,72.37,82.89,87.71,102.59,106.51,119.46,128.35,135.43,149.9,153.78,168.44,175.41,184.73,197.71,202.03,217.32,222.41,233.68,244.35,249.55,264.3,267.83,280.46,288.31,294.63,307.72,310.16,323.26,328.08,335.54,345.93,347.78,360.29,362.17,370.43,377.35,379.02,389.77,389.06,397.51,400.49,402.26,410.16,407.41,415.22,414.2,416.15,420.36,416.22,422.49,417.81,419.81,419.83,415,418.87,411.25,413,408.79,403.9,404.71,395.1,396.19,388.17,383.7,381.07,370.6,370.54,359.53,355.77,349.68,339.44,337.79,324.92,321.9,312.71,303.63,300.06,286.59,284.14,272.55,265.29,259.64,246.83,244.58,231.54,226.41,218.73,207.68,205.17,191.78,188.72,179.32,170.8,167.58,154.95,153.57,142.98,137.4,133.09,122.22,121.9,110.82,108.17,102.58,94.24,94.21,83.46,83.34,76.51,71.16,70.66,61.08,62.77,54.99,52.7,51.15,43.46,46.08,37.85,38.35,35.38,30.12,32.73,24.7,27.4,22.92,20.37,22.13,15.02,19.08,13.34,13.46,13.72,8.19,12.68,6.17,8.64,7.05,3.61,7.59,0.99,5.18,1.73,0.66,3.33,-2.61,2.49,-2.5,-1.23,-0.43,-5.01,0.12,-5.84,-2.56,-3.88,-6.56,-2.28,-8.46,-3.76,-7.1,-7.6,-4.89,-10.48,-5.13,-10.12,-8.44,-7.79,-12.06,-6.93,-12.9,-9.38,-10.94,-13.36,-9.26,-15.43,-10.64,-14.27,-14.55,-12.15,-17.7,-12.42,-17.66,-15.84,-15.56,-19.75,-14.82,-20.99,-17.4,-19.37,-21.67,-17.89,-24.17,-19.42,-23.43,-23.58,-21.58,-27.14,-22.01,-27.56,-25.63,-25.79,-29.91,-25.22,-31.6,-27.97,-30.35,-32.53,-29.06,-35.43,-30.72,-35.07,-35.08,-33.45,-38.98,-33.96,-39.76,-37.7,-38.23,-42.22,-37.73,-44.22,-40.49,-43.2,-45.18,-41.97,-48.32,-43.56,-48.16,-47.93,-46.56,-51.95,-46.95,-52.88,-50.57,-51.35,-55.08,-50.67,-57.15,-53.19,-56.1,-57.72,-54.64,-60.82,-55.89,-60.58,-59.96,-58.73,-63.8,-58.69,-64.58,-61.87,-62.75,-66.06,-61.59,-67.89,-63.57,-66.5,-67.63,-64.52,-70.37,-65.13,-69.75,-68.59,-67.35,-71.96,-66.61,-72.3,-69.07,-69.91,-72.66,-68.01,-73.98,-69.18,-72.02,-72.53,-69.29,-74.69,-69.04,-73.49,-71.7,-70.35,-74.41,-68.74,-74.15,-70.33,-71.07,-73.18,-68.31,-73.89,-68.58,-71.28,-71.14,-67.75,-72.66,-66.6,-70.85,-68.44,-67,-70.49,-64.53,-69.67,-65.29,-65.96,-67.48,-62.43,-67.65,-61.89,-64.51,-63.78,-60.32,-64.81,-58.44,-62.56,-59.62,-58.18,-61.2,-55.07,-60.02,-55.21,-55.91,-56.95,-51.87,-56.85,-50.79,-53.45,-52.26,-48.88,-53.07,-46.54,-50.67,-47.35,-46.06,-48.75,-42.61,-47.53,-42.44,-43.33,-44.04,-39.09,-43.96,-37.76,-40.61,-39.12,-35.97,-40.01,-33.48,-37.77,-34.22,-33.22,-35.73,-29.73,-34.74,-29.53,-30.74,-31.25,-26.56,-31.46,-25.25,-28.4,-26.75,-23.95,-27.93,-21.54,-26.07,-22.4,-21.82,-24.21,-18.48,-23.65,-18.41</v>
+        <v>-3.98,-2.66,-15.41,5.28,-19.15,3.07,-12.18,-7.54,-0.59,-17.52,5.68,-18.28,1.34,-9.02,-9.71,2.53,-17.73,6.79,-15.49,0.5,-4.48,-10.48,6.37,-16.21,8.31,-11.19,0.29,0.9,-10.17,10.36,-13.44,9.74,-6.05,0.26,6.35,-9.3,13.77,-10.11,10.47,-0.87,-0.16,11.03,-8.48,15.88,-6.97,9.9,3.47,-1.5,14.09,-8.39,16.02,-4.77,7.48,6.27,-4.31,14.76,-9.54,13.36,-3.93,2.54,6.49,-9.13,12.29,-12.6,7.16,-6.78,-6.02,4.02,-15.97,5.87,-18.15,-4.19,-12.88,-18.89,-4.84,-30.47,-5.22,-27.38,-15.71,-19.27,-29.77,-16.35,-44.47,-25.62,-47.28,-37.3,-36.13,-57.34,-27.18,-62.64,-43.22,-52.22,-52.17,-42.94,-65.43,-39.68,-64.25,-47.69,-57.94,-61.86,-45.08,-77.9,-49.63,-61.23,-48.76,-61.13,-63.76,-49.72,-78.47,-53.96,-56.84,-58.24,-33.49,-42.74,-26,-40.33,-15.63,-26.74,-19.02,-9.62,-18.88,26.06,5.28,20.98,35.57,31.08,56.58,35.33,66.73,48.56,91.56,78.6,75.54,121.04,83.67,138.83,117.2,147.37,146.46,163.52,181.16,168.5,197.75,171.42,218.47,209.02,211.33,237.52,211.11,275.16,264.37,278.22,247.2,289.15,263.28,278.83,276.78,285.32,286.28,347.86,294.29,369.9,290.67,338.45,385.75,346.26,401.14,321.06,410.78,396.52,393.32,369.51,336.97,407.29,348.93,418.11,412.77,376.26,356.65,382.2,358.25,362.98,349.97,346.27,374.91,343.18,385.4,409.97,343.19,361.05,326.95,315.96,324.46,325.75,292.87,335.87,307.3,333.39,306.39,319.14,292.06,313.08,240.65,233.56,248.24,254.33,254.2,195.18,203.91,221.91,212.68,208.2,185.22,200.36,164.54,193.37,184.51,155.68,145.07,138.91,138.37,128.47,141.37,134.32,97.31,129.39,80.58,111.4,88.18,89.6,96.95,66.17,85.97,65.28,71.97,65.54,49.35,58.65,40.21,56.88,31.13,48.81,40.14,26.24,45.25,15.44,38.78,13.66,26.26,22.66,9.68,25.66,2.38,23.24,3.05,8.5,13.86,-5.42,16.28,-7.86,9.15,-1.83,-3.59,6.53,-14.27,9.96,-12.93,1.36,-4.81,-12.28,4.04,-20.17,4.99,-15.96,-5.38,-5.22,-16.71,3.49,-20.22,0.72,-15.86,-8.12,-2.9,-20.39,1.74,-19.61,-1.51,-12.74,-10.84,-3.09,-20.88,3.06,-21.37,-3.87,-9.34,-14.23,1.54,-22.04,1.82,-16.77,-4.17,-8.81,-17.82,0.55,-18.01,1.97,-17.41,-6.69,-5.26,-18.39,0.04,-17.77,0.89,-13.92,-14.06,-3.53,-19.53,2.32,-18.82,-10.04,-10.74,-20.68,-6.48,-29.63,-1.08,-27.02,-9.32,-17.06,-24.52,-12.81,-28.69,-18,-30.32,-26.8,-22.91,-38.83,-7.5,-36.94,-24.75,-42.37,-40.7,-30.91,-42.6,-14.51,-52.34,-28.96,-39.01,-34.69,-24.27,-61.9,-29.45,-47.86,-34.15,-45.47,-45.08,-39.02,-65.56,-24.73,-44.26,-45.96,-54.17,-59.19,-28.37,-72.14,-39.94,-52.34,-58.76,-44.55,-52,-36.84,-63.18,-41.14,-60.56,-65.11,-58.93,-67.72,-39.54,-75.97,-63.21,-48.78,-63.74,-62.59,-79.87,-38.36,-76.96,-45.65,-46.82,-80.07,-51.66,-65.35,-53.55,-52.19,-40.84,-56.47,-63.26,-39.78,-61.31,-52.3,-76.72,-63.13,-38.11,-49.99,-44.88,-51.07,-67.68,-66.72,-77.27,-49.49,-80.87,-48.04,-80.23,-46.84,-39.7,-51.78,-35.55,-66.69,-36.62,-71.76,-56.25,-60.18,-63.14,-40.44,-59.95,-61.69,-54.36,-64.44,-36.02,-62.69,-28.35,-53.31,-48.82,-42.97,-68.8,-38.68,-77.97,-32.52,-63.31,-46.45,-68.48,-61.49,-31.82,-62.76,-34.44,-57.75,-54.7,-59.22,-61.76,-27.84,-56.79,-39.4,-65.99,-56.02,-51.62,-71.68,-44.83,-66.21,-52.06,-42.65,-52.63,-39.72,-50.59,-34.85,-58.22,-43.96,-31.36,-36.78,-34.19,-50.44,-18.44,-51.08,-34.65,-31.3,-34.18,-11.87,-44.92,-21.97,-24.71,-22.85,-13.4,-39.7,-10.06,-26.17,-9.58,-24.2,-26.38,-12.19,-22.92,-3.52,-30.55,-10.39,-13.86,-24.67,-1.61,-21.92,-1.54,-23.53,-6.24,-4.16,-21.37,3.79</v>
       </c>
     </row>
     <row r="17">
@@ -583,7 +583,7 @@
         <v>[R_01_标记]</v>
       </c>
       <c r="C17" t="str">
-        <v>a: 15.6ms -93.9uv b: 34.6ms 430.9uv</v>
+        <v>a: 15.6ms -50.1uv b: 34.3ms 176.2uv</v>
       </c>
     </row>
     <row r="18">
@@ -616,7 +616,7 @@
         <v>[L_01_闪光]</v>
       </c>
       <c r="C20" t="str">
-        <v>白色光: 0.01 cd·s/m²</v>
+        <v>b白色光:0.01cd.m-2,5ms</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +627,7 @@
         <v>[L_01_闪光背景]</v>
       </c>
       <c r="C21" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="22">
@@ -638,7 +638,7 @@
         <v>[L_01_采样]</v>
       </c>
       <c r="C22" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="23">
@@ -649,7 +649,7 @@
         <v>[L_01_分析时间]</v>
       </c>
       <c r="C23" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="24">
@@ -671,7 +671,7 @@
         <v>[L_01_详细数据(uv)]</v>
       </c>
       <c r="C25" t="str">
-        <v>0.54,-1.07,1.55,-1.99,2.36,-2.66,2.87,-2.98,2.99,-2.91,2.73,-2.46,2.11,-1.69,1.22,-0.7,0.16,0.38,-0.91,1.41,-1.87,2.26,-2.58,2.81,-2.96,3,-2.95,2.79,-2.56,2.22,-1.84,1.35,-0.88,0.3,0.19,-0.79,1.22,-1.79,2.08,-2.58,2.65,-3.05,2.84,-3.16,2.63,-2.9,2.01,-2.33,1.06,-1.55,-0.14,-0.68,-1.46,0.11,-2.78,0.66,-3.98,0.85,-4.99,0.57,-5.76,-0.26,-6.31,-1.65,-6.69,-3.57,-7.04,-5.94,-7.48,-8.66,-8.19,-11.61,-9.32,-14.68,-11.02,-17.78,-13.38,-20.83,-16.45,-23.79,-20.2,-26.69,-24.55,-29.54,-29.35,-32.39,-34.39,-35.32,-39.44,-38.34,-44.27,-41.48,-48.63,-44.7,-52.3,-47.9,-55.11,-50.93,-56.92,-53.6,-57.64,-55.66,-57.24,-56.83,-55.71,-56.85,-53.06,-55.47,-49.33,-52.49,-44.55,-47.75,-38.73,-41.19,-31.86,-32.82,-23.91,-22.73,-14.85,-11.08,-4.62,1.93,6.84,16.06,19.56,31.06,33.55,46.71,48.76,62.8,65.11,79.18,82.47,95.77,100.65,112.51,119.42,129.39,138.54,146.43,157.75,163.66,176.81,181.11,195.5,198.76,213.65,216.58,231.14,234.45,247.89,252.24,263.87,269.75,279.1,286.76,293.61,303.04,307.44,318.33,320.61,332.42,333.14,345.13,344.96,356.32,356.01,365.93,366.14,373.92,375.18,380.32,382.95,385.21,389.23,388.66,393.85,390.76,396.65,391.6,397.52,391.23,396.43,389.68,393.39,386.94,388.5,382.97,381.91,377.71,373.82,371.1,364.45,363.09,354.03,353.66,342.78,342.82,330.89,330.65,318.51,317.27,305.74,302.88,292.64,287.7,279.24,272,265.54,256.04,251.52,240.1,237.19,224.41,222.57,209.17,207.71,194.52,192.71,180.54,177.71,167.24,162.88,154.61,148.42,142.57,134.52,131.04,121.37,119.92,109.13,109.14,97.9,98.67,87.75,88.5,78.67,78.66,70.6,69.24,63.42,60.34,56.99,52.08,51.15,44.58,45.73,37.92,40.59,32.17,35.64,27.34,30.81,23.39,26.09,20.22,21.53,17.71,17.2,15.69,13.2,13.98,9.63,12.41,6.59,10.83,4.14,9.14,2.3,7.27,1.05,5.22,0.31,3.02,-0.03,0.78,-0.12,-1.41,-0.12,-3.42,-0.18,-5.14,-0.44,-6.47,-1.01,-7.39,-1.92,-7.88,-3.18,-7.99,-4.73,-7.82,-6.48,-7.51,-8.31,-7.18,-10.08,-7,-11.66,-7.08,-12.95,-7.53,-13.9,-8.38,-14.47,-9.64,-14.72,-11.26,-14.71,-13.13,-14.56,-15.13,-14.42,-17.12,-14.43,-18.97,-14.7,-20.56,-15.35,-21.82,-16.41,-22.73,-17.89,-23.3,-19.75,-23.62,-21.88,-23.78,-24.16,-23.92,-26.46,-24.19,-28.63,-24.7,-30.55,-25.57,-32.14,-26.83,-33.36,-28.52,-34.23,-30.57,-34.82,-32.89,-35.21,-35.38,-35.55,-37.87,-35.98,-40.24,-36.61,-42.36,-37.56,-44.13,-38.88,-45.51,-40.59,-46.51,-42.65,-47.18,-44.98,-47.61,-47.45,-47.94,-49.92,-48.3,-52.26,-48.81,-54.32,-49.6,-56.02,-50.71,-57.3,-52.19,-58.15,-53.98,-58.63,-56.03,-58.83,-58.2,-58.86,-60.36,-58.86,-62.37,-58.98,-64.09,-59.31,-65.42,-59.93,-66.31,-60.88,-66.74,-62.13,-66.75,-63.61,-66.44,-65.21,-65.91,-66.8,-65.31,-68.23,-64.78,-69.37,-64.43,-70.11,-64.35,-70.4,-64.57,-70.21,-65.08,-69.58,-65.83,-68.6,-66.71,-67.38,-67.59,-66.06,-68.33,-64.79,-68.8,-63.68,-68.88,-62.83,-68.52,-62.29,-67.69,-62.06,-66.42,-62.08,-64.8,-62.27,-62.93,-62.49,-60.96,-62.61,-59.03,-62.5,-57.28,-62.04,-55.79,-61.17,-54.63,-59.85,-53.82,-58.12,-53.29,-56.04,-52.98,-53.74,-52.75,-51.34,-52.48,-48.99,-52.03,-46.84,-51.28,-44.97,-50.15,-43.47,-48.62,-42.34,-46.7,-41.55,-44.46,-41.02,-42.01,-40.63,-39.48,-40.25,-37.01,-39.74,-34.74,-38.98,-32.79,-37.9,-31.22,-36.44,-30.06,-34.61,-29.27,-32.48,-28.79,-30.14,-28.5,-27.73,-28.26,-25.39,-27.93,-23.25,-27.4,-21.44,-26.57,-20.02,-25.38,-19.02,-23.84,-18.43,-22.01,-18.17,-19.96</v>
+        <v>-1.62,24.63,-2.14,14.05,13.15,-2.69,23.07,-4.1,13.74,11.07,-2.99,22.18,-5.24,14.18,9.76,-2.43,22.04,-5.51,15.4,9.26,-1.02,22.62,-4.93,17.35,9.48,1.13,23.8,-3.66,19.85,10.26,3.84,25.38,-1.9,22.67,11.35,6.84,27.1,0.06,25.53,12.47,9.81,28.63,1.9,28.1,13.3,12.47,29.68,3.37,30.01,13.48,14.37,29.9,3.93,31.01,12.76,15.47,28.97,3.72,30.87,10.88,15.16,26.64,1.23,28.54,7.37,13.14,22.2,-1.82,24.24,-0.01,8.73,14.89,-7.39,18.21,-8.22,0.22,6.89,-19.87,8.6,-21.74,-11.62,-3.75,-29.01,-4.43,-30.43,-21.69,-27.75,-44.61,-22.87,-41.37,-39.8,-38.73,-61.78,-40.82,-60.64,-44.22,-38.11,-65.32,-46.49,-75.92,-40.94,-53.26,-73.08,-47.03,-58.61,-52.3,-59.86,-61.79,-40.25,-66.44,-38.82,-46.62,-43.43,-8.78,-35.84,-7.27,-18.51,-31.78,6.92,-11.56,16.81,17.76,17.04,45.76,14.36,57.97,60.4,42.17,98.62,52.16,104.78,94.15,92.09,124.7,105.97,136.26,139.81,135.09,164.58,166.91,167.49,198.97,205.06,217,203.51,247.96,248.47,215.44,269.29,233.46,297.53,253.04,307.55,318.85,261.39,335.01,319.31,318.8,313.54,287.49,360.32,313.52,355.99,345.7,338.34,337.9,331.77,388.44,415.8,396.32,361.17,398.54,347.71,408.58,407.61,386.93,383.37,398.19,389.05,331.64,426.12,342.99,400.8,401.38,352.37,366.57,319.66,321.32,351.66,362.87,338.82,304.43,291.52,332.98,299.82,307.5,253.81,270.59,282.12,279.14,258.29,225.49,269.34,216.6,243.43,264.8,230.44,226.77,203.78,199.96,205.25,147.55,201.39,164.93,166.3,179.75,118.62,165.28,134.19,124.05,138.13,90.91,111.63,102.2,102.81,106.2,82.31,95.45,73.32,70.88,86.43,59.93,80.95,56.08,59.86,70.88,41.26,61.83,39.86,43.91,47.73,24.96,49.76,28.39,28.19,37.49,11.04,37.23,14.33,19.56,28.96,4.56,29.65,5.97,14.96,20.57,-3.18,23.39,-0.95,7.95,13.79,-8.47,18.25,-5.86,5.28,7.86,-12.17,15.55,-11.43,1.8,4.76,-15.4,12.75,-14.56,0.06,0.83,-16.05,9.12,-16.55,-0.38,-3.03,-15.79,8.42,-19.35,-0.22,-3.05,-15.1,8.06,-18,-0.93,-6.75,-16.72,7.43,-19.5,3.55,-7.81,-13.26,8.93,-18.43,0.59,-4.89,-13.51,8.65,-19.82,6.74,-9.9,-9.29,4.15,-21.02,8.01,-5.15,-8.45,10.72,-20.98,8.68,-14.61,-11.04,5.69,-24.06,0.43,-18.93,-8.68,-3.04,-22.48,6.49,-22.2,-11.32,-4.01,-33.3,-6.18,-24.22,-12.11,-4.55,-35.5,-7.81,-26.33,-16.61,-10.75,-32.79,-15.18,-39.04,-21.59,-13.55,-48.69,-16.59,-48.96,-33.86,-27.77,-54.86,-15.28,-56.47,-40.47,-28.47,-54.53,-31.64,-42.85,-52.7,-35.49,-67.94,-21.89,-67.25,-48.98,-33.18,-52.62,-33.47,-72.86,-58.29,-47.32,-71.23,-39.82,-77.25,-56.9,-66.52,-63,-49.02,-74.22,-46.56,-61.48,-67.65,-40.74,-85.37,-46.09,-51.77,-56.22,-33.08,-60.86,-58.41,-44.12,-56.04,-43.32,-86.35,-63.92,-57.9,-69.28,-30.38,-77.53,-42.31,-69.43,-69.56,-48.84,-87.5,-56.93,-61.34,-55.88,-53.16,-85.24,-49.85,-54.02,-55.04,-30.1,-68.26,-26.77,-47.26,-70.5,-50.62,-85.62,-46.24,-47.13,-68.63,-54.26,-65.05,-45.53,-73.85,-57.76,-57.24,-72.64,-36.26,-75.56,-68.85,-29.72,-73.34,-43.78,-57.63,-64.97,-31.49,-83.44,-44.27,-70.36,-66.46,-33.53,-74.79,-31.94,-59.04,-56.17,-57.32,-61.2,-46.24,-65.55,-53.72,-54.79,-74.9,-36.62,-65.58,-47.42,-34.93,-64.94,-37.55,-59.78,-45.76,-45.46,-55.24,-39.65,-54.39,-46.51,-46.63,-60.93,-16.84,-43.89,-36.64,-35.66,-46.92,-24.17,-44.63,-26.04,-31.78,-44.16,-13.73,-49.11,-14.9,-28.42,-31.19,-14.84,-39.04,-15.94,-20.49,-25.02,-4.96,-29.55,-7.15,-23.8,-23.52,3.27,-29.46,2.08,-12.12,-14.8,-1.12,-29.05,-0.09,-15.16</v>
       </c>
     </row>
     <row r="26">
@@ -682,7 +682,7 @@
         <v>[L_01_标记]</v>
       </c>
       <c r="C26" t="str">
-        <v>a: 15.6ms -88.3uv b: 34.6ms 405.1uv</v>
+        <v>a: 15.5ms -50.4uv b: 34.3ms 193.1uv</v>
       </c>
     </row>
     <row r="27">
@@ -693,7 +693,7 @@
         <v>[R_02_名字]</v>
       </c>
       <c r="C27" t="str">
-        <v>FERG(2)_dMax</v>
+        <v>FERG(2)_dRod</v>
       </c>
     </row>
     <row r="28">
@@ -715,7 +715,7 @@
         <v>[R_02_闪光]</v>
       </c>
       <c r="C29" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.03cd.m-2,5ms</v>
       </c>
     </row>
     <row r="30">
@@ -726,7 +726,7 @@
         <v>[R_02_闪光背景]</v>
       </c>
       <c r="C30" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="31">
@@ -737,7 +737,7 @@
         <v>[R_02_采样]</v>
       </c>
       <c r="C31" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="32">
@@ -748,7 +748,7 @@
         <v>[R_02_分析时间]</v>
       </c>
       <c r="C32" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="33">
@@ -770,7 +770,7 @@
         <v>[R_02_详细数据(uv)]</v>
       </c>
       <c r="C34" t="str">
-        <v>0.54,-1.07,1.55,-1.99,2.36,-2.66,2.87,-2.98,2.99,-2.91,2.73,-2.47,2.11,-1.7,1.21,-0.71,0.15,0.36,-0.94,1.38,-1.92,2.2,-2.66,2.71,-3.08,2.84,-3.14,2.55,-2.86,1.85,-2.28,0.8,-1.54,-0.5,-0.78,-1.95,-0.17,-3.45,0.12,-4.9,-0.09,-6.26,-0.91,-7.53,-2.46,-8.78,-4.77,-10.13,-7.87,-11.73,-11.71,-13.79,-16.26,-16.54,-21.43,-20.16,-27.15,-24.83,-33.35,-30.64,-39.98,-37.64,-46.97,-45.73,-54.29,-54.76,-61.88,-64.45,-69.66,-74.45,-77.5,-84.32,-85.24,-93.59,-92.62,-101.75,-99.33,-108.31,-104.96,-112.79,-109.07,-114.77,-111.14,-113.89,-110.67,-109.86,-107.14,-102.48,-100.12,-91.62,-89.24,-77.22,-74.24,-59.29,-55.01,-37.87,-31.56,-13.09,-4.06,14.94,27.19,46.03,61.8,79.99,99.28,116.6,139.11,155.6,180.75,196.68,223.69,239.51,267.43,283.71,311.57,328.88,355.75,374.55,399.67,420.26,443.08,465.52,485.8,509.84,527.6,552.77,568.31,593.87,607.67,632.77,645.44,669.14,681.3,702.71,714.9,733.27,745.87,760.68,773.81,784.81,798.35,805.58,819.14,822.94,835.9,836.81,848.43,847.16,856.62,853.92,860.46,857.05,860.06,856.5,855.6,852.25,847.35,844.34,835.65,832.83,820.85,817.87,803.33,799.67,783.48,778.52,761.64,754.81,738.14,728.97,713.27,701.48,687.27,672.85,660.4,643.59,632.86,614.19,604.88,585.06,576.68,556.58,548.49,529.02,520.57,502.56,493.17,477.31,466.56,453.3,440.98,430.47,416.66,408.77,393.78,388.08,372.46,368.3,352.73,349.36,334.59,331.2,317.94,313.78,302.62,297.11,288.42,281.23,275.1,266.16,262.41,251.94,250.14,238.59,238.08,226.09,226.09,214.39,214.08,203.4,202.04,192.99,189.99,183.02,178.03,173.3,166.26,163.69,154.82,154.04,143.81,144.25,133.32,134.27,123.41,124.09,114.09,113.78,105.31,103.45,97.01,93.23,89.08,83.3,81.41,73.81,73.88,64.93,66.41,56.75,58.94,49.34,51.48,42.71,44.05,36.8,36.73,31.53,29.64,26.77,22.91,22.35,16.67,18.15,11.04,14.02,6.08,9.87,1.84,5.65,-1.7,1.36,-4.62,-2.95,-7.02,-7.2,-9.06,-11.29,-10.9,-15.09,-12.71,-18.5,-14.62,-21.44,-16.74,-23.87,-19.13,-25.8,-21.8,-27.29,-24.69,-28.44,-27.73,-29.38,-30.79,-30.26,-33.74,-31.24,-36.47,-32.46,-38.88,-34,-40.9,-35.91,-42.52,-38.21,-43.78,-40.83,-44.77,-43.68,-45.59,-46.63,-46.39,-49.55,-47.31,-52.3,-48.47,-54.77,-49.98,-56.88,-51.87,-58.6,-54.16,-59.96,-56.78,-61.02,-59.65,-61.9,-62.63,-62.72,-65.58,-63.63,-68.37,-64.74,-70.87,-66.16,-72.99,-67.94,-74.7,-70.09,-76.02,-72.55,-76.99,-75.24,-77.73,-78.04,-78.35,-80.8,-79.01,-83.37,-79.82,-85.64,-80.89,-87.5,-82.28,-88.92,-84,-89.91,-86.02,-90.5,-88.24,-90.81,-90.56,-90.95,-92.82,-91.06,-94.89,-91.29,-96.63,-91.72,-97.95,-92.44,-98.81,-93.46,-99.19,-94.76,-99.15,-96.26,-98.77,-97.84,-98.19,-99.37,-97.55,-100.71,-96.97,-101.72,-96.57,-102.31,-96.43,-102.42,-96.59,-102.05,-97.02,-101.23,-97.66,-100.06,-98.39,-98.65,-99.1,-97.16,-99.63,-95.72,-99.85,-94.45,-99.67,-93.44,-99.03,-92.73,-97.91,-92.31,-96.34,-92.12,-94.42,-92.07,-92.27,-92.02,-90.03,-91.84,-87.84,-91.39,-85.83,-90.58,-84.08,-89.33,-82.67,-87.63,-81.57,-85.51,-80.75,-83.06,-80.11,-80.38,-79.53,-77.62,-78.88,-74.92,-78.01,-72.42,-76.82,-70.21,-75.24,-68.37,-73.24,-66.88,-70.86,-65.71,-68.15,-64.78,-65.24,-63.97,-62.27,-63.13,-59.37,-62.14,-56.69,-60.87,-54.32,-59.26,-52.34,-57.27,-50.76,-54.91,-49.54,-52.25,-48.61,-49.4,-47.83,-46.5,-47.09,-43.68,-46.24,-41.08,-45.16,-38.81,-43.77,-36.95,-42.03,-35.51,-39.93,-34.47,-37.55,-33.74,-34.97,-33.21,-32.34,-32.75,-29.78,-32.23,-27.45,-31.5,-25.45,-30.48,-23.85,-29.13,-22.69,-27.43,-21.94,-25.44,-21.53,-23.24</v>
+        <v>-18.9,-24.4,-17.9,-24.86,-17.04,-25.1,-16.35,-25.11,-15.84,-24.87,-15.55,-24.39,-15.46,-23.67,-15.58,-22.75,-15.88,-21.65,-16.34,-20.44,-16.94,-19.14,-17.61,-17.82,-18.32,-16.51,-19.06,-15.28,-19.76,-14.26,-20.4,-13.33,-20.87,-12.84,-21.35,-12.47,-21.46,-12.34,-21.67,-12.62,-21.44,-13.28,-21.67,-14.48,-21.33,-15.76,-21.22,-16.78,-21.53,-18.41,-20.92,-20.37,-21.12,-22.62,-20.25,-26.09,-21.32,-28.69,-22.26,-30.57,-22.14,-33.41,-24.04,-34.04,-26.91,-37.39,-26.64,-40.42,-35.44,-38.5,-32.03,-43.69,-35.56,-44.53,-47.19,-46.41,-40.35,-54.26,-42.49,-55.36,-60.06,-52.03,-51.15,-59.16,-55.72,-60.3,-61.3,-59.74,-61.92,-41.41,-51.72,-43.69,-57.78,-57.16,-71.25,-53.81,-53.32,-44.88,-62.66,-54.42,-30.28,-17.97,-33.01,-24.37,-31.54,-23.99,-14.34,-12.33,-5.66,-3.64,5.5,5.66,26.92,13.72,34.41,36.91,38.72,58.48,49.34,67.18,67.93,55.33,79.23,98.22,115.68,93.8,111.94,122.19,142.83,139.8,143.98,156.96,167.5,189.31,200.13,181.55,203.71,209.46,228.2,212.85,204.75,228.9,228.54,264.19,255.96,295,252.54,301.12,254.94,290.7,320.15,296.99,284.07,343.29,329.57,339.83,343.8,297.91,321.27,336.57,357.45,369.34,389.94,365.57,352.18,384.36,344.78,403.51,340.07,340.82,372.3,325.7,392.95,315.71,402.83,355.82,401.29,360.89,338.18,341.6,361,386.16,347.37,306.79,316.28,372.01,359.26,364.65,363.6,328.57,336.75,323.71,332.75,271.08,273.09,278.29,257.6,255.74,242.87,267.43,286.26,237.59,272.97,220.11,209.53,234.73,199.59,221.39,221.48,204.01,201.41,212,182.1,185.47,181.63,161.28,177.38,157.65,155.88,154.96,138.02,135.19,125.54,126.14,110.38,112.12,97.78,86.76,110.18,98.2,96.35,66.13,72.8,60.55,70.22,67.33,60.48,53.84,60.98,37.92,56.52,39.33,38.03,32.37,30.62,33.87,30.52,22.05,19.87,18.98,16.29,14.86,13.62,11.81,10.05,13.54,4.82,7.8,0.47,6.7,-4.91,4.83,-5.08,2.64,-7.8,1.37,-9.41,-2.92,-11.59,-3.75,-12.72,-6.96,-11.41,-8.76,-13.78,-9.52,-12.26,-12.48,-11.46,-12.34,-11.62,-15.39,-10.51,-18.48,-11.64,-19.82,-12.68,-20.31,-9.56,-21.85,-11.04,-22.85,-13.11,-20.58,-11.49,-24.89,-13.79,-22.16,-12.78,-20.17,-14.1,-20.98,-17.47,-19.12,-18.35,-17.67,-25.65,-24.91,-23.24,-22.97,-29.82,-23.93,-29.46,-27.6,-35.56,-28.48,-31.55,-23.92,-38.35,-21.17,-35.52,-33.11,-32.36,-23.08,-43.24,-25.04,-45.18,-26.49,-38.06,-31.11,-31.58,-39.56,-37.76,-32.57,-45.8,-37.9,-41.16,-53.52,-32.39,-43.84,-37.32,-55.2,-35.94,-41.24,-40.85,-48.38,-34.32,-52.97,-40.83,-64.16,-48.61,-52.13,-51.78,-49.81,-42.74,-44.56,-53.83,-67.66,-47.79,-55,-54.94,-58.38,-71.95,-44.36,-68.33,-69.86,-47.7,-45.36,-49.61,-62.34,-68.25,-49.93,-74.53,-47.33,-55.21,-59.64,-76.67,-71.45,-62.53,-53.86,-57.84,-57.3,-61.59,-57.13,-59.37,-49.55,-78.05,-60.29,-80.62,-70.31,-68.09,-71.61,-65.25,-64.94,-58.93,-75.41,-68.09,-65.66,-77.94,-60.92,-72.59,-74,-45.07,-59,-75.63,-73.38,-58.32,-65.49,-80.59,-62.32,-64.38,-54.62,-47.97,-85.68,-57.69,-62.77,-60.83,-60.37,-62.44,-56.25,-69.15,-61.85,-72.99,-68.9,-71.62,-69.27,-67.96,-55.94,-65.93,-71.74,-75.07,-45.12,-52.1,-55.12,-57.46,-69.12,-64.74,-55.31,-56.88,-61.75,-52.47,-42.7,-46.94,-56.63,-60.54,-63.29,-58.99,-57.05,-56.15,-59.94,-44.2,-39.23,-34.75,-55.22,-31.1,-57.04,-30.4,-53.82,-37.57,-43.55,-28.5,-49.39,-43.41,-32.86,-24.41,-48.29,-39.33,-28.89,-25.1,-32.6,-23.99,-25.5,-35.14,-32.45,-21.02,-23.59,-29.69,-19.44,-21.96,-23.39,-26.69,-21.28,-27.39,-17.35,-22.07,-12.34,-20.34,-11.37,-22.41,-13.18,-29.27,-17.31,-25.54,-15.17,-23.43,-12.02,-20.6,-16.38,-25.1,-22.08</v>
       </c>
     </row>
     <row r="35">
@@ -781,7 +781,7 @@
         <v>[R_02_标记]</v>
       </c>
       <c r="C35" t="str">
-        <v>a: 17.6ms -187.8uv b: 38.6ms 839.8uv</v>
+        <v>a: 16.7ms -39.2uv b: 37.0ms 185.7uv</v>
       </c>
     </row>
     <row r="36">
@@ -792,7 +792,7 @@
         <v>[L_02_名字]</v>
       </c>
       <c r="C36" t="str">
-        <v>FERG(2)_dMax</v>
+        <v>FERG(2)_dRod</v>
       </c>
     </row>
     <row r="37">
@@ -814,7 +814,7 @@
         <v>[L_02_闪光]</v>
       </c>
       <c r="C38" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.03cd.m-2,5ms</v>
       </c>
     </row>
     <row r="39">
@@ -825,7 +825,7 @@
         <v>[L_02_闪光背景]</v>
       </c>
       <c r="C39" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="40">
@@ -836,7 +836,7 @@
         <v>[L_02_采样]</v>
       </c>
       <c r="C40" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="41">
@@ -847,7 +847,7 @@
         <v>[L_02_分析时间]</v>
       </c>
       <c r="C41" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="42">
@@ -869,7 +869,7 @@
         <v>[L_02_详细数据(uv)]</v>
       </c>
       <c r="C43" t="str">
-        <v>-0.56,1.1,-1.61,2.05,-2.43,2.71,-2.91,2.99,-2.98,2.85,-2.63,2.31,-1.92,1.44,-0.94,0.37,0.17,-0.76,1.25,-1.79,2.14,-2.59,2.71,-3.04,2.88,-3.1,2.61,-2.77,1.91,-2.12,0.85,-1.28,-0.44,-0.41,-1.85,0.31,-3.25,0.7,-4.53,0.59,-5.64,-0.14,-6.58,-1.57,-7.42,-3.72,-8.29,-6.57,-9.39,-10.06,-10.92,-14.11,-13.13,-18.64,-16.22,-23.57,-20.36,-28.85,-25.66,-34.47,-32.13,-40.42,-39.68,-46.73,-48.14,-53.42,-57.24,-60.47,-66.63,-67.82,-75.93,-75.36,-84.7,-82.87,-92.52,-90.03,-98.95,-96.44,-103.63,-101.63,-106.19,-105.06,-106.36,-106.17,-103.88,-104.44,-98.57,-99.39,-90.26,-90.64,-78.86,-77.95,-64.27,-61.21,-46.45,-40.46,-25.37,-15.88,-1.07,12.22,26.4,43.44,56.91,77.33,90.3,113.41,126.32,151.2,164.65,190.28,204.9,230.28,246.65,270.87,289.4,311.81,332.65,352.87,375.88,393.87,418.61,434.61,460.38,474.89,500.78,514.46,539.48,553.01,576.22,590.19,610.77,625.62,642.99,658.86,672.75,689.5,699.94,717.12,724.47,741.37,746.19,761.96,764.99,778.69,780.67,791.46,793.07,800.25,801.98,805.15,807.23,806.31,808.7,803.94,806.31,798.27,800.06,789.55,790.08,778.01,776.56,763.89,759.81,747.39,740.24,728.7,718.3,708,694.49,685.5,669.32,661.39,643.27,635.93,616.78,609.39,590.21,582.11,563.87,554.45,537.96,526.79,512.61,499.52,487.9,472.99,463.86,447.54,440.51,423.42,417.85,400.79,395.91,379.75,374.74,360.28,354.4,342.27,335,325.58,316.64,309.98,299.4,295.25,283.35,281.17,268.53,267.55,254.9,254.25,242.38,241.19,230.83,228.36,220.07,215.77,209.86,203.51,199.98,191.67,190.23,180.33,180.41,169.56,170.4,159.39,160.15,149.8,149.67,140.74,139.03,132.09,128.37,123.72,117.86,115.49,107.66,107.28,97.95,98.97,88.84,90.53,80.41,81.94,72.69,73.28,65.63,64.65,59.14,56.2,53.09,48.1,47.33,40.51,41.73,33.58,36.18,27.41,30.59,22.03,24.96,17.42,19.31,13.5,13.74,10.12,8.36,7.14,3.3,4.35,-1.29,1.62,-5.31,-1.21,-8.69,-4.22,-11.43,-7.43,-13.58,-10.82,-15.24,-14.29,-16.55,-17.73,-17.69,-21.01,-18.84,-23.99,-20.15,-26.57,-21.75,-28.68,-23.7,-30.31,-26.01,-31.51,-28.63,-32.38,-31.46,-33.06,-34.35,-33.72,-37.17,-34.51,-39.76,-35.58,-42.02,-37.02,-43.87,-38.89,-45.31,-41.16,-46.39,-43.78,-47.19,-46.61,-47.86,-49.52,-48.55,-52.34,-49.41,-54.92,-50.58,-57.16,-52.13,-58.99,-54.11,-60.4,-56.48,-61.45,-59.15,-62.23,-62.01,-62.88,-64.89,-63.56,-67.64,-64.41,-70.11,-65.56,-72.19,-67.07,-73.83,-68.98,-75.03,-71.24,-75.84,-73.76,-76.38,-76.4,-76.78,-79.02,-77.2,-81.44,-77.79,-83.53,-78.65,-85.18,-79.86,-86.36,-81.42,-87.07,-83.29,-87.38,-85.38,-87.4,-87.53,-87.28,-89.6,-87.18,-91.42,-87.24,-92.86,-87.56,-93.84,-88.21,-94.3,-89.18,-94.29,-90.44,-93.87,-91.86,-93.17,-93.31,-92.34,-94.63,-91.53,-95.67,-90.89,-96.3,-90.51,-96.45,-90.46,-96.07,-90.73,-95.23,-91.26,-93.99,-91.93,-92.49,-92.6,-90.88,-93.13,-89.33,-93.35,-87.97,-93.15,-86.91,-92.47,-86.17,-91.29,-85.77,-89.65,-85.61,-87.66,-85.61,-85.45,-85.59,-83.19,-85.42,-81.02,-84.95,-79.08,-84.08,-77.47,-82.73,-76.22,-80.92,-75.32,-78.69,-74.69,-76.15,-74.21,-73.45,-73.73,-70.75,-73.1,-68.21,-72.18,-65.94,-70.87,-64.05,-69.12,-62.56,-66.94,-61.43,-64.39,-60.59,-61.6,-59.91,-58.69,-59.24,-55.85,-58.43,-53.21,-57.34,-50.91,-55.88,-49.02,-54.01,-47.55,-51.75,-46.48,-49.16,-45.7,-46.38,-45.08,-43.54,-44.48,-40.81,-43.73,-38.34,-42.72,-36.24,-41.35,-34.58,-39.59,-33.37,-37.46,-32.56,-35.05,-32.04,-32.48,-31.68,-29.9,-31.32,-27.47,-30.81,-25.33,-30.02,-23.59,-28.89,-22.3,-27.37,-21.47,-25.5,-21.03,-23.38,-20.87,-21.12</v>
+        <v>17.86,2.8,14.07,7.46,9.3,12.7,4.71,17.35,1.43,20.38,0.3,21.15,1.66,19.59,5.3,16.15,10.48,11.76,16.1,7.58,20.97,4.71,24.08,3.96,24.83,5.62,23.17,9.44,19.62,14.65,15.12,20.11,10.82,24.67,7.83,27.32,6.93,27.51,8.35,25.23,11.81,21.09,16.55,16,21.4,11.15,25.2,7.5,27.01,6.14,26.3,6.8,22.8,9.74,17.65,13.34,11.63,17.2,5.65,19.82,1.54,19.98,-0.96,18.79,-0.8,12.91,0.29,6.14,2.62,0.16,4.7,-7.89,4.98,-12.11,4.47,-17.63,0.41,-17.12,-8.03,-16.84,-13.32,-18.07,-19.56,-20.15,-29.15,-24.41,-44.17,-22.24,-38.66,-24.15,-50,-33.23,-45.44,-46.63,-41.79,-48.72,-44.85,-61.46,-42.61,-47.68,-24.84,-64.36,-36.65,-54.18,-36.81,-44.4,-37.26,-28.08,-36.94,-14.67,-21.55,-16.48,-34.12,-6.24,-11.97,0.83,-14.56,22.43,-3.73,24.41,22.81,22.97,34.01,40.24,64.83,54.91,76.64,68.92,89.79,84.25,101.3,102.18,106.03,136.92,130.04,163.54,138.11,158.76,151.01,170.73,177.25,221.69,193.97,220.98,226.69,231.99,230.13,254.27,279.36,264.95,271.56,246.16,294.32,280.56,285.85,285.6,289.77,336.28,357.46,327.45,323.89,347.39,376.29,344.24,341.18,396.75,370.84,358.26,389.79,371.81,399.95,382.96,393,341.43,371.27,403.41,403.49,347.62,367.57,401.06,431.66,363.72,343.57,397.91,396.89,385.71,367.02,390.23,316.73,372.82,323.39,357.8,362.36,366.51,302.43,331.78,328,290.28,334.18,278.57,305.64,252.19,309.68,257.63,264.48,233.83,273.21,261.91,266.91,250.41,205.59,196.94,208.17,195.18,201.49,195.99,186.45,177.63,155.28,184.32,145.94,153.03,142.06,141.86,136.1,128.28,117.03,111.46,121.29,96.84,109.07,87.29,87.05,73.47,77.51,71.21,60.82,65.97,49.34,66.35,42.21,61.07,31.91,54.67,30.21,43.23,28.9,36.78,27.67,24.79,31.95,16.82,32.07,12.03,30.73,6.21,26.37,5,19.74,6.97,12.54,9.34,6.7,14.1,-1.26,15.21,-3.64,15.41,-5.27,13.25,-3.78,9.98,-2.57,3.52,2.66,-2.56,7.57,-5.48,11.38,-9.26,10.5,-8.78,11.81,-7.62,7.84,-1.94,0.8,2.75,-2.73,7.17,-8.52,10.86,-11.27,9.04,-10.42,10.98,-5.46,4.43,-2.14,2.59,0.42,-1.19,2.76,-6.38,7.27,-11.22,10.05,-14.28,5.26,-12.52,4.71,-10.45,-1.3,-2.22,-10.53,-1.78,-16.5,-2.61,-15.36,-3.21,-16.76,0.28,-21.04,-6.17,-13.66,-15.09,-15.99,-20.72,-9.25,-27.65,-7.67,-35.29,-17.83,-29.68,-19.1,-35.47,-20.23,-32.18,-22.4,-29.1,-35.25,-16.65,-43.81,-25.17,-45.57,-23.49,-39.65,-20.54,-45.4,-26.54,-30.72,-47,-36.83,-48.02,-28.45,-52.78,-36.74,-44.21,-39.1,-51.47,-42.04,-47.7,-30.26,-39.62,-56.33,-52.97,-47.47,-43.97,-68.53,-29.57,-66.43,-44.73,-54.65,-30.26,-41.77,-30.2,-53.17,-53.82,-55.64,-56.95,-44.3,-43.42,-28.11,-66.15,-55.66,-48.32,-35.6,-54.18,-55.75,-47.28,-46.72,-52.2,-46.5,-41.75,-60,-52.36,-50.21,-50.78,-70.75,-37.3,-66.87,-65.01,-40.81,-59.66,-56.89,-71.65,-35.39,-66.2,-54.75,-52.89,-62.42,-77.93,-50.31,-59.7,-51.17,-70.93,-48.75,-67.08,-79.15,-47.21,-70.84,-56.68,-81.76,-52.27,-79.83,-55.61,-54.08,-71.04,-56.04,-61.27,-66.79,-56.71,-53.7,-58.53,-61.25,-53.59,-33.2,-76.49,-47.7,-73.11,-46.62,-37.56,-66.98,-57.69,-58.65,-54.9,-51.33,-48.89,-57.18,-31.07,-41.92,-49.17,-37.75,-52.88,-38.82,-51.68,-41.19,-47.72,-31.04,-49.06,-35.23,-48.3,-32.29,-47.77,-36.66,-43.1,-22.08,-23.11,-40.13,-28.86,-34.08,-26.16,-32.95,-9.73,-40.49,-12.31,-23.66,-12.59,-18.85,-21.22,-15.01,-24.4,-8.02,-33.25,-4.13,-21.79,-2.92,-29.96,-12.42,-25.48,-13.71,-20.64,-13.61,-7.1,-18.9,-2.32,-18.05,-7.67,-26.3,1.47</v>
       </c>
     </row>
     <row r="44">
@@ -880,7 +880,7 @@
         <v>[L_02_标记]</v>
       </c>
       <c r="C44" t="str">
-        <v>a: 17.6ms -176.6uv b: 38.6ms 789.4uv</v>
+        <v>a: 16.7ms -40.3uv b: 36.8ms 186.2uv</v>
       </c>
     </row>
     <row r="45">
@@ -891,7 +891,7 @@
         <v>[R_03_名字]</v>
       </c>
       <c r="C45" t="str">
-        <v>FERG(3)_dOps</v>
+        <v>FERG(3)_dRod</v>
       </c>
     </row>
     <row r="46">
@@ -913,7 +913,7 @@
         <v>[R_03_闪光]</v>
       </c>
       <c r="C47" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.10cd.m-2,5ms</v>
       </c>
     </row>
     <row r="48">
@@ -924,7 +924,7 @@
         <v>[R_03_闪光背景]</v>
       </c>
       <c r="C48" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="49">
@@ -935,7 +935,7 @@
         <v>[R_03_采样]</v>
       </c>
       <c r="C49" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="50">
@@ -946,7 +946,7 @@
         <v>[R_03_分析时间]</v>
       </c>
       <c r="C50" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="51">
@@ -968,7 +968,7 @@
         <v>[R_03_详细数据(uv)]</v>
       </c>
       <c r="C52" t="str">
-        <v>-11.61,-9.77,-12.28,-8.42,-12.71,-7.4,-12.88,-6.9,-12.86,-7.09,-12.71,-8,-12.53,-9.55,-12.36,-11.52,-12.19,-13.58,-11.96,-15.3,-11.55,-16.3,-10.85,-16.26,-9.81,-15.08,-8.5,-12.87,-7.12,-10.04,-6,-7.18,-5.57,-5,-6.2,-4.12,-8.11,-4.94,-11.25,-7.47,-15.21,-11.28,-19.23,-15.54,-22.36,-19.15,-23.61,-21.04,-22.22,-20.42,-17.96,-17.04,-11.25,-11.4,-3.24,-4.67,4.39,1.47,9.72,5.25,11.04,5.22,7.39,0.75,-1.15,-7.68,-13.26,-18.47,-26.51,-29.12,-37.86,-36.82,-44.31,-39.08,-43.68,-34.51,-35.24,-23.29,-20.13,-7.37,-1.27,9.84,17.2,24.15,30.76,31.63,35.67,29.58,29.94,17.43,14.01,-2.92,-9.12,-27.33,-34.45,-50.23,-56.05,-65.95,-68.47,-70.06,-68.11,-60.63,-54.27,-38.9,-29.48,-9.17,0.9,22.02,29.91,47.39,50.56,60.65,57.57,58.08,48.78,39.61,25.73,8.9,-6.52,-27.31,-40.59,-60.8,-68.46,-83.77,-83.46,-90.73,-81.88,-79.87,-63.92,-53.53,-33.69,-17.67,1.76,19.53,34.15,49.59,55.95,65.77,62.2,64.63,51.65,46.78,27.03,16.68,-5.69,-18.52,-38.77,-50.73,-64.6,-72.82,-77.49,-80.31,-74.97,-72.22,-58.23,-51.2,-31.69,-22.72,-1.84,6.4,24.4,29.61,41.31,42.17,45.64,42.08,37.22,30.39,18.77,10.7,-4.88,-11.87,-28.09,-32.01,-45.77,-45.46,-54.47,-49.89,-53.06,-45.27,-42.77,-33.63,-26.69,-18.39,-8.88,-3.43,6.62,7.92,16.73,13.53,19.88,12.84,16.23,6.83,7.37,-2.41,-4.15,-12.34,-15.56,-20.56,-24.49,-25.4,-29.43,-26.21,-29.96,-23.33,-26.65,-17.96,-20.8,-11.69,-14.03,-6.1,-7.87,-2.41,-3.46,-1.23,-1.33,-2.52,-1.46,-5.65,-3.33,-9.69,-6.18,-13.6,-9.23,-16.53,-11.82,-17.95,-13.58,-17.73,-14.4,-16.11,-14.42,-13.59,-13.92,-10.79,-13.21,-8.31,-12.53,-6.59,-12.03,-5.86,-11.73,-6.15,-11.55,-7.27,-11.39,-8.94,-11.13,-10.81,-10.72,-12.54,-10.17,-13.88,-9.58,-14.68,-9.07,-14.86,-8.77,-14.48,-8.79,-13.65,-9.17,-12.51,-9.89,-11.24,-10.85,-10.02,-11.9,-9,-12.87,-8.29,-13.6,-7.96,-13.95,-8.05,-13.88,-8.53,-13.37,-9.34,-12.52,-10.36,-11.43,-11.46,-10.29,-12.5,-9.25,-13.35,-8.47,-13.88,-8.07,-14.02,-8.09,-13.76,-8.54,-13.12,-9.34,-12.2,-10.39,-11.11,-11.52,-10.02,-12.59,-9.06,-13.44,-8.38,-13.95,-8.07,-14.05,-8.18,-13.73,-8.69,-13.03,-9.54,-12.06,-10.59,-10.94,-11.71,-9.85,-12.74,-8.92,-13.53,-8.29,-13.98,-8.05,-14.01,-8.23,-13.63,-8.8,-12.88,-9.69,-11.88,-10.77,-10.76,-11.89,-9.68,-12.89,-8.8,-13.63,-8.23,-14.01,-8.05,-13.98,-8.3,-13.53,-8.93,-12.73,-9.86,-11.7,-10.96,-10.58,-12.07,-9.52,-13.03,-8.68,-13.72,-8.17,-14.04,-8.06,-13.93,-8.38,-13.42,-9.06,-12.58,-10.03,-11.52,-11.14,-10.4,-12.24,-9.37,-13.17,-8.57,-13.8,-8.12,-14.05,-8.09,-13.87,-8.46,-13.3,-9.21,-12.42,-10.21,-11.34,-11.32,-10.22,-12.4,-9.22,-13.29,-8.47,-13.87,-8.09,-14.05,-8.12,-13.81,-8.56,-13.18,-9.35,-12.25,-10.38,-11.16,-11.51,-10.05,-12.57,-9.08,-13.41,-8.38,-13.93,-8.06,-14.04,-8.17,-13.73,-8.67,-13.05,-9.51,-12.08,-10.57,-10.97,-11.69,-9.87,-12.72,-8.94,-13.52,-8.3,-13.97,-8.05,-14.02,-8.22,-13.64,-8.79,-12.9,-9.67,-11.91,-10.75,-10.79,-11.87,-9.71,-12.87,-8.81,-13.62,-8.23,-14.01,-8.05,-13.98,-8.29,-13.54,-8.91,-12.76,-9.84,-11.73,-10.93,-10.61,-12.04,-9.54,-13.01,-8.7,-13.71,-8.18,-14.03,-8.06,-13.94,-8.36,-13.44,-9.04,-12.6,-10.01,-11.55,-11.11,-10.42,-12.21,-9.39,-13.15,-8.59,-13.79,-8.13,-14.05,-8.08,-13.88,-8.45,-13.32,-9.19,-12.44,-10.18,-11.37,-11.3,-10.25,-12.38,-9.24,-13.28,-8.49,-13.86,-8.09,-14.05,-8.11,-13.82,-8.55,-13.2,-9.33,-12.28,-10.36,-11.18</v>
+        <v>-7.45,2.61,-3.48,-0.75,1.08,-4.18,5.16,-6.66,7.8,-7.41,8.44,-6.14,7.01,-3.06,3.98,1.1,0.25,5.34,-3.16,8.61,-5.28,10.1,-5.53,9.47,-3.8,6.88,-0.57,3,3.35,-1.17,6.84,-4.58,9,-6.37,9.15,-6.14,7.19,-4.15,3.53,-0.9,-1.08,2.63,-5.39,5.16,-8.48,6.18,-9.86,5.34,-8.99,1.79,-6.61,-2.41,-3.3,-7.41,-0.41,-11.88,1.57,-14.73,0.18,-15.49,-1.48,-14.41,-6.29,-12.48,-10.38,-8.43,-16.8,-6.79,-21.5,-4.44,-22.21,-8.04,-23.14,-12.26,-23.64,-17.31,-23.67,-24.32,-15.2,-26.38,-13.87,-36.45,-16.28,-30.99,-22.83,-39.12,-24.51,-30.65,-25.84,-37.14,-41.68,-26.07,-33.31,-35.58,-49.53,-24.76,-43.75,-34.3,-45.83,-25.2,-31.83,-45.17,-22.11,-47.01,-25.19,-32.68,-23.43,-30.02,-26.37,-22.6,-1.31,-6.18,-6.25,-2.17,-0.2,4.74,13.23,6.8,18.51,31.26,28.61,44.35,43.25,37.68,37.79,44.98,85.22,65.74,88.46,85.57,105.07,74.52,109.85,111.22,140.03,128.56,157.96,133.57,130.11,169.19,168.87,189.6,190.84,193.61,184.46,201.83,226.7,255.01,244.79,255.05,247.57,237.44,289.45,257.8,290.96,261.23,308.95,264.74,322.4,302.83,312.5,308.86,351.08,313.16,300.45,305.3,345.54,350.96,327.93,387.74,366.06,320.93,383.11,341.26,370.52,404.62,408.05,380.88,418.07,374.03,397.06,405.5,384.19,363.87,336.88,387.74,387.26,407.34,361.77,333.5,372.21,334.91,337.49,363.49,373.46,367.61,356.54,354.19,369.53,338.08,290.32,304.33,337.39,301.42,283.21,292.39,297.37,292.88,253.99,283.36,256.08,263.13,248.95,250.51,225.25,257.99,202.72,225.3,210.09,203.96,202.87,179.47,184.7,162.51,169.92,166.9,151.62,149.51,148.39,125.1,142.03,133,142.94,110.44,123.37,128.46,103.4,106.11,86.6,106.87,72.52,95.77,80.38,79.89,78.18,63.23,71.06,60.31,65,50.91,59.03,41.98,50.27,31.52,51.54,32.24,39.15,35.88,33.41,31.66,28.22,30.6,21.12,34.04,12.73,28.34,13.83,22.94,14.48,18.06,15.04,10.44,15.96,5.16,18.76,1.52,16.9,1.05,15.65,0.54,10.61,5.19,6.98,6.7,1.25,7.97,-4.66,8.35,-5.21,8.17,-4.5,9,-2.94,3.94,-2.26,-4.59,-1.67,-5.6,4.46,-10.48,4.63,-11.56,-0.94,-12.95,-2.63,-12.24,-4.04,-6.51,-12.74,-3.25,-14.8,-5.04,-20.12,-5.8,-19.58,-12.13,-21.4,-12.15,-14.66,-16.05,-14.72,-22.27,-10.99,-29.77,-12.53,-26.77,-16.82,-24.42,-23.56,-31.2,-26.11,-31.32,-22.4,-26.84,-26.14,-19.27,-35.53,-21.66,-38.96,-23.4,-34.98,-35.36,-29.4,-31.55,-23.34,-45.42,-25.28,-42.07,-24.93,-39.16,-26.39,-43.86,-37.69,-44.52,-24.83,-36.22,-32.04,-44.34,-34.36,-37.99,-40.94,-35.04,-44.41,-41.07,-38.42,-29.39,-36.08,-35.37,-32.99,-57.75,-46.82,-57.9,-40.06,-61.41,-39.06,-48.91,-53.89,-50.05,-30.27,-41.1,-49.32,-58.77,-68.6,-29.05,-56.79,-38.13,-58.09,-50.13,-68.39,-55.04,-72.42,-58.94,-64.67,-55.89,-62.64,-74.94,-56.88,-60.59,-35.11,-65.83,-42.16,-68.14,-49.84,-69.67,-63.11,-47.31,-82.26,-38.73,-76.82,-70.47,-65.24,-43.69,-52.22,-47.8,-68.02,-71.98,-78.48,-50.09,-62.93,-59.78,-57.05,-74.51,-53.9,-79.53,-57.59,-72.64,-65.51,-71.29,-65.62,-59.34,-52.51,-54.41,-55.17,-46.85,-52.05,-32.6,-67.02,-42.58,-58.66,-55.57,-52.44,-63.61,-50.37,-63.58,-51.25,-42.76,-50.18,-43.49,-44.01,-62.03,-36.11,-44.83,-51.01,-36.26,-48.21,-42.6,-52.14,-20.61,-39.82,-27.73,-33.85,-18.72,-36.29,-28.04,-35.44,-36.93,-23.61,-37.5,-21.68,-45.8,-14.66,-38.53,-24.9,-25.94,-13.39,-27.8,-26.7,-24.79,-23.67,-16.58,-29,-16.12,-33.58,-11.1,-24.08,-12.8,-32.96,-24.23,-27.56,-24.46,-16.97,-27.19,-16.37,-24.85,-10.29,-26.02,-6.09,-25.38,-12.48,-19.76</v>
       </c>
     </row>
     <row r="53">
@@ -979,7 +979,7 @@
         <v>[R_03_标记]</v>
       </c>
       <c r="C53" t="str">
-        <v>111uv</v>
+        <v>a: 18.8ms -39.1uv b: 40.5ms 315.4uv</v>
       </c>
     </row>
     <row r="54">
@@ -990,7 +990,7 @@
         <v>[L_03_名字]</v>
       </c>
       <c r="C54" t="str">
-        <v>FERG(3)_dOps</v>
+        <v>FERG(3)_dRod</v>
       </c>
     </row>
     <row r="55">
@@ -1012,7 +1012,7 @@
         <v>[L_03_闪光]</v>
       </c>
       <c r="C56" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.10cd.m-2,5ms</v>
       </c>
     </row>
     <row r="57">
@@ -1023,7 +1023,7 @@
         <v>[L_03_闪光背景]</v>
       </c>
       <c r="C57" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="58">
@@ -1034,7 +1034,7 @@
         <v>[L_03_采样]</v>
       </c>
       <c r="C58" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="59">
@@ -1045,7 +1045,7 @@
         <v>[L_03_分析时间]</v>
       </c>
       <c r="C59" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="60">
@@ -1067,7 +1067,7 @@
         <v>[L_03_详细数据(uv)]</v>
       </c>
       <c r="C61" t="str">
-        <v>-11.98,-7.52,-13.02,-7.48,-10.69,-10.13,-7.3,-12.21,-6.44,-11.28,-9.06,-8.47,-12.46,-7.34,-13.34,-9.77,-11.43,-13.82,-9.66,-15.69,-10.68,-13.78,-13.64,-10.3,-15,-8.62,-12.38,-9.5,-7.35,-10.37,-3.85,-8.54,-4.19,-4.64,-6.89,-2.37,-8.75,-4.71,-8.74,-10.71,-9.14,-16.4,-12.64,-18.76,-18.72,-18.36,-23.36,-17.85,-22.72,-18.16,-16.79,-17.07,-9.17,-11.65,-3.38,-2.28,0.2,6.67,3.34,10.22,6.48,6.89,6.88,-0.69,0.99,-9.09,-11.46,-17.23,-25.95,-26.07,-36.34,-35.2,-39.27,-40.89,-35.65,-38.21,-28,-25.52,-17.25,-6.69,-2.82,11.44,14.26,23.68,29.07,28.72,34.73,27.25,27.29,19.03,8.81,2.75,-14.3,-20.74,-35.73,-45.87,-52.16,-63.84,-62.05,-67.78,-63.07,-56.82,-51.99,-35.48,-28.06,-9.72,3.75,16.15,33.69,38.9,52.26,53.96,55.14,55.42,43.8,39.64,22.25,9.28,-5.93,-26.62,-37.19,-57.3,-65.71,-75.6,-83.17,-79.67,-82.52,-70.57,-62.82,-49.62,-30.56,-18.85,4.16,16.42,32.98,46.84,51.69,62.66,58.53,59.14,51.93,39.1,31.04,10.24,-1.09,-19.83,-36.08,-46.29,-63.15,-65.87,-74.78,-74.65,-70.23,-68.75,-54.03,-47.86,-31.64,-17.76,-6.73,11.65,17.64,31.84,36.74,39.66,44.57,36.95,37.63,26.64,18.44,10.33,-5.4,-10.59,-25.92,-32.18,-39.23,-47.84,-45.59,-52.02,-46.16,-44.3,-40.51,-29.68,-27.86,-14.59,-10.26,-2.47,6.5,6.69,16.14,13.41,16.37,16.06,10.06,11.99,1.99,1.16,-5.3,-12.23,-12.45,-22.24,-20.27,-25.76,-26.97,-24.34,-28.85,-21.66,-24.14,-19.42,-15.39,-16.25,-7.69,-10.46,-4.29,-3.32,-4.21,1.27,-4.3,0.41,-3.21,-4.66,-2.82,-9.73,-5.69,-11.67,-11.43,-11.22,-16.42,-11.47,-17.26,-13.87,-14.23,-16.42,-10.9,-15.94,-10.29,-11.94,-11.82,-7.5,-12.33,-6.22,-9.99,-8.46,-6.57,-11.11,-5.58,-11.09,-8.24,-8.75,-12.05,-7.28,-13.35,-8.99,-11.3,-12.51,-8.69,-14.27,-8.71,-12.45,-11.39,-9.04,-13.59,-7.68,-12.61,-9.64,-9.28,-12.46,-7.12,-12.79,-8.39,-10.14,-11.61,-7.47,-13.18,-7.83,-11.4,-10.89,-8.37,-13.33,-7.59,-12.48,-10,-9.36,-12.94,-7.5,-13.11,-8.98,-10.31,-12.11,-7.65,-13.35,-8.09,-11.27,-11.1,-8.18,-13.29,-7.54,-12.19,-10.06,-9.03,-12.92,-7.38,-12.92,-9.09,-10.06,-12.25,-7.57,-13.33,-8.25,-11.11,-11.34,-8.09,-13.37,-7.66,-12.06,-10.3,-8.88,-13.04,-7.39,-12.81,-9.27,-9.85,-12.4,-7.5,-13.27,-8.38,-10.9,-11.52,-7.95,-13.38,-7.74,-11.88,-10.5,-8.7,-13.13,-7.42,-12.68,-9.47,-9.66,-12.55,-7.45,-13.2,-8.54,-10.7,-11.71,-7.84,-13.39,-7.84,-11.7,-10.7,-8.54,-13.21,-7.45,-12.54,-9.66,-9.46,-12.69,-7.42,-13.13,-8.71,-10.49,-11.89,-7.74,-13.38,-7.96,-11.51,-10.91,-8.38,-13.27,-7.5,-12.4,-9.86,-9.27,-12.81,-7.39,-13.04,-8.88,-10.29,-12.06,-7.65,-13.36,-8.08,-11.32,-11.11,-8.23,-13.32,-7.56,-12.24,-10.06,-9.08,-12.93,-7.39,-12.94,-9.06,-10.08,-12.22,-7.57,-13.32,-8.22,-11.12,-11.3,-8.1,-13.36,-7.64,-12.08,-10.27,-8.9,-13.03,-7.39,-12.82,-9.25,-9.88,-12.38,-7.51,-13.28,-8.37,-10.93,-11.49,-7.97,-13.38,-7.73,-11.9,-10.47,-8.73,-13.12,-7.41,-12.7,-9.44,-9.68,-12.53,-7.46,-13.21,-8.52,-10.72,-11.68,-7.86,-13.39,-7.83,-11.72,-10.68,-8.56,-13.2,-7.45,-12.56,-9.64,-9.48,-12.67,-7.42,-13.14,-8.69,-10.52,-11.86,-7.75,-13.38,-7.94,-11.54,-10.88,-8.4,-13.26,-7.5,-12.42,-9.84,-9.29,-12.8,-7.4,-13.05,-8.86,-10.31,-12.04,-7.66,-13.36,-8.07,-11.35,-11.08,-8.25,-13.31,-7.56,-12.26,-10.04,-9.1,-12.91,-7.39,-12.95,-9.04,-10.11,-12.2,-7.58,-13.33,-8.2,-11.15,-11.28,-8.11,-13.35,-7.63,-12.1,-10.24,-8.92,-13.02,-7.39,-12.84,-9.22</v>
+        <v>18.16,8.78,22.18,6.62,25.78,5.03,28.78,4.15,31.02,4.08,32.4,4.85,32.86,6.46,32.42,8.83,31.14,11.86,29.12,15.37,26.53,19.17,23.53,23.05,20.35,26.78,17.19,30.13,14.26,32.91,11.75,34.93,9.81,36.06,8.55,36.23,8.04,35.4,8.29,33.62,9.28,30.96,10.89,27.54,12.99,23.58,15.41,19.25,17.99,14.77,20.54,10.44,22.77,6.4,24.53,3.01,25.75,0.24,26.22,-1.82,25.79,-2.72,24.29,-3.12,21.95,-2.61,19.62,-0.63,15.51,1.27,11.76,4.1,7.4,5.39,3.13,8.83,-0.64,10.09,-5.99,12.09,-9.31,11.89,-11.6,12.73,-15.25,11.9,-18.91,12.83,-17.78,10.15,-13.41,0.45,-21.3,-2.13,-16.9,-9.39,-10.19,-12.89,-18.32,-15.93,-7.86,-12.62,-14.95,-23.84,-15.95,-27.65,-9.47,-35.13,-7.51,-23.4,-4.74,-28.33,-0.77,-37.3,-5.05,-28.02,-13.69,-26.83,5.23,-3.55,11.12,-5.51,5.16,10.7,-9.7,1.88,0.15,40.8,1.21,21.64,22.52,36.22,35.3,42.34,31.36,70.66,60.76,83.4,61.86,91.05,86.89,102.9,75.23,109.51,116.18,126.5,120.07,158.06,138.7,162.24,188.18,185.42,162.6,196.94,189.1,168.42,199.25,185.97,254.77,199.84,268.95,213.81,284.69,271.67,267.83,269.73,267.67,295.78,333.91,275.5,332.02,349.48,340.1,317.24,363.54,363.18,372.8,370.45,367.9,400.15,370.16,338.3,325.81,414.07,399.92,379.79,329.56,391.78,348.5,416.48,360.95,386.09,417.23,423.42,362.57,412.53,372.15,410.2,344.45,370.49,398.75,389.14,373.6,347.67,390.12,352.98,352,334.98,336.47,365.03,330.68,356.25,359.19,308.41,363.22,312.66,286.13,308.85,283.02,308.41,275.89,301.22,244.86,280.32,274.33,258.14,245.69,243.73,220.72,224.86,199.82,202.07,172.26,216.83,182.96,190.51,175.45,187.76,157.36,182.32,140.61,140.63,119.43,135.8,130.3,115.59,100.7,119.59,100.97,90.97,92.98,93.13,87.55,81.23,87.51,68.32,91.42,61.74,84.06,53.24,72.01,50.74,67.56,39.13,62.4,41.35,59.44,34.15,55.09,37.9,47.42,37.01,38.94,34.14,32.49,38.13,28.69,37.2,22.63,40.05,18.92,40.7,17.41,42.18,12.82,39.78,12.06,39.33,12.35,36.64,9.98,32.58,12.83,29.71,14.01,23.83,14.25,21.79,19.46,15.4,19.81,9.42,23.74,6.73,23.76,1.59,22.99,1.34,24.03,-1.06,23.58,-4.02,23.67,-7.77,21.33,-7.61,16.82,-3.77,8.5,-7.11,7.76,-2.92,3.61,-3.75,-2.77,3.9,-11.67,0.89,-16.57,5.12,-20.36,2.71,-20.82,7.22,-28.11,-1.85,-30.51,3.72,-23.49,-1.82,-23.2,1.23,-20.21,-11.37,-27.56,-10.33,-25.46,-15.53,-18.39,-11.44,-20.45,-20.7,-10.27,-18.49,-15.98,-31.71,-4.83,-28.09,-13.94,-24.84,-11.25,-24.74,-16.34,-32.8,-2.07,-26.67,-8.31,-39.52,-7.63,-23.32,-12.76,-36.31,-19.43,-15.15,-26.88,-12.68,-16.86,-21.03,-45.08,-13.66,-32.51,-17.87,-29.46,-4.86,-39.75,-17.11,-31.32,-11.24,-48.52,-10.9,-36.64,-26.98,-33.74,-29.29,-46.91,-21.4,-42.12,-29.09,-42.79,-31.48,-29.72,-50.5,-38.3,-34.48,-23.08,-60.24,-40.74,-49.95,-43.55,-49.64,-28.52,-69.05,-32.9,-58.88,-29.42,-69.52,-31.15,-60.67,-46.72,-41.77,-32.4,-68.37,-52.36,-43.98,-37.9,-42.82,-51.34,-43.25,-76.79,-53.9,-63.43,-28.48,-61.16,-33.58,-74.82,-32.33,-69.35,-23.64,-57.91,-31.09,-69.77,-49.67,-54.45,-22.77,-41.43,-38.41,-33.15,-42.89,-45.42,-36.69,-51.16,-45.43,-26.23,-33.1,-27.33,-39.77,-19.71,-44.03,-28.33,-38.4,-10.74,-47.64,-19.74,-42.99,-23.57,-28.38,-12.48,-35.08,-17.62,-37.87,-24.5,-14.01,-20.49,-23.85,-17.99,-7.11,-18.49,-7.08,-22.41,-7.85,-26.78,1.41,-25.45,-11.2,-27.45,4.77,-34.63,-2.13,-34.3,6.54,-29.6,1.25,-16.28,-12.75,-18.82,-7.32,-19.55,-17.04,-8.67,-14.45</v>
       </c>
     </row>
     <row r="62">
@@ -1078,7 +1078,7 @@
         <v>[L_03_标记]</v>
       </c>
       <c r="C62" t="str">
-        <v>104.7uv</v>
+        <v>a: 18.8ms -40.3uv b: 40.5ms 279.6uv</v>
       </c>
     </row>
     <row r="63">
@@ -1089,7 +1089,7 @@
         <v>[R_04_名字]</v>
       </c>
       <c r="C63" t="str">
-        <v>FERG(4)_lCone</v>
+        <v>FERG(4)_dRod</v>
       </c>
     </row>
     <row r="64">
@@ -1111,7 +1111,7 @@
         <v>[R_04_闪光]</v>
       </c>
       <c r="C65" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:0.30cd.m-2,5ms</v>
       </c>
     </row>
     <row r="66">
@@ -1122,7 +1122,7 @@
         <v>[R_04_闪光背景]</v>
       </c>
       <c r="C66" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="67">
@@ -1133,7 +1133,7 @@
         <v>[R_04_采样]</v>
       </c>
       <c r="C67" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="68">
@@ -1144,7 +1144,7 @@
         <v>[R_04_分析时间]</v>
       </c>
       <c r="C68" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="69">
@@ -1166,7 +1166,7 @@
         <v>[R_04_详细数据(uv)]</v>
       </c>
       <c r="C70" t="str">
-        <v>-1.59,2.7,-2.98,2.36,-1.03,-0.62,2.08,-2.91,2.85,-1.93,0.42,1.22,-2.48,3,-2.6,1.41,0.2,-1.76,2.78,-2.96,2.23,-0.83,-0.82,2.22,-2.95,2.78,-1.77,0.22,1.4,-2.6,3,-2.5,1.22,0.4,-1.93,2.84,-2.93,2.07,-0.66,-1.05,2.31,-3.04,2.62,-1.7,-0.11,1.42,-2.88,2.74,-2.67,0.67,0.16,-2.62,2.24,-3.66,0.97,-1.6,-2.59,0.82,-4.96,0.3,-4.14,-3.37,-1.95,-7.07,-2,-7.95,-5.69,-6.66,-10.7,-6.65,-13.62,-10.38,-13.82,-16.53,-14.2,-21.54,-17.89,-23.57,-24.75,-24.55,-31.46,-27.9,-35.16,-34.65,-36.53,-42.09,-38.91,-46.67,-44.31,-47.79,-51.01,-48.26,-55.22,-50.92,-55.16,-55.24,-52.82,-57.72,-51.56,-55.65,-52.17,-50,-51.89,-44.3,-47.43,-40.56,-38.67,-37.11,-28.82,-30.47,-20.9,-19.4,-14.48,-6.4,-6.28,4.93,5.98,13.79,20.83,22.9,34.61,35.32,45.38,50.86,55,66.21,66.95,78.52,82.32,88.59,98.55,99.86,112.21,114.54,122.87,131.06,133.5,145.83,147.1,157.19,163.31,167.24,178.71,179.41,190.63,194.53,200.04,209.81,210.36,221.85,223.51,230.36,237.64,238.35,249.06,248.61,256.27,260.46,261.5,270.37,268.07,275.82,276.58,277.98,284.09,280.35,287.34,284.69,286.37,289.04,284.37,289.82,284.11,285.88,284.81,279.77,283.02,274.92,276.55,271.82,266.98,267.56,257.98,259.18,251.27,247.11,244.83,234.8,235.29,225,221.84,216.8,207.33,206.82,195.17,193.16,185.7,177.66,175.94,164.03,163.08,153.79,147.8,144.71,133.61,133.46,123.04,119.43,114.92,105.53,105.76,95.03,93.76,87.91,80.9,80.99,70.76,71.5,64.53,60.26,59.71,50.73,52.91,45.17,43.67,42.07,34.95,37.83,29.81,30.8,27.9,23.08,25.89,18.13,21.1,16.86,14.52,16.55,9.63,13.87,8.47,8.58,9.28,3.74,8.45,2.26,4.55,3.57,-0.15,4.23,-2.22,1.76,-0.97,-2.62,0.72,-5.37,-0.34,-4.65,-4.16,-2.4,-7.53,-2.19,-7.66,-5.22,-5.36,-9,-4.09,-10.16,-6.14,-8.24,-10.04,-6.22,-12.23,-7.19,-11.07,-10.88,-8.67,-13.96,-8.57,-13.81,-11.7,-11.45,-15.42,-10.38,-16.42,-12.7,-14.47,-16.71,-12.69,-18.83,-14.01,-17.65,-17.93,-15.46,-21.03,-15.74,-20.85,-19.19,-18.63,-23,-17.93,-23.96,-20.62,-22.09,-24.78,-20.61,-26.87,-22.31,-25.69,-26.44,-23.71,-29.52,-24.34,-29.27,-28.04,-27.16,-31.86,-26.74,-32.69,-29.69,-30.81,-33.88,-29.52,-35.81,-31.46,-34.5,-35.64,-32.6,-38.54,-33.42,-38.07,-37.19,-35.9,-40.82,-35.6,-41.34,-38.61,-39.27,-42.62,-37.98,-44.18,-39.96,-42.55,-43.98,-40.53,-46.48,-41.33,-45.57,-44.95,-43.14,-48.16,-42.75,-48.17,-45.6,-45.7,-49.21,-44.22,-50.2,-46.03,-48.05,-49.66,-45.73,-51.56,-46.32,-50.04,-49.58,-47.19,-52.2,-46.54,-51.52,-49.06,-48.52,-52.11,-46.72,-52.38,-48.22,-49.6,-51.34,-46.88,-52.52,-47.16,-50.31,-49.98,-46.98,-51.92,-46.01,-50.51,-48.15,-46.97,-50.6,-44.83,-50.13,-46,-46.75,-48.61,-43.66,-49.11,-43.68,-46.25,-46.08,-42.52,-47.41,-41.32,-45.37,-43.16,-41.38,-45.09,-39.03,-44.02,-40.01,-40.19,-42.23,-36.88,-42.18,-36.79,-38.86,-38.94,-34.91,-39.82,-33.66,-37.32,-35.38,-33.11,-36.98,-30.75,-35.51,-31.72,-31.43,-33.75,-28.14,-33.36,-28.14,-29.8,-30.23,-25.87,-30.87,-24.78,-28.15,-26.57,-23.93,-28.05,-21.78,-26.38,-22.94,-22.28,-24.96,-19.21,-24.43,-19.48,-20.83,-21.69,-17.1,-22.26,-16.35,-19.48,-18.37,-15.44,-19.86,-13.65,-18.14,-15.14,-14.18,-17.27,-11.46,-16.72,-12.13,-13.2,-14.55,-9.8,-15.14,-9.48,-12.41,-11.8,-8.64,-13.37,-7.29,-11.67,-9.14,-7.91,-11.42,-5.6,-10.88,-6.7,-7.5,-9.33,-4.45,-9.95,-4.58,-7.3,-7.19,-3.81,-8.83,-2.89,-7.15,-5.1,-3.58,-7.49,-1.68,-6.95,-3.17</v>
+        <v>0.57,-2.51,6.83,-4.82,5.02,1.05,-2.12,7.18,-4.54,5.22,1.2,-2.06,7.18,-4.6,5.07,1.01,-2.34,6.84,-5.01,4.59,0.49,-2.94,6.21,-5.69,3.85,-0.28,-3.77,5.36,-6.58,2.92,-1.21,-4.74,4.39,-7.56,1.92,-2.19,-5.75,3.39,-8.55,0.92,-3.16,-6.69,2.48,-9.47,0.02,-4.05,-7.64,1.67,-10.3,-0.94,-4.95,-8.36,0.64,-11.53,-2.12,-6.06,-9.83,-0.45,-12.56,-3.19,-7.54,-11.65,-1.95,-14.8,-6.63,-11.31,-16.11,-6.52,-19.32,-10.83,-15.64,-20.58,-14.26,-25.15,-16.95,-26.51,-30.09,-22.62,-34.3,-25.51,-27.99,-43.16,-26.59,-49.09,-35.52,-45.05,-53.04,-50.17,-49.07,-52.94,-61.07,-65.56,-44.9,-68.55,-50.32,-51.4,-73.99,-50.19,-76.25,-46.22,-69.42,-76.02,-44.76,-53.22,-61.72,-66.59,-54.59,-42.72,-57.66,-44.74,-50.38,-31.26,-23.86,-28.55,-20.7,0.87,-7.49,5.52,5.44,15.83,21.46,34.42,41.01,46.06,71.49,55.18,70.49,94.23,85.65,88.53,101.19,113.81,127.66,116.74,152.65,140.04,173.6,154.61,187.05,184.93,221.44,209.55,216.18,238.91,252.88,252.81,223.16,249.19,253.33,259.68,279.74,316.75,324.67,288.85,290.7,365.67,351.18,370.67,321.92,388.95,384.56,374.83,386.07,330.72,378.14,424.82,391.69,376.81,380.63,393.83,422.18,394.77,364.42,382.1,421.66,417.81,418.16,414.28,412.36,440.85,382.89,383.12,399.66,403.26,368.18,387.17,353.45,322.22,307.24,319.03,341.5,291.82,336.14,286.87,310.75,322.12,273.88,295.6,298.03,239.23,236.6,253.51,257.15,233.93,230.18,196.21,180.67,186.67,204.3,164.95,180.29,174.64,180.03,140.47,158.67,146.28,123.64,118.84,96.12,109.07,94.18,101.42,87.58,80.16,86.89,73.46,62.76,70.42,46.82,63.76,49.26,46.38,52.21,37.32,42.16,34.05,24.17,32.27,23.68,29.78,19.39,18.41,22.56,10.84,16.54,13.39,6.51,17.3,3.69,11.71,9.18,2.84,11.68,-1.27,9.39,4.07,0.23,9.61,-3.6,5.35,1.53,-1.84,7.38,-3.85,3.77,0.03,-3.35,6.58,-6.38,3.19,-1.69,-6.14,3.31,-8.77,1.57,-2.44,-7.03,2.82,-9.3,0.82,-2.63,-7.41,-0.55,-10.29,-1.13,-6.43,-9.24,1.32,-15.6,-3.88,-5.55,-14.58,-3.16,-17.78,-6.29,-11.26,-15.9,-9.19,-19.95,-13.17,-10.58,-20.69,-11.39,-24.43,-16.8,-15.26,-24.08,-14.37,-29.19,-17.99,-17.11,-24.02,-11.11,-32.55,-24.66,-25.45,-25.63,-17.9,-26.05,-27.91,-22.23,-35.29,-25.13,-36.33,-30.31,-26,-33.89,-17.2,-37.23,-20.44,-37.18,-32.45,-21.59,-41.51,-32.93,-33.05,-29.5,-21.47,-48.4,-31.99,-28.21,-47.41,-38.12,-44.85,-41.23,-27.16,-48.38,-39.51,-57.04,-36.6,-29.86,-51.88,-28.26,-36.67,-52.13,-43.31,-51.74,-27.87,-41,-56.08,-48.21,-50.43,-28.51,-62.27,-34.74,-44.25,-57.19,-36.88,-43.82,-47.85,-41.01,-42.99,-62.43,-58.68,-56.85,-69.33,-66.06,-41.48,-80.96,-54.4,-47.79,-59.18,-60.68,-82.68,-53.04,-58.7,-77.39,-39.94,-87.05,-57.31,-80.76,-79.25,-56.2,-77.95,-74.17,-75.9,-76.27,-44.62,-64.81,-56.87,-72.13,-72.17,-71.77,-88.79,-77.67,-60,-64.92,-61.44,-56,-46.52,-59.43,-75,-64.61,-63.44,-55.66,-70.65,-63.63,-58.14,-78.09,-69.13,-73.36,-72.46,-53.88,-84.87,-76.37,-67.37,-77.81,-68.79,-78.53,-41.57,-71.12,-71.7,-51.8,-74.42,-45.87,-50.48,-54.12,-59.24,-53.81,-42.39,-39.32,-48.52,-47.6,-49.56,-42.46,-34.91,-46.97,-45.07,-55.4,-32.03,-36.46,-55.64,-23.17,-58.94,-32.03,-32.74,-53.37,-27.87,-47.4,-27.6,-35.85,-37.08,-35.41,-34.63,-25.86,-42.31,-43.63,-33.76,-44.59,-30.47,-31.95,-36.75,-20.14,-43.12,-24.3,-25.99,-30.12,-17.55,-30.96,-22.64,-20.46,-27.12,-22.96,-30.42,-24.87,-26.46,-25.76,-22.25,-29.92,-20.1,-19.89,-28.77,-10.61,-22.03,-14.09,-16.32,-27.44,-14.92,-22.03,-20.66</v>
       </c>
     </row>
     <row r="71">
@@ -1177,7 +1177,7 @@
         <v>[R_04_标记]</v>
       </c>
       <c r="C71" t="str">
-        <v>a: 21.6ms -66.3uv b: 46.6ms 287.3uv</v>
+        <v>a: 20.5ms -53.5uv b: 44.8ms 283.5uv</v>
       </c>
     </row>
     <row r="72">
@@ -1188,7 +1188,7 @@
         <v>[L_04_名字]</v>
       </c>
       <c r="C72" t="str">
-        <v>FERG(4)_lCone</v>
+        <v>FERG(4)_dRod</v>
       </c>
     </row>
     <row r="73">
@@ -1210,7 +1210,7 @@
         <v>[L_04_闪光]</v>
       </c>
       <c r="C74" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:0.30cd.m-2,5ms</v>
       </c>
     </row>
     <row r="75">
@@ -1221,7 +1221,7 @@
         <v>[L_04_闪光背景]</v>
       </c>
       <c r="C75" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="76">
@@ -1232,7 +1232,7 @@
         <v>[L_04_采样]</v>
       </c>
       <c r="C76" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="77">
@@ -1243,7 +1243,7 @@
         <v>[L_04_分析时间]</v>
       </c>
       <c r="C77" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="78">
@@ -1265,7 +1265,7 @@
         <v>[L_04_详细数据(uv)]</v>
       </c>
       <c r="C79" t="str">
-        <v>-2.4,2.88,-1.05,-1.62,2.99,-1.96,-0.64,2.73,-2.63,0.42,2.13,-2.97,1.43,1.25,-2.93,2.26,0.22,-2.53,2.81,-0.83,-1.81,3,-1.79,-0.86,2.82,-2.52,0.2,2.28,-2.93,1.23,1.45,-2.98,2.1,0.44,-2.65,2.71,-0.63,-2,2.96,-1.64,-1.12,2.83,-2.46,-0.12,2.3,-3.02,0.84,1.42,-3.27,1.6,0.25,-3.26,1.99,-1.15,-3.06,1.87,-2.71,-2.83,1.1,-4.41,-2.8,-0.44,-6.27,-3.23,-2.83,-8.36,-4.38,-6.13,-10.8,-6.53,-10.35,-13.73,-9.86,-15.43,-17.26,-14.45,-21.25,-21.47,-20.24,-27.58,-26.31,-26.97,-34.06,-31.61,-34.19,-40.25,-37.01,-41.27,-45.61,-42.04,-47.47,-49.56,-46.11,-52.02,-51.56,-48.61,-54.2,-51.16,-48.99,-53.43,-48.08,-46.82,-49.4,-42.23,-41.85,-42.04,-33.73,-34.03,-31.54,-22.86,-23.51,-18.34,-10.03,-10.58,-2.99,4.32,4.39,13.91,19.79,20.98,31.78,36.06,38.81,50.15,52.92,57.54,68.66,70.27,76.88,87.11,88.08,96.59,105.38,106.34,116.43,123.43,125.01,136.17,141.24,143.99,155.55,158.79,163.08,174.29,176,181.97,192.1,192.7,200.25,208.65,208.68,217.45,223.63,223.65,233.05,236.76,237.23,246.57,247.76,249.05,257.53,256.42,258.7,265.57,262.58,265.81,270.42,266.12,270.06,271.96,266.99,271.21,270.21,265.19,269.14,265.29,260.77,263.82,257.47,253.84,255.41,247.12,244.56,244.15,234.63,233.13,230.43,220.48,219.8,214.7,205.13,204.88,197.53,189.01,188.69,179.47,172.52,171.61,161.1,156.01,154.02,142.94,139.74,136.32,125.46,123.95,118.92,109.02,108.78,102.17,93.9,94.37,86.43,80.24,80.79,71.96,68.09,68.13,58.99,57.41,56.43,47.65,48.09,45.75,37.99,39.96,36.14,29.97,32.84,27.65,23.49,26.55,20.31,18.36,20.93,14.14,14.37,15.86,9.12,11.27,11.26,5.2,8.79,7.1,2.3,6.7,3.37,0.28,4.8,0.11,-1.02,2.93,-2.65,-1.78,0.98,-4.88,-2.22,-1.07,-6.57,-2.53,-3.22,-7.73,-2.89,-5.4,-8.43,-3.46,-7.53,-8.75,-4.33,-9.5,-8.81,-5.55,-11.23,-8.77,-7.13,-12.65,-8.77,-9,-13.72,-8.96,-11.08,-14.45,-9.46,-13.25,-14.89,-10.34,-15.37,-15.13,-11.64,-17.33,-15.29,-13.35,-19.04,-15.5,-15.4,-20.43,-15.89,-17.71,-21.48,-16.57,-20.13,-22.24,-17.63,-22.53,-22.77,-19.1,-24.79,-23.18,-20.96,-26.78,-23.6,-23.17,-28.45,-24.14,-25.62,-29.75,-24.92,-28.18,-30.71,-26.02,-30.71,-31.39,-27.49,-33.09,-31.87,-29.32,-35.17,-32.28,-31.46,-36.89,-32.75,-33.81,-38.2,-33.39,-36.26,-39.11,-34.28,-38.65,-39.66,-35.47,-40.85,-39.94,-36.98,-42.73,-40.07,-38.75,-44.21,-40.17,-40.7,-45.23,-40.36,-42.72,-45.78,-40.74,-44.67,-45.91,-41.36,-46.4,-45.7,-42.25,-47.79,-45.27,-43.38,-48.75,-44.75,-44.67,-49.22,-44.25,-46.01,-49.18,-43.89,-47.28,-48.68,-43.74,-48.34,-47.81,-43.83,-49.07,-46.66,-44.16,-49.37,-45.38,-44.66,-49.18,-44.11,-45.24,-48.48,-42.95,-45.77,-47.32,-41.99,-46.14,-45.76,-41.3,-46.21,-43.94,-40.86,-45.89,-41.97,-40.63,-45.12,-40.01,-40.54,-43.88,-38.18,-40.47,-42.2,-36.58,-40.3,-40.15,-35.27,-39.91,-37.85,-34.28,-39.19,-35.43,-33.56,-38.08,-33.04,-33.05,-36.55,-30.8,-32.63,-34.63,-28.84,-32.2,-32.37,-27.21,-31.63,-29.9,-25.95,-30.81,-27.33,-25.04,-29.66,-24.81,-24.4,-28.15,-22.48,-23.94,-26.28,-20.45,-23.53,-24.12,-18.79,-23.06,-21.75,-17.54,-22.4,-19.31,-16.69,-21.47,-16.93,-16.17,-20.21,-14.74,-15.88,-18.63,-12.86,-15.71,-16.77,-11.37,-15.52,-14.71,-10.31,-15.19,-12.56,-9.67,-14.63,-10.46,-9.4,-13.76,-8.54,-9.4,-12.58,-6.92,-9.55,-11.1,-5.68,-9.72,-9.41,-4.87,-9.77,-7.61,-4.49,-9.6,-5.83,-4.49,-9.14,-4.2,-4.78,-8.35,-2.84,-5.23,-7.26,-1.84,-5.73,-5.92,-1.25,-6.12</v>
+        <v>-2.85,-8.52,4.78,-12.21,5.07,-7.71,-1.93,1.19,-9.63,6.68,-10.87,3.94,-4.4,-4.44,3.99,-10.86,6.7,-9.56,1.2,-1.84,-7.69,5.13,-12.17,4.79,-8.47,-2.89,-0.3,-11.34,4.53,-13.38,1.2,-7.64,-7.8,0.16,-14.89,2.4,-14.2,-3.53,-6.97,-12.86,-0.36,-17.76,-0.92,-14.4,-8.78,-6.42,-17.38,-1.64,-19.71,-4.92,-13.99,-14.01,-6.3,-21.17,-3.69,-20.44,-9.73,-13.12,-18.91,-7.07,-24.59,-8.1,-21.97,-16.03,-13.96,-24.43,-9.67,-28.27,-13.23,-24.45,-22.3,-15.52,-33.63,-13.48,-34.79,-23.51,-31.4,-33.43,-23.12,-40.07,-27.71,-45.38,-34.09,-40.74,-47.67,-38.2,-47.76,-34.3,-46.31,-49.96,-41.98,-56.9,-51.94,-55.55,-51.56,-66.11,-59.52,-54.28,-79.72,-59.87,-64.08,-54.16,-56.6,-72.66,-50.37,-54.74,-35.33,-47.78,-45.04,-51.22,-55,-29.16,-47.42,-35.9,-20.03,-21.12,-17.9,-8.2,-9.49,-7.75,-1.67,18.87,16.06,42.72,28.18,54.09,55.82,45.1,70.96,45.68,83.18,81.91,103.92,115.74,91.91,122.07,131.05,128.43,139.93,139.62,163.61,155.79,188.09,203.61,191.23,194.07,230.07,242.1,203.52,258.03,242.46,228.28,290.35,277.14,289.46,251.57,270.27,262.1,279.46,304.43,321.37,343.85,318.42,359.94,379.41,371.49,384.63,318.33,393.46,329.86,378.43,362.33,334.1,425.51,350.25,421.43,345.49,363.06,402.33,411.83,429.77,379.96,359.05,343.02,362.28,401.68,344.08,381.05,377.2,362.87,367.39,346.61,351.06,296.67,315.43,320.81,337.94,269.38,255.15,297.87,286.27,253.91,260.41,242.19,273.02,245.51,232.39,197.85,199.65,222.63,189.74,218.75,156.42,172.44,162.2,147.37,152.74,132.03,160.27,110.93,122.09,125.08,118.95,97.68,79.72,95.25,83.6,87.76,71.93,57.91,62.05,43.33,59.06,49.32,47.91,49.62,32.78,45.33,22.57,31.52,19.88,23.51,27.31,10.31,23.4,5.5,11.54,7.57,1.8,11.09,-9.08,9.32,-5.82,1.64,0.68,-9.31,2.4,-14.22,-0.06,-10.89,-8.38,-2.13,-17.05,0.26,-16.9,-5.72,-10.97,-14.46,-4.39,-20.87,-4.64,-19.09,-11.69,-10.28,-19.41,-5,-23.66,-8.41,-17.79,-15.08,-9.82,-23.81,-6.35,-25.21,-12.85,-18.91,-21.72,-11.37,-27.94,-9.47,-25.6,-18.43,-17.27,-29.38,-12.95,-30.59,-17.52,-26.11,-27.32,-18.45,-35.17,-16.16,-35.37,-22.06,-27.12,-34.4,-26.11,-38.51,-23.76,-42.8,-31.67,-32.56,-45.16,-30.51,-45.38,-28.22,-45.83,-42.52,-29.52,-46.26,-27.57,-53.02,-32.89,-45.38,-40.91,-39.88,-48.4,-39.37,-50.36,-39.81,-45.05,-59.31,-37.07,-52.53,-39.67,-56.3,-52.17,-51.37,-58.17,-47.57,-51.47,-53.84,-49,-48,-48.25,-63.73,-35.78,-64.34,-54.29,-52.64,-53.62,-58.07,-74.93,-59.25,-50.87,-46.97,-41.56,-63.78,-43.74,-67.33,-50.1,-59.78,-69.11,-68.08,-66.52,-53,-65,-66.01,-65.9,-71.83,-57.61,-65.84,-68.57,-58.36,-81.65,-50.17,-78.63,-46.58,-85.13,-82.56,-89.06,-71.13,-74.55,-81.82,-82.28,-93.37,-63.91,-64.42,-84.56,-63.48,-77.16,-71.15,-77.81,-86.5,-92.7,-81.19,-58.12,-78.43,-70.65,-69.88,-90.46,-80.1,-91.66,-75.93,-94.44,-83.34,-71.95,-93.4,-88.36,-101.47,-84.9,-107.53,-101.1,-67.31,-112.47,-60.98,-98.96,-94.88,-86.15,-85.1,-72.19,-88.18,-84.93,-102.44,-65.63,-67.7,-84.76,-89.92,-106.58,-81.53,-99.74,-65.8,-87.98,-95.43,-80.76,-100.32,-63.81,-83.82,-65.12,-55.33,-76.92,-57.91,-80.22,-75.18,-80.34,-60.25,-46.63,-68.42,-47.6,-59.73,-61.6,-70.56,-66.01,-55.64,-82.02,-59.36,-66.21,-54.4,-54.5,-66.88,-50.81,-71.16,-46.92,-44.07,-71.47,-50.04,-65.23,-45.34,-50.13,-61.27,-39.41,-62.73,-50.67,-60.64,-44.08,-43.73,-46.47,-40.85,-63.62,-44.4,-51.05,-50.27,-42.89,-47.47,-41.86,-51.84,-41.29,-46.4,-42.79,-38.17,-53.93,-36.3,-56,-35.06,-50.19,-46.16,-33.1,-55.46,-33.74,-48.09</v>
       </c>
     </row>
     <row r="80">
@@ -1276,7 +1276,7 @@
         <v>[L_04_标记]</v>
       </c>
       <c r="C80" t="str">
-        <v>a: 21.6ms -62.3uv b: 46.6ms 270.1uv</v>
+        <v>a: 20.6ms -58.2uv b: 44.9ms 369.2uv</v>
       </c>
     </row>
     <row r="81">
@@ -1287,7 +1287,7 @@
         <v>[R_05_名字]</v>
       </c>
       <c r="C81" t="str">
-        <v>FERG(5)_Flicker</v>
+        <v>FERG(5)_dRod</v>
       </c>
     </row>
     <row r="82">
@@ -1298,7 +1298,7 @@
         <v>[R_05_放大器]</v>
       </c>
       <c r="C82" t="str">
-        <v>1-300 Hz</v>
+        <v>1-75 Hz</v>
       </c>
     </row>
     <row r="83">
@@ -1309,7 +1309,7 @@
         <v>[R_05_闪光]</v>
       </c>
       <c r="C83" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:1.0cd.m-2,5ms</v>
       </c>
     </row>
     <row r="84">
@@ -1320,7 +1320,7 @@
         <v>[R_05_闪光背景]</v>
       </c>
       <c r="C84" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="85">
@@ -1331,7 +1331,7 @@
         <v>[R_05_采样]</v>
       </c>
       <c r="C85" t="str">
-        <v>刺激间隔: 50.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="86">
@@ -1342,7 +1342,7 @@
         <v>[R_05_分析时间]</v>
       </c>
       <c r="C86" t="str">
-        <v>500 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="87">
@@ -1364,7 +1364,7 @@
         <v>[R_05_详细数据(uv)]</v>
       </c>
       <c r="C88" t="str">
-        <v>63.87,70.97,68.67,69.52,75.34,71.34,73.35,77.15,71.92,74.81,76.05,70.17,73.46,71.86,65.91,69.03,64.59,59.13,61.44,54.49,49.92,50.86,41.96,38.53,37.65,27.57,25.37,22.4,12.03,10.94,5.86,-3.91,-4.17,-11.13,-19.48,-19.28,-27.67,-33.95,-33.73,-42.88,-46.71,-46.87,-56,-57.24,-58.1,-66.4,-65.21,-66.97,-73.66,-70.46,-73.13,-77.6,-72.98,-76.41,-78.26,-72.94,-76.81,-75.91,-70.64,-74.52,-70.99,-66.45,-69.84,-64.12,-60.82,-63.24,-55.95,-54.21,-55.24,-47.17,-47.07,-46.41,-38.41,-39.77,-37.32,-30.19,-32.63,-28.47,-22.87,-25.85,-20.27,-16.66,-19.55,-12.98,-11.55,-13.73,-6.74,-7.41,-8.33,-1.53,-3.93,-3.2,2.83,-0.74,1.82,6.61,2.6,6.94,10.14,6.47,12.32,13.81,11.2,18.09,17.94,16.99,24.31,22.81,23.89,30.98,28.56,31.78,37.99,35.18,40.36,45.13,42.5,49.2,52.12,50.2,57.75,58.62,57.8,65.39,64.24,64.72,71.5,68.54,70.34,75.51,71.15,74.04,76.93,71.69,75.27,75.45,69.89,73.6,70.92,65.59,68.79,63.38,58.75,60.79,53.09,49.45,49.8,40.47,37.97,36.24,26.1,24.68,20.72,10.66,10.11,4.01,-5.11,-5.13,-13.01,-20.47,-20.37,-29.45,-34.7,-34.9,-44.44,-47.22,-48.06,-57.22,-57.53,-59.26,-67.22,-65.33,-68.01,-74.04,-70.44,-73.98,-77.54,-72.89,-77.01,-77.81,-72.81,-77.12,-75.14,-70.5,-74.49,-70.01,-66.32,-69.48,-63.04,-60.71,-62.57,-54.88,-54.1,-54.32,-46.22,-46.93,-45.31,-37.64,-39.58,-36.13,-29.65,-32.35,-27.28,-22.57,-25.46,-19.17,-16.57,-19.04,-12.05,-11.63,-13.09,-6.02,-7.57,-7.58,-1.04,-4.09,-2.36,3.09,-0.8,2.71,6.67,2.71,7.84,10.08,6.8,13.18,13.68,11.78,18.87,17.84,17.82,24.98,22.81,24.92,31.51,28.72,32.94,38.38,35.54,41.57,45.38,43.07,50.35,52.25,50.95,58.74,58.66,58.67,66.13,64.2,65.63,71.92,68.45,71.19,75.56,71.02,74.72,76.61,71.54,75.68,74.77,69.7,73.66,69.93,65.35,68.44,62.16,58.42,60.01,51.72,49.02,48.63,39.05,37.4,34.72,24.71,23.95,18.96,9.38,9.21,2.13,-6.22,-6.19,-14.89,-21.37,-21.55,-31.18,-35.39,-36.16,-45.91,-47.69,-49.33,-58.34,-57.83,-60.47,-67.91,-65.48,-69.07,-74.29,-70.49,-74.82,-77.37,-72.87,-77.56,-77.28,-72.77,-77.33,-74.33,-70.44,-74.36,-69.03,-66.26,-69.01,-62,-60.63,-61.8,-53.89,-53.99,-53.31,-45.35,-46.77,-44.15,-36.98,-39.33,-34.91,-29.22,-31.99,-26.1,-22.37,-24.98,-18.12,-16.55,-18.42,-11.19,-11.74,-12.36,-5.4,-7.72,-6.75,-0.66,-4.19,-1.48,3.24,-0.78,3.61,6.65,2.92,8.7,9.95,7.24,13.97,13.54,12.47,19.56,17.76,18.72,25.55,22.87,26,31.95,28.97,34.11,38.68,36.01,42.75,45.56,43.75,51.43,52.35,51.8,59.63,58.69,59.62,66.76,64.19,66.58,72.22,68.42,72.04,75.5,70.97,75.36,76.19,71.47,76.01,74.03,69.6,73.61,68.92,65.18,67.96,60.95,58.14,59.12,50.4,48.6,47.34,37.7,36.8,33.12,23.42,23.17,17.14,8.2,8.23,0.23,-7.23,-7.34,-16.73,-22.19,-22.83,-32.85,-36.02,-37.51,-47.28,-48.15,-50.67,-59.33,-58.14,-61.71,-68.48,-65.68,-70.14,-74.43,-70.61,-75.62,-77.11,-72.94,-78.04,-76.68,-72.81,-77.45,-73.49,-70.46,-74.11,-68.06,-66.25,-68.42,-61.01,-60.58,-60.91,-52.97,-53.87,-52.21,-44.6,-46.56,-42.94,-36.42,-39.01,-33.68,-28.88,-31.54,-24.95,-22.23,-24.4,-17.13,-16.58,-17.72,-10.42,-11.85,-11.56,-4.88,-7.84,-5.88,-0.4,-4.23,-0.58,3.3,-0.67,4.49,6.55,3.23,9.52,9.78,7.79,14.7,13.39,13.24,20.16,17.71,19.7,26.02,22.99,27.11,32.29,29.31,35.29,38.9,36.58,43.88,45.7,44.53,52.44,52.42,52.73,60.43,58.73,60.63,67.27,64.22</v>
+        <v>7.5,-6.42,2.36,6.5,-7.08,3.12,5.24,-7.71,3.7,3.77,-8.29,4.1,2.11,-8.77,4.33,0.34,-9.14,4.4,-1.49,-9.37,4.34,-3.34,-9.43,4.16,-5.13,-9.31,3.89,-6.81,-8.98,3.54,-8.34,-8.45,3.15,-9.65,-7.7,2.72,-10.73,-6.74,2.29,-11.52,-5.59,1.86,-12.03,-4.29,1.44,-12.24,-2.84,1.01,-12.14,-1.29,0.6,-11.79,0.31,0.2,-11.14,1.88,-0.22,-10.37,3.28,-0.77,-9.49,4.52,-1.4,-8.3,5.69,-2.23,-7.75,6.29,-3.36,-6.4,6.73,-4.67,-6.17,6.08,-7.22,-6.73,4.14,-9.64,-6.98,3.18,-12.04,-7.22,-2.52,-14.71,-11.11,-6.36,-18.03,-14.87,-7.47,-22.53,-15.35,-16.9,-29.86,-20.16,-26.61,-39.72,-31.47,-30.37,-50.95,-33.1,-32.04,-48.89,-39.31,-37.6,-54.89,-39.72,-57.31,-58.79,-44.96,-53.33,-62.53,-50.81,-58.64,-71.72,-52.68,-57.1,-66.94,-46.37,-48.06,-54.9,-48.47,-49.65,-56.78,-34.95,-34.62,-23.43,-29.52,-32.09,-27.2,-1.89,-18.45,4.57,14.43,15.68,24.77,40.29,34.63,44.28,65.57,58.8,80.71,91.18,74.53,117.46,97.43,105.7,112.88,119.17,120.3,171.87,145.43,177.45,189.52,170.26,170.28,221.81,229.74,218.11,229.82,245.03,250.24,240.04,277.78,302.98,280.93,304.25,332.7,309.77,322.22,312,376.07,353.34,307.63,321.51,337.29,354.36,409.65,402.48,343.57,373.74,355.53,348.28,420.97,420.61,430.09,359.59,411.22,399.83,408.41,412.7,375.22,420.34,358.15,413.14,391.21,404.87,382.68,399.31,331.56,374.8,371.61,306,329.14,328.83,361.05,370.63,293.26,347.31,314.18,314.16,265.46,308.34,295.81,289.78,291.97,275.96,244.37,245.74,214.11,206.97,210.65,192.23,217.23,184.75,192.5,173.71,163.91,164.28,160.73,157.47,130.59,131.09,138.97,124.1,120.12,126.65,113.47,119,103.46,83.39,93.84,88.64,71.02,92.37,64.53,66.24,74.99,55.97,53.17,62.62,44.15,41.19,56.08,40.01,39.68,47.32,32.23,35.62,36.4,23.26,28.95,31.13,18.44,23.63,27.46,13.5,20.92,22.5,6.28,17.52,18.23,4.16,17.1,11.99,1.82,14.36,8.94,-1.45,11.74,5.39,-1.07,10.37,1.48,-2.52,10.21,-1.54,-4.66,8.12,-4.6,-6.35,6.6,-8.29,-7.35,3.81,-9.08,-6.13,1.44,-10.12,-6.84,-0.43,-13.42,-8.56,1.56,-13.45,-8.77,-4.08,-14.32,-8.62,-1.38,-15.44,-4.34,-6.58,-20.41,-6.05,-6.46,-20.93,-2.74,-6.01,-17.31,-8.91,-8.26,-20.12,-1.05,-16.37,-14.87,-3.02,-17.07,-15.33,-1.45,-19.8,-15.96,-7.89,-21.12,-19.84,-11.44,-20.53,-12.51,-3.33,-22.13,-16.55,-4.66,-20.63,-14.25,-9.18,-23.96,-17.6,-19.34,-31.06,-23.32,-7.61,-28.31,-21.4,-26.39,-41.1,-16.35,-23.92,-36.17,-14.56,-20.14,-32.18,-25.48,-32.5,-28.13,-20.17,-22,-37.02,-32.99,-30.93,-35.15,-36.55,-51.54,-41.6,-24.94,-47.44,-51.51,-41.56,-40.27,-52.02,-32.79,-56.42,-64.07,-49.72,-57.74,-47.74,-29.97,-66.72,-66.62,-60.91,-69.6,-40.14,-60.96,-56.14,-41.22,-55.32,-68.83,-48.92,-48.59,-71.26,-67.84,-64.51,-49.6,-56.51,-42.63,-57.25,-68.54,-65.36,-81.3,-64.07,-72.36,-76.11,-67.98,-50.37,-74.74,-50.2,-56.39,-58.97,-60.35,-45.37,-51.54,-47.86,-67.58,-51.78,-41.88,-75.02,-71.72,-64.33,-47.55,-46.82,-45.7,-68.19,-62.92,-52.15,-68.92,-64.68,-46,-60.29,-58.49,-39.68,-39.75,-30.97,-36,-52.16,-57.72,-52.73,-59.18,-25.14,-56.72,-44.22,-41.12,-41.22,-52.91,-38.09,-58.78,-47.32,-21.19,-44.27,-34.96,-32.92,-48.5,-44.18,-19.53,-31.77,-52.5,-36.52,-34.28,-42.37,-36.22,-43.78,-38.84,-26.9,-50.85,-46.43,-28.01,-47.78,-37.5,-23.29,-32.1,-40.8,-24.29,-31.41,-30.4,-21.08,-30.8,-24.86,-17.51,-38.18,-15.41,-19.01,-27.17,-11.3,-18.18,-27.78,-8.5,-26.07,-23.39,-11.34,-22.42,-23.02,-6.98,-17.34</v>
       </c>
     </row>
     <row r="89">
@@ -1375,7 +1375,7 @@
         <v>[R_05_标记]</v>
       </c>
       <c r="C89" t="str">
-        <v>幅值: 64.1uv 相位: 36.5°</v>
+        <v>a: 21.4ms -48.7uv b: 48.5ms 360.7uv</v>
       </c>
     </row>
     <row r="90">
@@ -1386,7 +1386,7 @@
         <v>[L_05_名字]</v>
       </c>
       <c r="C90" t="str">
-        <v>FERG(5)_Flicker</v>
+        <v>FERG(5)_dRod</v>
       </c>
     </row>
     <row r="91">
@@ -1397,7 +1397,7 @@
         <v>[L_05_放大器]</v>
       </c>
       <c r="C91" t="str">
-        <v>1-300 Hz</v>
+        <v>1-75 Hz</v>
       </c>
     </row>
     <row r="92">
@@ -1408,7 +1408,7 @@
         <v>[L_05_闪光]</v>
       </c>
       <c r="C92" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:1.0cd.m-2,5ms</v>
       </c>
     </row>
     <row r="93">
@@ -1419,7 +1419,7 @@
         <v>[L_05_闪光背景]</v>
       </c>
       <c r="C93" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="94">
@@ -1430,7 +1430,7 @@
         <v>[L_05_采样]</v>
       </c>
       <c r="C94" t="str">
-        <v>刺激间隔: 50.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="95">
@@ -1441,7 +1441,7 @@
         <v>[L_05_分析时间]</v>
       </c>
       <c r="C95" t="str">
-        <v>500 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="96">
@@ -1463,7 +1463,7 @@
         <v>[L_05_详细数据(uv)]</v>
       </c>
       <c r="C97" t="str">
-        <v>57.8,63.34,64.75,60.77,63.34,67.27,63.36,61.73,66.08,64.3,59.16,61.27,62.14,55.71,53.74,55.95,50.74,44.64,45.75,43.22,34.79,32.59,32.36,24.33,18.04,18.19,12.77,3.59,1.76,-0.46,-9.94,-15.18,-15.44,-22.54,-30.8,-31.37,-34.64,-43.8,-46.69,-46.6,-53.87,-59.58,-58.15,-61.45,-68.64,-68.27,-67.31,-73.44,-75.53,-71.89,-74.54,-78.71,-74.95,-73.12,-77.38,-75.66,-70.31,-72.18,-73.1,-66.67,-64.53,-66.88,-62.01,-56.08,-57.53,-55.71,-47.96,-46.42,-47.27,-40.49,-35.33,-36.89,-33.21,-25.69,-25.56,-25.44,-18.07,-14.8,-16.79,-12.11,-6.03,-7.65,-6.83,0.09,0.98,-1.28,3.89,7.93,4.87,6.52,12.49,11.22,9.33,14.86,16.88,13.26,16.11,21.06,18.4,17.73,23.63,24.07,20.95,25.31,29.31,26.16,27.36,33.52,32.82,30.99,36.79,39.74,36.73,39.89,45.78,44.11,43.81,50.35,51.81,49.11,53.63,58.29,55.47,56.31,62.39,61.68,59.03,63.81,66.09,61.8,63.02,67.29,63.81,60.83,64.67,63.67,57.76,58.63,60.05,53.67,50.22,52.28,47.75,40.58,40.77,39.02,30.35,26.8,26.89,19.45,12,11.73,7.31,-2.29,-5.12,-6.53,-15.51,-21.81,-21.89,-27.82,-36.61,-37.7,-39.73,-48.53,-52.27,-51.42,-57.52,-63.83,-62.41,-64.22,-71.28,-71.51,-69.37,-74.51,-77.29,-73.22,-74.38,-78.75,-75.35,-72.13,-75.81,-74.85,-68.78,-69.42,-70.93,-64.66,-61.16,-63.44,-59.41,-52.59,-53.24,-52.36,-44.6,-41.89,-43.22,-37.24,-31.13,-32.41,-29.91,-22.15,-21.14,-21.94,-15.21,-10.97,-13.16,-9.68,-3.1,-4.16,-4.51,2.1,3.96,1.13,5.28,10.1,7.33,7.75,13.83,13.5,10.79,15.66,18.72,15.11,16.85,22.37,20.52,18.89,24.58,26.19,22.78,26.27,31.2,28.6,28.76,35.12,35.53,33.1,38.27,42.33,39.49,41.56,47.95,47.14,45.89,52.05,54.58,51.56,55,60.33,57.94,57.54,63.46,63.63,60.15,63.94,66.97,62.61,62.41,66.76,63.87,59.67,62.74,62.5,56.07,55.56,57.34,51.26,46.4,48.06,44.31,36.31,35.39,34.33,25.71,20.8,21,14.35,5.94,5.04,1.64,-8.09,-12,-12.74,-20.95,-28.21,-28.32,-32.99,-42.04,-43.8,-44.67,-52.81,-57.39,-56.01,-60.76,-67.48,-66.29,-66.63,-73.27,-74.2,-71.08,-75.03,-78.39,-74.17,-73.8,-78.13,-75.29,-70.85,-73.7,-73.53,-67.02,-66.32,-68.25,-62.42,-57.65,-59.63,-56.53,-49.08,-48.78,-48.76,-41.28,-37.4,-38.99,-34.01,-27.13,-27.91,-26.57,-18.87,-16.89,-18.41,-12.56,-7.44,-9.57,-7.36,-0.53,-0.83,-2.22,3.82,6.66,3.52,6.53,11.97,9.73,8.99,14.94,15.64,12.36,16.38,20.39,17.07,17.69,23.54,22.68,20.26,25.49,28.27,24.84,27.35,33,31.19,30.39,36.67,38.27,35.44,39.8,44.82,42.38,43.35,49.97,50.14,48.09,53.6,57.15,54.03,56.26,62.04,60.26,58.67,64.16,65.22,61.13,63.72,67.34,63.14,61.51,65.68,63.49,58.24,60.3,60.77,54.08,52.1,54.04,48.45,42.31,43.33,40.4,31.83,29.67,29.17,20.88,14.68,14.76,9.05,-0.1,-1.81,-4.23,-13.77,-18.78,-19.05,-26.27,-34.3,-34.67,-38.03,-47.04,-49.58,-49.44,-56.66,-61.98,-60.31,-63.61,-70.49,-69.72,-68.69,-74.65,-76.29,-72.44,-75.03,-78.82,-74.71,-72.84,-76.89,-74.75,-69.3,-71.12,-71.69,-65.03,-62.95,-65.11,-59.93,-54.04,-55.5,-53.4,-45.61,-44.22,-44.92,-37.99,-33.03,-34.63,-30.77,-23.36,-23.45,-23.21,-15.84,-12.86,-14.89,-10.1,-4.24,-6.07,-5.13,1.7,2.3,0.06,5.3,9.07,5.9,7.69,13.54,12.05,10.28,15.86,17.65,14.04,17.07,21.9,19.12,18.66,24.61,24.86,21.87,26.43,30.3,27.13,28.58,34.74,33.89,32.26,38.2,40.98,38.01,41.39,47.18,45.37,45.26,51.82,53.04,50.38,55.02,59.44,56.47,57.43,63.37</v>
+        <v>-7.84,-0.82,-13.29,-4.14,-3.57,-13.55,-1.33,-7.39,-11.99,-0.25,-11.21,-9.12,-1.29,-13.98,-5.84,-4.22,-15.01,-3.22,-8.32,-14.12,-2.13,-12.52,-11.69,-3.03,-15.75,-8.59,-5.81,-17.22,-5.84,-9.8,-16.64,-4.39,-13.99,-14.32,-4.8,-17.29,-11.04,-7.03,-18.83,-7.85,-10.54,-18.26,-5.76,-14.4,-15.79,-5.41,-17.48,-12.24,-6.95,-19.02,-8.5,-10.03,-18.38,-6,-13.44,-16.07,-4.87,-16.57,-12.81,-6.29,-18.77,-8.97,-9.65,-18.75,-6.08,-12.84,-17.98,-4.9,-17.75,-14.03,-8.65,-19.85,-11.5,-10.57,-24.21,-12.35,-18.72,-22.07,-13.74,-24.6,-22.18,-15.98,-28.94,-24.82,-24.67,-33.96,-19.19,-24.13,-32.71,-23.47,-33.71,-33.26,-33.71,-47.49,-35.29,-29.09,-49.36,-33.89,-39.27,-57.41,-34.65,-49.41,-56.94,-35.49,-61.43,-60.52,-42.41,-55.01,-48.78,-57.71,-47.92,-29.66,-47.23,-55.98,-29.77,-33.41,-37.22,-29.77,-27.31,-31.29,-26.71,-21.39,-7.69,0.67,-13.32,10.34,-7.05,23.12,16.07,33.25,46.89,42.45,37.54,49.83,77.74,53,80.22,93.79,90.11,94.37,111.98,125.79,151.75,131.91,151.97,164.29,175.14,172.54,151.35,181.36,184.08,188.66,192.32,242.97,231.44,237.87,236.24,257.55,262.3,255.52,248.49,262.56,318.51,280.27,290.63,317.49,324.31,335.01,323.94,326.66,347.4,379.18,323.51,384.9,316.52,406.12,342.04,372.13,331.15,393.54,402.69,397.03,377.88,346.91,399.94,416.88,426.73,358.71,335.47,360.47,355.1,410.51,389.64,381.95,338.67,326.61,354.14,367.31,380.59,354.12,372.72,360.64,297.87,312.9,297.76,339.9,327.17,293.75,324.02,318.26,259.11,250.3,259.7,267.53,275.86,223.36,242.24,236.59,253.49,219.37,230.11,201.49,198.3,186.76,185.69,182.79,191.5,164.75,176.49,151.29,172.89,157.41,159.02,143.92,133.08,143.33,123.88,98.61,112.08,111,108.3,107.7,84.52,94.6,84.46,64.66,76.13,80.79,65.37,68.68,63.03,46.36,65.26,45.78,49.09,50.89,33.51,45.27,40.6,26.78,36.86,32.54,24.95,31.25,22.54,22.95,26.55,9.27,20.27,16.59,5.72,17.74,10.25,4.69,15.45,3.24,5.25,10.5,-1.88,5.41,5.88,-7.27,4.48,-1.49,-7.32,4.49,-5.89,-5.4,2.5,-10.7,-5.98,-2.88,-13.76,-3.01,-8.08,-15.03,-5.23,-12.38,-16.51,-3.69,-17.43,-14.17,-9.45,-20.08,-11.32,-12.44,-21.2,-12.43,-18.5,-19.31,-13.04,-22.94,-20.56,-15.78,-29.2,-16.36,-20.11,-24.45,-17.94,-22.87,-22.05,-11.55,-29.35,-25.95,-12.09,-29.36,-16.4,-20.19,-29.15,-20.15,-27.9,-27.54,-16.56,-33.53,-26.96,-19.16,-30.85,-24.04,-22.45,-34.51,-19.23,-31.61,-28.55,-24.34,-35.89,-27.47,-30.21,-33.82,-21.87,-22.29,-42.63,-27.16,-29.2,-38.76,-33.31,-37.39,-31.1,-37.83,-52.94,-41.84,-34.62,-57.47,-31.07,-46.43,-42.5,-34.97,-49.1,-59.85,-44.36,-40.4,-46.37,-37.22,-53.6,-46.9,-34.58,-55.76,-32.92,-47.98,-59.76,-57.77,-50.04,-60.1,-43.99,-63.36,-56.11,-43.72,-76,-39.58,-67.88,-76.59,-41.12,-72.94,-51.45,-51.18,-73.17,-56.88,-54.6,-57.21,-54.98,-73.51,-67.81,-46.38,-53.51,-68.86,-71.23,-79.18,-65.17,-54.98,-71.36,-61.39,-79.51,-54.26,-76.85,-59.68,-69.54,-59.93,-82.07,-47.36,-75.19,-85.17,-41.12,-76.51,-72.32,-72.79,-63.4,-58.88,-41.66,-64.47,-60.43,-47.74,-50.43,-61.77,-64.6,-59.54,-63.4,-42.74,-67.93,-34.5,-74.28,-38.98,-49.43,-65.56,-40.3,-44.7,-55.02,-35.86,-58.25,-39.84,-57.04,-48.52,-64.13,-29.29,-64.95,-46.22,-36.26,-61.4,-49.13,-55.53,-41.02,-35.19,-55.25,-57.38,-43.31,-51.12,-33.85,-39.01,-44.13,-28.5,-43.3,-52.17,-37.6,-45.78,-40.22,-32.84,-46.57,-42.01,-39.01,-53.26,-25.68,-42.73,-40.61,-21.87,-38.36,-41.36,-29.77,-44.99,-34.44,-32.55,-40.22,-30.16,-30.7,-40.36,-25.59,-27.19,-29.66,-19.38,-26.33,-23.15,-23.11,-23.77</v>
       </c>
     </row>
     <row r="98">
@@ -1474,12 +1474,3774 @@
         <v>[L_05_标记]</v>
       </c>
       <c r="C98" t="str">
-        <v>幅值: 60.2uv 相位: 36.5°</v>
+        <v>a: 21.5ms -44.8uv b: 48.6ms 367.5uv</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B99" t="str">
+        <v>[R_06_名字]</v>
+      </c>
+      <c r="C99" t="str">
+        <v>FERG(6)_dRod</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B100" t="str">
+        <v>[R_06_放大器]</v>
+      </c>
+      <c r="C100" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B101" t="str">
+        <v>[R_06_闪光]</v>
+      </c>
+      <c r="C101" t="str">
+        <v>b白色光:3.0cd.m-2,4ms</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B102" t="str">
+        <v>[R_06_闪光背景]</v>
+      </c>
+      <c r="C102" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B103" t="str">
+        <v>[R_06_采样]</v>
+      </c>
+      <c r="C103" t="str">
+        <v>刺激间隔:2.0S</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B104" t="str">
+        <v>[R_06_分析时间]</v>
+      </c>
+      <c r="C104" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B105" t="str">
+        <v>[R_06_数据长度]</v>
+      </c>
+      <c r="C105" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B106" t="str">
+        <v>[R_06_详细数据(uv)]</v>
+      </c>
+      <c r="C106" t="str">
+        <v>-5.11,-2.18,7.97,0.38,-7.31,2.77,5.83,-6.07,-4.93,5.95,-0.11,-9.09,0.06,4.87,-6.69,-7.3,4.08,-0.26,-10.26,-2.23,4.26,-6.63,-8.96,2.69,0.21,-10.53,-3.79,4.23,-5.7,-9.67,1.96,1.41,-9.82,-4.54,4.82,-3.93,-9.47,1.85,3.21,-8.27,-4.61,5.82,-1.58,-8.6,2.08,5.21,-6.24,-4.39,6.76,0.75,-7.66,1.8,6.63,-4.64,-4.76,6.28,2.17,-8.3,0.54,5.82,-5.58,-7.79,3.15,0.61,-10.63,-5.12,2.2,-10.71,-13.69,-5.35,-7.62,-21.37,-15.51,-7.66,-21.84,-29.12,-14.24,-17.93,-31.73,-27.05,-26.06,-32.74,-43.5,-34.87,-42.97,-45.99,-52.77,-40.56,-44.11,-69.9,-62.91,-55.54,-62.35,-59.91,-56.67,-65.46,-74.81,-61.42,-59.96,-58.72,-60.74,-60.27,-52.65,-66.57,-60.78,-32.63,-52.7,-49.85,-25.02,-35.54,-26.92,-34.28,-16.76,-20.17,-12.17,-5.58,12.3,12.96,20.01,32.22,35.55,25.68,51.03,57.57,52.41,67.55,72.04,74.28,92.16,95.06,121.32,120.42,130.55,149.77,126.51,147.9,176.74,173.55,156.19,168.83,221.43,225.43,201.96,211.57,245.89,227.72,234.51,240.48,257.58,268.2,287.31,276.51,305.21,320.6,306.29,353.67,315.92,339.49,368.56,339.82,310.6,385.29,334.76,347.96,381.96,385.5,395.98,343.1,341.83,336.92,341.27,372.5,383.63,385.1,335.21,346.97,337.82,370.8,319.14,350.46,329.42,326.18,285.15,320.34,315.81,266.91,273.29,313.35,302.55,246.42,269.82,259.96,255.88,218.45,255.34,238.09,189.4,224.28,186.17,185.69,202.99,167.12,147.93,160.99,160.76,133.48,114.25,146.76,135.35,113.8,100.87,122.26,109.3,86.65,90.65,98.55,67.56,75.43,71.46,71.43,49.63,49.59,63.51,47.54,42.73,51.74,40.95,27.37,32.19,38.8,26.58,19.02,31.1,27.34,11.57,15.23,26.13,13.8,7.65,17.33,18.81,5.63,7.24,15.99,8.66,-0.31,10,11.79,0.06,0.54,12.28,5.04,-4.15,4.22,8.86,-3.55,-4.37,6.72,2.21,-7.52,0.05,6.46,-5.06,-8.69,2.65,0.14,-11.51,-4.44,3.17,-6.45,-11.87,-1.99,-2.78,-13.78,-8.18,0.5,-10.1,-16.82,-6.63,-3.31,-16.6,-12.76,-1.73,-13.4,-19.83,-8.08,-4.11,-17.21,-17.9,-4.74,-11.53,-24.19,-14.32,-6.99,-21.87,-19.69,-8.44,-14.21,-25.16,-13.66,-10.18,-22.55,-21.03,-13.51,-11.39,-25.2,-15.39,-15.21,-23.5,-29.89,-14.66,-14.02,-29.67,-21.59,-15.3,-21.05,-26.17,-22.12,-10.13,-31.25,-25.61,-20.66,-18.43,-32.21,-24.04,-13.39,-28.9,-25.8,-18.7,-27.8,-25.72,-25.92,-22.19,-33.45,-28.36,-15.49,-23.6,-41.14,-26.8,-30.89,-32.66,-42.87,-33.68,-41.16,-32.95,-42.81,-31.53,-51.04,-51.27,-41.9,-37.1,-44.81,-41.55,-32.09,-38.16,-56.94,-28.01,-48.83,-59.46,-42.35,-47,-60.13,-49.61,-40.11,-47.87,-61.4,-65.65,-51.51,-41.95,-48.91,-48.61,-54.1,-70.79,-57.23,-51.28,-52.27,-59.13,-47.37,-64.93,-66.25,-81.46,-61.23,-58.72,-84.26,-49.74,-56.95,-60.29,-68.32,-41.23,-72.41,-55.29,-48.72,-50.19,-74,-80.93,-51.78,-71.92,-51.73,-60.72,-53.24,-63.84,-66.85,-68.43,-53.63,-67.11,-59.62,-44.42,-61.18,-49.06,-47.03,-38.08,-56.32,-48.26,-34.69,-43.36,-53.14,-56.46,-44.92,-52.38,-53.52,-56.8,-63.86,-44.35,-66.27,-40.48,-63.14,-71.22,-54.07,-54.09,-60.02,-43.09,-35.51,-49.49,-52.61,-32.26,-54.05,-57.78,-41.92,-46.08,-48.34,-45.5,-37.98,-36.64,-43.81,-35.61,-38.35,-39.04,-40.28,-29.95,-29.73,-50.66,-55.59,-42.57,-35.76,-37.44,-30.35,-36.11,-35.73,-38.67,-30.7,-41.41,-36.3,-32.36,-27.71,-41.58,-42.28,-26.77,-32.51,-40.97,-29.99,-21.19,-34.44,-37.69,-28.11,-30,-29.09,-35.8,-14.64,-24.83,-36.18,-15.51,-18.71,-25.29,-23.22,-19.78,-19.86,-30.06,-18.63,-16.19,-24.49,-26.63,-11.21,-21.65,-26.76,-18.96,-14.74,-26.81,-21.93,-6.96,-19.1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B107" t="str">
+        <v>[R_06_标记]</v>
+      </c>
+      <c r="C107" t="str">
+        <v>a: 24.3ms -52.6uv b: 51.7ms 333.5uv</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B108" t="str">
+        <v>[L_06_名字]</v>
+      </c>
+      <c r="C108" t="str">
+        <v>FERG(6)_dRod</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B109" t="str">
+        <v>[L_06_放大器]</v>
+      </c>
+      <c r="C109" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B110" t="str">
+        <v>[L_06_闪光]</v>
+      </c>
+      <c r="C110" t="str">
+        <v>b白色光:3.0cd.m-2,4ms</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B111" t="str">
+        <v>[L_06_闪光背景]</v>
+      </c>
+      <c r="C111" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B112" t="str">
+        <v>[L_06_采样]</v>
+      </c>
+      <c r="C112" t="str">
+        <v>刺激间隔:2.0S</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B113" t="str">
+        <v>[L_06_分析时间]</v>
+      </c>
+      <c r="C113" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B114" t="str">
+        <v>[L_06_数据长度]</v>
+      </c>
+      <c r="C114" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B115" t="str">
+        <v>[L_06_详细数据(uv)]</v>
+      </c>
+      <c r="C115" t="str">
+        <v>-8.64,-19.34,-9.18,-5.72,-18.73,-14.22,-4.78,-16.12,-18.72,-6.3,-12.51,-21.47,-9.99,-9.2,-21.8,-14.88,-7.4,-19.79,-19.64,-7.85,-16.22,-22.94,-10.54,-12.35,-23.88,-14.77,-9.47,-22.27,-19.3,-8.56,-18.66,-22.76,-9.93,-14.19,-24.09,-13.14,-10.23,-22.83,-17.15,-7.94,-19.3,-20.61,-7.93,-14.48,-22.33,-10.09,-9.72,-21.62,-13.56,-6.35,-18.57,-17.13,-5.25,-13.94,-19.48,-6.69,-9.11,-19.98,-9.9,-5.26,-17.98,-14.03,-3.78,-14.34,-18.22,-5.1,-10.45,-20.53,-9.56,-8.33,-21.58,-14.48,-7.36,-21.29,-20.79,-9.31,-18.71,-27.86,-16.26,-16.99,-30.94,-25.92,-20.56,-35.86,-34.44,-25.36,-37.7,-49.39,-34.49,-43.71,-58.63,-46.15,-44.63,-67.13,-59.08,-48.08,-55.86,-72.74,-64.16,-62.68,-84.75,-67.44,-64.52,-85.41,-62.57,-68.1,-68.29,-75.09,-64.89,-62.11,-71.78,-63.58,-66.57,-61.04,-59.38,-42.44,-66.99,-59.37,-48.09,-46.38,-52.6,-16.15,-22.63,-26.47,-17.92,-3.85,-7.86,4.27,17.62,27.9,33.32,44.44,43.93,39.49,52.26,72.09,63.95,93.82,99.33,89.63,95.84,131,130.43,120.28,166.7,144.07,153.97,173.24,166.1,189.33,195.23,222.54,206.47,198.82,216.91,256.57,238.85,258.99,290.39,252.82,258.56,262.01,311.84,310.99,312.38,320.02,324.32,290.27,363.44,304.22,356.81,353.32,302.64,370.49,379.59,346.88,332.01,326.74,351.44,372,334.25,375.59,323.74,356.58,316.73,348.03,354,360.48,296.64,318.48,306.12,337.43,269.85,289.63,327.47,318.49,269.56,278.09,245.53,245.11,250.02,286.97,249.77,242.65,244.5,187.35,224.95,234.07,176.83,179.96,202.45,185.92,179.82,166.85,174.54,144.22,151.56,142.18,119.05,107.21,128.46,96.06,96.45,85.61,101.66,80.82,72.57,76.24,65.47,55.41,69.72,54.92,37.03,57.86,50.54,33.1,41.67,43.07,19.1,27.44,31.62,23.1,12.64,23.86,19.07,7.02,14.93,15.3,3.78,6.05,15.78,2.93,-0.96,9.77,0.94,-5.53,4.47,3.26,-9.3,-2.65,3.32,-10.65,-8.82,2.82,-7.34,-14.17,-1.07,-5.16,-17.25,-6.56,-3.24,-16.77,-12.78,-3.55,-15.77,-18.23,-5.62,-11.54,-21.93,-9.91,-9.15,-23.73,-17.04,-9.9,-22.28,-22.09,-10.38,-18.68,-25.53,-12.47,-14.64,-28.67,-16.43,-13.93,-24.95,-25.39,-11.07,-24.13,-27.99,-15.73,-21.32,-32.62,-18.36,-16.58,-28.02,-21.69,-17.54,-26.31,-26.99,-19.31,-26.27,-32.81,-23.64,-22.64,-32.35,-28.66,-14.41,-30.83,-28.63,-18.36,-23.31,-33.75,-15.81,-23.9,-35.64,-24.89,-16.22,-36.88,-32.29,-20.49,-32.67,-28.73,-29.21,-27.07,-39.38,-29.22,-19.12,-33.27,-41.01,-26.97,-42.17,-38.29,-24.28,-40.79,-43.23,-29.57,-36.04,-44.71,-46.31,-27.2,-36.23,-50.88,-29.52,-35.56,-50.66,-48.89,-52.43,-53.19,-51.03,-49.77,-53.56,-44.22,-38.98,-53.3,-54.34,-45.65,-43.39,-66.74,-55.26,-52,-70.71,-45.35,-61.81,-52.17,-61.32,-47.85,-59.77,-63.45,-66.52,-71.56,-68.26,-74.84,-55.62,-61.16,-64.28,-68.69,-61.35,-76.13,-58.31,-52.73,-87.16,-69.98,-75.15,-80.99,-68.76,-43.99,-62.86,-76.12,-64.6,-71.37,-58.72,-59.65,-58.53,-90.62,-68.85,-57.97,-83.91,-82.26,-62.6,-53.38,-85.23,-55.28,-76.38,-60.13,-75.26,-53.6,-72.53,-53.18,-43.39,-49.31,-64.46,-51.51,-71.14,-84.55,-51.6,-60.88,-61.9,-76.58,-37.27,-69.64,-72.77,-49.49,-63.76,-58.23,-67.49,-40.73,-76.57,-54.81,-45.76,-56.68,-52.07,-52.46,-47.81,-50.18,-34.9,-62.14,-60.76,-38.09,-44.77,-46.15,-60,-45.91,-55.41,-46.95,-32.29,-39.5,-69.1,-39.4,-48.37,-45.89,-48.88,-45.67,-54.08,-51.9,-47.05,-38.58,-62.69,-43.36,-48.06,-59.82,-49.46,-30.15,-48.53,-39.49,-33.34,-37.63,-43.29,-36.51,-31.21,-52.63,-35.55,-33.9,-48.83,-33.4,-27.99,-34.31,-35.53,-22.74,-25.66,-33.48,-29.92,-24.63,-40.26,-31.66,-14.54,-31.44,-25.16,-16.54,-24.65,-29.24</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B116" t="str">
+        <v>[L_06_标记]</v>
+      </c>
+      <c r="C116" t="str">
+        <v>a: 24.3ms -58.3uv b: 51.7ms 397.5uv</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B117" t="str">
+        <v>[R_07_名字]</v>
+      </c>
+      <c r="C117" t="str">
+        <v>FERG(7)_dMax</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B118" t="str">
+        <v>[R_07_放大器]</v>
+      </c>
+      <c r="C118" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B119" t="str">
+        <v>[R_07_闪光]</v>
+      </c>
+      <c r="C119" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B120" t="str">
+        <v>[R_07_闪光背景]</v>
+      </c>
+      <c r="C120" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B121" t="str">
+        <v>[R_07_采样]</v>
+      </c>
+      <c r="C121" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B122" t="str">
+        <v>[R_07_分析时间]</v>
+      </c>
+      <c r="C122" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B123" t="str">
+        <v>[R_07_数据长度]</v>
+      </c>
+      <c r="C123" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B124" t="str">
+        <v>[R_07_详细数据(uv)]</v>
+      </c>
+      <c r="C124" t="str">
+        <v>-19.81,-29.9,-29.21,-19.1,-16.61,-26.05,-31.84,-24.45,-16.29,-21,-30.78,-29.34,-19.06,-17.01,-26.55,-31.66,-23.7,-15.77,-20.88,-30.32,-28.19,-17.8,-16.21,-25.89,-30.36,-22.07,-14.39,-19.93,-29.19,-26.29,-16.34,-15.12,-25.42,-29.86,-20.56,-14.3,-20.65,-29.57,-26.14,-16.57,-17.27,-28.47,-31.99,-23.93,-19.21,-25.48,-38.41,-34.53,-22.74,-25.38,-39.46,-45.44,-39.52,-36.57,-40.05,-57.49,-56.04,-49.65,-45.94,-65.13,-65.84,-66.42,-57.94,-76.94,-91.53,-91.64,-87.56,-74.9,-102.14,-88.39,-97.55,-95.79,-97.76,-119.99,-91.47,-91.77,-112.07,-103.43,-86.47,-117.27,-86.64,-91.49,-94.26,-98.26,-106.72,-89.13,-88.69,-73.72,-72.75,-50.08,-60.87,-39.26,-24.91,-31.55,-31.57,-2.71,20.59,46.19,67.4,84.47,83.4,84.86,106.89,147.56,151.14,145.07,145.26,201.79,219.31,235.37,288.65,242.67,309.45,350.22,352.98,315.04,353.37,446.43,455.8,391.53,454.59,451.65,530.55,444.74,565.72,572.26,551.34,540.96,597.03,585.03,596.46,638.44,626.28,709.42,609.29,741.64,746.71,625.43,762.53,745.25,697.78,808.54,661.68,704.86,665.11,776.64,841.69,771.4,838.97,671.39,691.46,789.37,828.33,773.53,659.79,753.8,732.52,688.32,778.22,688.82,657.96,655.74,666.12,710.93,633.19,688.79,714.81,668.72,670.03,627.89,573.32,593.26,619.67,559.57,522.19,529.72,532.73,534.19,566.6,479.69,472.52,469.6,471.69,444.01,394.49,440.02,406.92,421.53,361.46,432.65,353.82,356.95,383.42,318.17,341.56,339.59,299.56,329.2,288.33,283.06,288.58,297.54,251.89,246.13,266.4,213.26,268.63,215.8,229.05,237.89,236.54,225.13,163.4,209.44,196.71,194.72,179.37,160.83,189,168.59,144.38,155.53,153.31,129.2,111.04,109.21,108.97,147.13,115.23,125.12,105.14,88.58,89.24,87.54,81.67,73.27,76.02,95.73,83.89,49.82,69.83,68.22,60.5,56.59,51.5,45.95,50.33,42.65,28.04,22.73,36.3,32.52,4.91,13.4,18.44,13.3,13.16,0.48,5.22,10.03,5.49,-7.15,-14.65,2.6,-7.76,-18.32,-19.14,-11.38,-8.56,-19.12,-25.77,-20.59,-17.66,-23.52,-32.9,-27.59,-24.77,-25.16,-31.11,-41.87,-34.88,-22.77,-27.38,-36.45,-37.83,-28.18,-34.92,-31.76,-42.6,-34.02,-36.26,-35.22,-52.28,-50.54,-44.37,-30.01,-49.25,-46.31,-39.35,-32.91,-39.66,-42.5,-49.91,-46.71,-35.38,-48.49,-48.74,-41.9,-33.7,-37.27,-57.94,-47.07,-45.48,-34.72,-55.22,-60.67,-51.17,-36.89,-57.54,-64.35,-72.32,-58.88,-45.52,-65.29,-72.12,-70.81,-42.96,-46.93,-74.61,-71.78,-71.31,-48.38,-77.33,-86.13,-74.02,-63.47,-64.91,-73.32,-80.07,-60.78,-52.05,-77.01,-82.04,-86.58,-86.16,-86.33,-105.68,-93.89,-61.31,-70.07,-104.16,-82.96,-67.21,-64.62,-78.93,-98.92,-110.01,-83.21,-92.94,-109.59,-103.07,-106.31,-104.81,-89.1,-104.27,-87.9,-97.03,-86.71,-80.07,-101.79,-105.58,-85.17,-92.35,-123.4,-88.91,-111.43,-102.04,-109.77,-97.57,-98.35,-93.98,-84.47,-111.4,-117.56,-99.75,-106.87,-99.45,-82.06,-102.91,-102,-104.64,-119.52,-96.53,-74.87,-108.17,-102.79,-87.17,-94.35,-88.64,-104.69,-105.11,-88.4,-86.58,-90.55,-98.3,-101.96,-83.99,-70.91,-78.03,-78.48,-101.48,-78.75,-69.86,-108.56,-69.18,-82.82,-93.1,-97.04,-97.16,-90.64,-67.61,-67.99,-96,-87.06,-79.87,-67.17,-80.52,-82.57,-68.38,-51.09,-66.17,-65.18,-91.05,-76.91,-56.43,-85.59,-87.09,-74.56,-74.72,-53.13,-65.11,-73.57,-60.46,-51.42,-78.74,-84.83,-62.83,-56.5,-61.49,-64.33,-63.07,-54.77,-65.59,-67.04,-61.14,-66.54,-45.65,-55.34,-53.51,-57.5,-39.37,-44.94,-54.85,-48.36,-55.52,-48.28,-54.34,-59.42,-40.28,-31.73,-30.84,-42.47,-39.87,-43.22,-35.73,-30.09,-47.54,-41.08,-23.91,-35.54,-42.34,-44.86,-35.22,-16.57,-35.5,-34.36,-33.16,-16.85,-23.53,-35.83,-27.29,-24.01,-16.91,-27.24,-29.74,-20,-17.47,-11.97,-30.22,-23.52</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B125" t="str">
+        <v>[R_07_标记]</v>
+      </c>
+      <c r="C125" t="str">
+        <v>a: 25.2ms -134.2uv b: 55.5ms 618.9uv</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B126" t="str">
+        <v>[L_07_名字]</v>
+      </c>
+      <c r="C126" t="str">
+        <v>FERG(7)_dMax</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B127" t="str">
+        <v>[L_07_放大器]</v>
+      </c>
+      <c r="C127" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B128" t="str">
+        <v>[L_07_闪光]</v>
+      </c>
+      <c r="C128" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B129" t="str">
+        <v>[L_07_闪光背景]</v>
+      </c>
+      <c r="C129" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B130" t="str">
+        <v>[L_07_采样]</v>
+      </c>
+      <c r="C130" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B131" t="str">
+        <v>[L_07_分析时间]</v>
+      </c>
+      <c r="C131" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B132" t="str">
+        <v>[L_07_数据长度]</v>
+      </c>
+      <c r="C132" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B133" t="str">
+        <v>[L_07_详细数据(uv)]</v>
+      </c>
+      <c r="C133" t="str">
+        <v>9.18,-3.35,3.86,16.31,9.41,-4.04,1.43,14.79,9.83,-4.28,-0.65,13.39,10.46,-4.02,-2.28,12.17,11.34,-3.23,-3.42,11.17,12.45,-1.93,-4.04,10.4,13.76,-0.17,-4.17,9.82,15.16,1.95,-3.88,9.38,16.59,4.3,-3.24,8.97,17.91,6.82,-2.49,8.33,18.72,9.02,-1.7,7.37,19.1,10.15,-1.62,5.28,18.69,11.29,-1.71,2.27,15.46,9.64,-4.35,-1.01,12.4,8.85,-6.34,-7.32,1.65,1.37,-15.48,-17.64,-3.27,-9.42,-28.36,-30.91,-17.61,-10.7,-32.76,-35.8,-39.47,-33.03,-43.82,-51.61,-60.63,-41.67,-48.73,-73.86,-64.63,-47.52,-70.53,-74.48,-63.2,-73.36,-99.73,-83.95,-92.29,-97.16,-98.83,-100.78,-90.4,-65.63,-97.96,-106.37,-92.54,-65.05,-71.75,-52.27,-31.29,-6.43,-35.88,-52.92,-22.62,14.47,46.04,26.99,56.58,102.98,67.36,122.25,137.04,117.59,140.44,170.76,160.16,221.58,225.68,269.24,253.06,332.47,325.04,355.97,359.69,360.42,370.42,409.85,419.49,471.82,444.53,529.58,530.7,491.17,511.32,580.43,505.32,601.34,671.91,627.5,625.21,672.31,761.77,726.47,676.14,756.36,755.65,689.96,796.17,779.07,681.82,714.23,836.71,847.43,758.8,740.09,813.65,778.05,737.54,787.51,725.79,723.51,784.26,740.72,863.56,740.14,823.95,853.6,733.7,805.6,718.86,693.51,733.1,636.18,752.33,641.66,704.25,711.26,618.65,611.37,621.98,582.12,555.89,667.19,629.98,599.44,573.34,589.05,523.89,509.67,503.06,513.16,516.72,469.91,420.68,475.79,487.38,429.28,434.35,403.74,441.64,354.81,360.08,385.87,372.9,328.96,322.63,298.63,321.02,291.57,298.94,315.07,313.57,272.35,245.18,272.03,266.27,229.26,202.15,237.94,241.74,243.25,217.44,223.72,222.53,180.08,156.25,215.92,197.72,180.75,153.68,180.68,186.6,141.45,129.83,142.91,171.34,127.25,132.59,141.87,129.38,131.47,94.93,103.94,119.56,121.58,98.25,86.12,92.27,90.66,79.01,60.02,68.01,92.94,57.9,69.11,72.51,58.18,52.38,47.09,44.69,52.08,31.29,36.26,28.47,39.28,31.02,16.18,25.44,30.45,15.85,3.43,12.2,19.29,13.12,-3.73,2.02,10.91,5.07,-8.93,-3.7,4.97,6.63,-9.13,-14.56,2.24,-2.67,-22.45,-20.87,-2.2,-1.36,-20.3,-20.72,-9.15,-12.34,-20.22,-23.21,-9.53,-6.34,-17.52,-31.95,-17.25,-15.14,-28.39,-37.02,-24.63,-17.68,-24.12,-37.21,-16.49,-17.49,-26.39,-28.06,-35.74,-17.38,-29.67,-38.73,-34.75,-28.38,-26.32,-34.61,-31.08,-20.17,-18.68,-32.84,-40.84,-37.9,-33.48,-34.66,-47.75,-42.5,-46.28,-48.46,-36.43,-22.53,-33.98,-43.68,-61.63,-31.19,-42.92,-41.77,-55.86,-51.52,-53.63,-74.46,-50.56,-60.17,-53.58,-58.38,-75.32,-42.78,-40.96,-49.82,-63.69,-48.81,-39.86,-52.44,-95.72,-85.32,-55.57,-68.63,-67.32,-90.69,-49.34,-80.91,-69.23,-71.62,-58.02,-88.41,-74.83,-68.03,-66.48,-65.52,-97.6,-105.45,-60.05,-89.91,-90.2,-109.82,-73.09,-88.69,-77.24,-106.13,-89.81,-63.65,-97.02,-103.89,-81.09,-72.13,-74.26,-79.82,-76.48,-87.25,-100.17,-84.28,-89.04,-58.45,-96.36,-91.86,-64.9,-74.13,-100.81,-89.75,-71.33,-81.69,-64.47,-87.7,-95.33,-65.28,-74.05,-73.18,-87.13,-67.62,-75.69,-93.4,-74.82,-60.45,-66.05,-72.99,-62.12,-66.69,-56,-75.24,-59.68,-50.62,-67.41,-74.14,-75.87,-54.21,-43.3,-88.28,-82.89,-65.08,-61.88,-86.25,-89.83,-54.4,-59.11,-55.6,-59.82,-57.73,-46.62,-69.42,-74.8,-47.23,-50.69,-48.88,-67.52,-73.61,-39.66,-69.35,-70.99,-47.05,-40.56,-55,-63.77,-71.9,-43.64,-47.32,-65.73,-52.09,-52.74,-35.68,-51.31,-47.32,-38.77,-30.39,-57.88,-44.08,-44.6,-42.85,-41.49,-48.57,-35.96,-29.61,-34.67,-45.41,-26.86,-34.09,-43.27,-34.04,-31.46,-19.58,-24.19,-33.31,-22.51,-10.77,-26.39,-34.57,-20.36,-9,-19.73,-28.02,-24.04,-8.56,-20.12,-29.89,-23.32,-1.39,-8.6</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B134" t="str">
+        <v>[L_07_标记]</v>
+      </c>
+      <c r="C134" t="str">
+        <v>a: 25.2ms -137.3uv b: 55.6ms 630.0uv</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B135" t="str">
+        <v>[R_08_名字]</v>
+      </c>
+      <c r="C135" t="str">
+        <v>FERG(8)_dOps</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B136" t="str">
+        <v>[R_08_放大器]</v>
+      </c>
+      <c r="C136" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B137" t="str">
+        <v>[R_08_闪光]</v>
+      </c>
+      <c r="C137" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B138" t="str">
+        <v>[R_08_闪光背景]</v>
+      </c>
+      <c r="C138" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B139" t="str">
+        <v>[R_08_采样]</v>
+      </c>
+      <c r="C139" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B140" t="str">
+        <v>[R_08_分析时间]</v>
+      </c>
+      <c r="C140" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B141" t="str">
+        <v>[R_08_数据长度]</v>
+      </c>
+      <c r="C141" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B142" t="str">
+        <v>[R_08_详细数据(uv)]</v>
+      </c>
+      <c r="C142" t="str">
+        <v>-23.44,-33.6,-32.05,-20.18,-9.41,-10.1,-21.32,-31.89,-31.19,-19.56,-8.06,-7.45,-17.92,-28.96,-29.35,-18.53,-6.53,-4.9,-14.96,-26.67,-28.35,-18.14,-6.02,-3.36,-12.68,-24.82,-27.33,-17.46,-4.69,-0.43,-8.63,-20.53,-23.72,-14.65,-0.88,4.43,-3.54,-15.07,-20.63,-11.85,0.37,5.44,-2.3,-15.89,-22.93,-17.5,-6.05,-0.72,-8.88,-21.86,-31.08,-24.82,-11.91,-4.66,-9.7,-22.05,-28.35,-22.51,-7.7,2.55,-0.54,-8.93,-16.02,-11.16,0.51,8.81,6.06,-9.67,-22.4,-22.12,-13.84,-8.39,-15.1,-30.7,-46,-46.33,-40.54,-30.58,-36.99,-42.92,-54.55,-49.65,-31.43,-14.42,-8.3,-12.51,-15.14,-12.59,2.22,26.95,25.92,16.87,6.31,-3.62,2.33,5.54,-1.38,-19.19,-41.69,-57.03,-52.64,-41.62,-49.34,-67.35,-75.23,-68.13,-66.54,-38.6,-27.28,-21.84,-22.25,-12.53,2.85,33.81,53.07,50.97,32.51,31.12,34.21,44.39,48.83,29.44,-1.04,-22.76,-33.24,-32.18,-34.78,-61.59,-77.62,-95.47,-77.2,-69.33,-48.08,-47.27,-49.44,-42.82,-23.09,5.01,28.61,34.67,38.28,46.55,39.55,50.09,61.43,55.95,34.8,14.71,-6.3,-8.31,-12.02,-27.34,-53.16,-71.84,-87.64,-73.82,-58.9,-63.51,-61.72,-64.61,-57.36,-39.13,-14.97,-2.14,0.64,-6.89,2.35,24.49,37.34,37.76,20.08,11.84,5.06,1.33,3.34,-2.74,-21.84,-41.77,-58.02,-56.18,-38.85,-37.64,-50.28,-60.61,-58.77,-47.39,-27.62,-18.5,-17.49,-24.12,-23.09,-11.65,7.79,13.32,13.5,1.02,-11.9,-3.07,3.72,8.37,0.66,-15.45,-27.06,-25.51,-16.75,-10.78,-14.85,-28.77,-38.92,-31.86,-17.9,-7.65,-7.63,-18.27,-25.14,-20.08,-5.65,5.51,5.34,-7.06,-15.5,-13.38,-2.84,6.82,5.33,-8.38,-19.82,-21.25,-11.12,-1.07,-2.11,-14.16,-26.71,-28.01,-16.91,-6.08,-5.1,-14.84,-26.86,-28.68,-18.46,-6.25,-3.87,-13.65,-25.94,-29.05,-19.96,-8.23,-5.1,-14.54,-27.43,-32.09,-24.07,-11.8,-7.79,-16.3,-29.39,-34.57,-27.18,-14.54,-9.15,-16.48,-29.25,-35.2,-28.34,-15.34,-8.73,-14.82,-27.49,-34.21,-28.22,-15.1,-7.51,-12.47,-25.01,-32.53,-27.47,-14.44,-5.83,-9.72,-21.97,-30.27,-26.16,-13.27,-3.78,-6.55,-18.49,-27.53,-24.47,-11.89,-1.65,-3.37,-14.98,-24.79,-22.89,-10.79,0.02,-0.7,-11.97,-22.56,-21.89,-10.42,0.84,1.07,-9.84,-21.14,-21.75,-11.03,0.58,1.74,-8.73,-20.68,-22.56,-12.66,-0.79,1.29,-8.64,-21.14,-24.26,-15.24,-3.16,-0.13,-9.42,-22.33,-26.62,-18.48,-6.23,-2.21,-10.74,-23.9,-29.25,-21.99,-9.59,-4.55,-12.17,-25.41,-31.73,-25.33,-12.8,-6.7,-13.29,-26.45,-33.62,-28.06,-15.44,-8.26,-13.73,-26.66,-34.57,-29.87,-17.2,-8.98,-13.24,-25.83,-34.42,-30.58,-17.95,-8.74,-11.78,-23.93,-33.14,-30.21,-17.74,-7.63,-9.45,-21.11,-30.92,-28.96,-16.79,-5.91,-6.55,-17.69,-28.08,-27.18,-15.47,-3.96,-3.48,-14.1,-25.06,-25.29,-14.18,-2.21,-0.69,-10.77,-22.29,-23.72,-13.37,-1.08,1.41,-8.11,-20.17,-22.83,-13.37,-0.89,2.52,-6.42,-18.95,-22.85,-14.35,-1.8,2.49,-5.79,-18.7,-23.82,-16.34,-3.78,1.37,-6.18,-19.34,-25.59,-19.15,-6.64,-0.62,-7.32,-20.59,-27.87,-22.46,-10.03,-3.11,-8.85,-22.06,-30.25,-25.83,-13.5,-5.66,-10.33,-23.31,-32.28,-28.82,-16.62,-7.85,-11.35,-23.95,-33.57,-31.04,-19,-9.33,-11.59,-23.66,-33.84,-32.23,-20.41,-9.89,-10.87,-22.33,-32.97,-32.29,-20.79,-9.49,-9.21,-19.99,-31.04,-31.32,-20.25,-8.31,-6.81,-16.86,-28.3,-29.6,-19.1,-6.65,-4,-13.33,-25.13,-27.49,-17.71,-4.93,-1.22,-9.82,-21.97,-25.46,-16.54,-3.57,1.1,-6.78,-19.25,-23.9,-15.97,-2.98,2.57,-4.57,-17.32,-23.14,-16.28,-3.39,2.97,-3.41,-16.36,-23.31,-17.59,-4.9,2.23,-3.34,-16.38,-24.4,-19.83,-7.41,0.46,-4.21,-17.2</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B143" t="str">
+        <v>[R_08_标记]</v>
+      </c>
+      <c r="C143" t="str">
+        <v>105.5uv</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B144" t="str">
+        <v>[L_08_名字]</v>
+      </c>
+      <c r="C144" t="str">
+        <v>FERG(8)_dOps</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B145" t="str">
+        <v>[L_08_放大器]</v>
+      </c>
+      <c r="C145" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B146" t="str">
+        <v>[L_08_闪光]</v>
+      </c>
+      <c r="C146" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B147" t="str">
+        <v>[L_08_闪光背景]</v>
+      </c>
+      <c r="C147" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B148" t="str">
+        <v>[L_08_采样]</v>
+      </c>
+      <c r="C148" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B149" t="str">
+        <v>[L_08_分析时间]</v>
+      </c>
+      <c r="C149" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B150" t="str">
+        <v>[L_08_数据长度]</v>
+      </c>
+      <c r="C150" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B151" t="str">
+        <v>[L_08_详细数据(uv)]</v>
+      </c>
+      <c r="C151" t="str">
+        <v>1.7,-8.81,-15.83,-10.97,0.09,3.97,-3.82,-13.44,-13.08,-3.24,4.8,0.52,-10.36,-15.19,-8.3,1.75,2.21,-7.59,-16.06,-13.08,-3.1,2.86,-3.17,-13.37,-14.25,-4.29,5.71,5.09,-4.24,-9.13,-2.89,9.81,12.81,6.5,-4.17,-2.59,7.31,14.55,7.84,-4.07,-9.5,-3.57,4.99,3.6,-8.24,-16.56,-16.52,-5.58,1.49,-6.09,-16.17,-14.61,-2.55,8.88,9.5,2.59,-0.03,9.11,18.77,23.64,13.36,3.28,8.18,14.92,18.05,5.9,-9.05,-18.22,-14.99,-12.11,-16.63,-28.17,-42.68,-34.99,-24.41,-24.61,-28.76,-28.85,-26.04,-9.71,6.62,8.74,11.01,10.56,22.19,33.45,40.43,29.52,17.45,8.88,17.88,13.24,-1.98,-23.91,-36.99,-41.89,-39.71,-42.43,-62.66,-61.95,-67.99,-44.16,-43.24,-42.77,-36.47,-24.94,-1.59,23.1,32.87,22.09,27.87,47.11,60.53,50.31,47.25,23.73,30.69,24.11,15.18,-5.67,-28.88,-52.79,-52.13,-49.4,-53.64,-63.56,-76.94,-59.64,-41.38,-28.92,-28.52,-27.27,-8.29,20.34,41.27,49.14,55.05,44.82,48.3,66.42,68.58,49.77,22.82,24.13,14.42,4.6,-19.33,-38.66,-58.35,-60.74,-60.96,-50.97,-70.59,-72.91,-60.81,-35.06,-28.55,-21.61,-18.95,-5.97,18.44,38.95,38.17,34.41,23.33,28.49,40.9,43.08,21.46,5.61,-3.5,-5.01,-12.47,-28.72,-50.68,-50.37,-54.02,-49.54,-43.33,-52.28,-58.68,-41.86,-23.64,-15.27,-17.63,-18.35,-8.64,7.1,17.32,14.62,8.49,6.88,15.06,19.28,10.28,-0.39,-14.86,-13.7,-8.36,-8.31,-19.12,-35.34,-37.21,-23.22,-20.64,-22.56,-30.47,-32.75,-19.87,-5.79,-1.76,-8.12,-13.33,-6.97,6.17,13.45,6.34,-5.68,-5.72,2.67,9.75,5.78,-7.01,-15.31,-11.54,-2.45,-1.65,-11.29,-21.59,-20.74,-11.43,-4.39,-8.62,-18.28,-21.62,-12.72,-1.8,-1.12,-10.46,-18.08,-13.95,-3.01,1.94,-5.71,-16.34,-18.79,-9.64,-2.19,-5.71,-17.2,-23.68,-18.09,-8.21,-6.69,-16.18,-25.73,-24.13,-14.08,-7.43,-12.93,-23.8,-26.7,-18.34,-8.69,-9.43,-19.65,-26.81,-22.35,-11.52,-7.59,-15.19,-25.35,-25.67,-15.82,-7.81,-11.37,-22.13,-27.02,-20.02,-9.49,-8.1,-17.26,-25.72,-22.93,-11.97,-5.84,-11.61,-21.97,-23.96,-14.84,-5.29,-6.53,-16.7,-23.13,-17.68,-6.65,-3.08,-11.02,-20.55,-19.86,-9.52,-1.86,-5.95,-16.63,-20.79,-13.22,-2.96,-2.35,-12.02,-20.19,-16.9,-6.12,-0.93,-7.65,-18.19,-19.86,-10.75,-2.04,-4.46,-15.27,-21.58,-15.97,-5.52,-3.18,-12.09,-21.78,-20.85,-10.78,-4.17,-9.41,-20.56,-24.5,-16.88,-7.36,-7.91,-18.3,-26.36,-22.74,-12.26,-8.04,-15.62,-26.2,-27.36,-18.06,-9.96,-13.21,-24.22,-29.95,-23.74,-13.41,-11.72,-20.96,-30.12,-28.28,-17.82,-11.55,-17.17,-27.94,-30.85,-22.38,-12.8,-13.69,-23.91,-30.99,-26.23,-15.27,-11.25,-18.85,-28.67,-28.57,-18.44,-10.31,-13.76,-24.33,-28.91,-21.64,-11.02,-9.61,-18.79,-27.11,-24.14,-13.17,-7.17,-13.09,-23.45,-25.38,-16.24,-6.84,-8.31,-18.61,-25.02,-19.55,-8.64,-5.33,-13.49,-23.09,-22.38,-12.15,-4.73,-9.1,-19.95,-24.15,-16.65,-6.63,-6.34,-16.26,-24.52,-21.29,-10.69,-5.8,-12.81,-23.49,-25.19,-16.17,-7.69,-10.4,-21.37,-27.69,-22.09,-11.76,-9.65,-18.73,-28.42,-27.4,-17.34,-10.86,-16.25,-27.4,-31.2,-23.46,-13.96,-14.61,-24.99,-32.88,-29.05,-18.47,-14.27,-21.83,-32.24,-33.12,-23.62,-15.45,-18.68,-29.54,-34.97,-28.47,-17.99,-16.26,-25.39,-34.28,-32.12,-21.44,-15.1,-20.66,-31.24,-33.83,-25.11,-15.44,-16.31,-26.43,-33.26,-28.25,-17.18,-13.18,-20.78,-30.46,-30.15,-19.9,-11.82,-15.37,-25.92,-30.36,-22.99,-12.43,-11.19,-20.49,-28.77,-25.74,-14.83,-9.04,-15.18,-25.63,-27.54,-18.46,-9.28,-11.03,-21.52,-27.99,-22.57,-11.85,-8.86,-17.29,-27.01,-26.35,-16.25,-9.13,-13.81,-24.84,-29.09,-21.67</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B152" t="str">
+        <v>[L_08_标记]</v>
+      </c>
+      <c r="C152" t="str">
+        <v>103.1uv</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B153" t="str">
+        <v>[R_09_名字]</v>
+      </c>
+      <c r="C153" t="str">
+        <v>FERG(9)_dMax</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B154" t="str">
+        <v>[R_09_放大器]</v>
+      </c>
+      <c r="C154" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B155" t="str">
+        <v>[R_09_闪光]</v>
+      </c>
+      <c r="C155" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B156" t="str">
+        <v>[R_09_闪光背景]</v>
+      </c>
+      <c r="C156" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B157" t="str">
+        <v>[R_09_采样]</v>
+      </c>
+      <c r="C157" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B158" t="str">
+        <v>[R_09_分析时间]</v>
+      </c>
+      <c r="C158" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B159" t="str">
+        <v>[R_09_数据长度]</v>
+      </c>
+      <c r="C159" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B160" t="str">
+        <v>[R_09_详细数据(uv)]</v>
+      </c>
+      <c r="C160" t="str">
+        <v>-13.74,-13.51,-10.76,-6.57,-2.61,-0.45,-0.93,-3.73,-7.58,-10.73,-11.78,-10.16,-6.49,-2.21,0.93,1.71,-0.14,-3.75,-7.52,-9.79,-9.51,-6.79,-2.7,1.1,2.98,2.21,-0.85,-4.95,-8.27,-9.36,-7.95,-4.5,-0.66,2.22,2.43,0.34,-3.9,-8.12,-10.26,-10.8,-8.42,-4.48,-1.57,-0.41,-1,-4.77,-10.16,-14.09,-15.6,-14.24,-12.5,-8.16,-6.71,-7.34,-9.29,-15.9,-24.47,-26.72,-24.94,-28.49,-20.66,-20.3,-21.65,-27.39,-33.07,-32.98,-43.83,-49.26,-51.86,-41.1,-48.38,-45.93,-53.09,-54.77,-60.05,-70.71,-76.86,-84.18,-66.27,-59.62,-63.92,-70,-62.16,-72.23,-76.78,-85.78,-87.57,-88.82,-79.13,-73.2,-45.04,-68.36,-60.07,-75.19,-58.09,-45.54,-68.35,-20.8,-17.44,2.22,0.54,28.02,6.06,41.24,14.49,15.85,83.94,47.14,60.91,103.64,145.54,117.16,182.67,133.91,146.21,160.68,200.88,196.46,302.26,321.27,268.54,332.97,323.17,322.42,396.71,351.35,386.23,398.86,472.57,417.91,447.91,503.8,558.38,511.2,554.71,539.82,584.91,557.55,613.38,561.14,652.98,562.9,656.18,708.53,615.14,675.41,678.53,637.04,699.18,675.09,728.5,700.8,721.81,695.27,770.33,694.68,746.16,864.11,802.11,829.14,802.61,836.67,721.52,744.2,708.57,837.46,805.97,786.17,694.17,818.28,724.42,662.88,675.24,701.33,752.3,681.97,685.89,752.73,694.73,724.59,700.46,617.97,716.3,592.5,662.43,624.64,650.74,607.87,635.26,517.6,572.38,551.69,597.7,558.94,501.36,533.19,464.36,447.92,496.01,488.26,487.57,451.22,453.85,494.4,469.59,453.6,384.49,366.72,333.99,370.3,401.77,362.03,350.75,365.76,374.24,277.01,326.55,329.38,299.37,251.47,274.87,259.89,262.15,250.94,250.08,240.77,219.8,209.83,232.6,222.53,182.5,195.89,187.13,164.97,203.46,170.44,169.73,157.5,148.16,141.14,113.42,159.27,130.94,149.71,113.22,84.68,79.6,104.52,70.02,107.34,86.08,90.94,92.15,70.71,71.92,76.73,46.45,53.56,46.41,51.12,49.21,43.46,42.4,41.68,37.78,29.48,18.78,17,18.37,24.23,23.33,27.33,24.79,7.78,5.03,2.34,5.72,10.84,6.5,6.09,4.54,5.89,2.69,-4.78,-5.68,-4.03,-7.93,-10.18,-7.15,-1.4,-4.23,-10.03,-8.19,-11.92,-23.38,-13.63,-18.57,-17.62,-15.75,-11.48,-7.99,-10.94,-21.39,-28.18,-28.7,-23.2,-30.13,-20.37,-28.52,-13.62,-18.15,-38.06,-35.38,-34.72,-36.95,-35,-38,-32.43,-22.54,-31.56,-27.25,-50.91,-41.55,-45.46,-38.48,-41.49,-35.05,-35.58,-36.32,-45.65,-59.25,-47.28,-46.42,-68.44,-61.49,-47.32,-52.6,-40.74,-57.81,-50.3,-69.3,-56.42,-77.29,-75.09,-58.91,-57.1,-45.01,-60.62,-60.89,-55.85,-66.13,-77.94,-71.79,-67.83,-51.98,-62.79,-49.34,-64.04,-64.64,-69.7,-79.46,-74.28,-80.07,-51.95,-56.13,-78.94,-50.45,-71.77,-68.53,-78.53,-90.26,-86.27,-80.21,-61.56,-77.16,-86.35,-82.88,-76.21,-92.22,-99.06,-97.99,-74.01,-92.75,-83.45,-71.68,-61.21,-74.29,-88.1,-73.09,-79.14,-75.91,-102.15,-95.97,-87.57,-72.85,-61.23,-94.18,-100.41,-85.17,-104.95,-86.39,-84.34,-59.29,-53.65,-63.85,-93.43,-77.24,-93.32,-71.6,-72.75,-86.99,-65.2,-61.53,-78.67,-72.36,-67.43,-86.83,-66.45,-72.14,-62.28,-75.69,-62.04,-52.68,-76.05,-59.92,-72.78,-69.72,-91.49,-72.67,-71.31,-86.93,-69.58,-78.29,-85.08,-74.12,-76.26,-59.27,-77.61,-78.33,-59.05,-75.66,-44.59,-48.94,-74.08,-63.25,-67.45,-63.66,-49.67,-65.27,-42.12,-40.55,-43.7,-42.07,-35.97,-52.63,-45.42,-55.29,-38.8,-38.51,-36.24,-33.37,-25.64,-34.63,-41.35,-38.29,-50.09,-52.57,-34.63,-27.53,-34.07,-25.9,-26.23,-25.81,-40.05,-31.97,-28.47,-25.49,-18.87,-19.3,-22.97,-26.21,-25.33,-35.63,-24.23,-36.79,-22.2,-20.94,-21.79,-10.52,-12.95,-19.79,-15.59,-18.87,-31.65,-30.85,-23.55,-10.02,-7.45,-7.93,-12.26</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B161" t="str">
+        <v>[R_09_标记]</v>
+      </c>
+      <c r="C161" t="str">
+        <v>a: 29.9ms -164.4uv b: 62.8ms 689.0uv</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B162" t="str">
+        <v>[L_09_名字]</v>
+      </c>
+      <c r="C162" t="str">
+        <v>FERG(9)_dMax</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B163" t="str">
+        <v>[L_09_放大器]</v>
+      </c>
+      <c r="C163" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B164" t="str">
+        <v>[L_09_闪光]</v>
+      </c>
+      <c r="C164" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B165" t="str">
+        <v>[L_09_闪光背景]</v>
+      </c>
+      <c r="C165" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B166" t="str">
+        <v>[L_09_采样]</v>
+      </c>
+      <c r="C166" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B167" t="str">
+        <v>[L_09_分析时间]</v>
+      </c>
+      <c r="C167" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B168" t="str">
+        <v>[L_09_数据长度]</v>
+      </c>
+      <c r="C168" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B169" t="str">
+        <v>[L_09_详细数据(uv)]</v>
+      </c>
+      <c r="C169" t="str">
+        <v>11.86,15.29,12.86,6.16,-0.63,-3.28,-0.06,7.25,14.44,17.29,14.34,7.45,0.93,-1.25,2.58,10.12,16.87,19.04,15.14,8.21,1.75,0.14,3.81,11.65,17.28,18.93,14.54,6.2,-0.24,-2.3,3.06,9.22,15.43,14.49,7.02,0.74,-6.03,-10.28,-3,0.31,6.66,0.71,-7.79,-18.27,-22.4,-20.06,-18.03,-16.07,-11.62,-20.02,-20.27,-35.81,-49,-48.39,-48.76,-49.35,-36.31,-39.24,-68.27,-60.79,-70.31,-62.59,-78.03,-80.81,-54.69,-59.8,-83.43,-88.55,-87.44,-68.14,-91.32,-53.96,-37.62,-75.34,-53.12,-52.41,-83.63,-64.54,-47.29,-26.48,0.74,5.25,-25.63,2.92,9.67,9,30.73,59.68,68.2,61.44,82.68,104.97,121.24,99.55,166.33,163.24,197.74,232.04,243.82,190.45,228.77,271.2,269.08,335.61,389.65,368.05,385.75,396.33,370.6,379,406.88,491.91,520.35,523.18,536.24,586.2,534.86,558.82,549.57,569.23,630.41,601.93,587.04,705.53,656.29,638.99,646.31,768.5,648.68,723.97,702.21,714.91,706.54,760.64,728.25,684.7,788.19,824.19,786.45,788.25,719.74,717.63,840.09,780.24,789.75,672.33,792.25,805.35,673.46,765.98,764.51,699.54,773.14,675.76,707.48,721.93,716.7,609.58,664.76,705.74,680.58,597.91,594.93,617.7,572.65,650.01,556.26,617.53,547.96,510.9,528.77,477.88,547.51,500,485.34,514.61,470.78,452.96,479.39,374.45,398.46,402.84,415.49,369.86,356.42,323.71,304.53,314.87,368.35,298.09,319.02,328.48,308.25,284.58,314.14,312.63,300.91,239.65,287.49,264.9,244.8,230.41,205.4,185.84,210.32,197.54,211.24,196.34,216.49,173.47,176.04,181.68,170.43,159.35,194.73,163.93,150.9,133.61,107.87,136.43,139.42,123.76,120.69,145.37,96.69,103.89,83.82,109.01,96.89,103.41,107.85,88.89,81.77,77.91,48.59,51.38,45.67,65.67,50.15,59.17,51.49,37.37,23.48,36.89,32.55,42.78,43.55,30.66,14,9.19,6.12,7.85,11.25,18.16,16.06,7.03,3.43,-2.51,-15.56,-8.26,-1.83,4.86,6.09,-4.82,-14.06,-22.51,-20.02,-15.09,-7.3,-2.06,-6.5,-8.4,-17.23,-28.39,-27.62,-20.44,-11.36,-3.21,-6.66,-22.19,-30.37,-28.04,-27.11,-23.99,-22.23,-18.18,-14.43,-21.71,-24.42,-41.18,-30.32,-19.39,-12.76,-19.51,-15.66,-37,-43.08,-43.45,-42.83,-33.97,-26.76,-17.07,-31.79,-46.04,-38.73,-55.49,-51.39,-46.74,-32.23,-43.25,-25.77,-48.44,-65.06,-60.22,-53.35,-42.39,-37.12,-54.29,-48.49,-45.45,-69.04,-53.47,-61.6,-46.18,-55.45,-45.73,-66.23,-71.44,-85.31,-72.03,-76.79,-77.37,-67.46,-47.21,-71.75,-86.44,-67.44,-67.38,-83.46,-66.02,-48.18,-84.31,-87.16,-92.69,-103.5,-84.39,-93.94,-70.16,-84.81,-89.79,-94.15,-92.85,-104.64,-90.71,-76.12,-62.93,-74.33,-90.86,-94.39,-105.11,-89.59,-96.05,-75.1,-97.19,-70.88,-60.6,-65.37,-100.33,-75.24,-92.94,-87.27,-83.16,-53.75,-70.35,-94.94,-78.97,-110.77,-75.86,-73.54,-62.04,-77.99,-57.97,-62.49,-83.04,-100.4,-104.91,-84.36,-78.42,-59.32,-56.26,-87.14,-85.45,-92.87,-63.89,-69.99,-77.33,-72.08,-78.74,-75.31,-83.63,-93.01,-65.37,-80.16,-59.51,-64.26,-71.97,-84.17,-72.71,-83.19,-63.36,-81.2,-47.97,-79.41,-53.62,-80.05,-70.72,-66.29,-73.41,-72.39,-50.64,-48.35,-61.93,-63.09,-71.63,-89.96,-76.21,-62.47,-62.34,-68.95,-58.47,-79.27,-88.16,-87.33,-64.54,-62.56,-63.85,-50.65,-71.54,-65.46,-56.25,-70.51,-64.3,-37.66,-50.68,-49.88,-45.13,-48.34,-57.98,-63.1,-45.13,-47.5,-38.78,-41.93,-50.68,-42.17,-41.15,-48.34,-39.02,-26.78,-34.81,-34.44,-42.21,-45.66,-51.14,-35.46,-32.22,-15.2,-25.48,-26.97,-29.61,-32.01,-37.23,-29.85,-15.07,-13.53,-11.26,-17.27,-28.32,-28.36,-35.06,-25.06,-21.02,-8.02,-15.21,-10.26,-26.91,-24.96,-28.51,-20.22,-9.24,-10.75,-6.96,-17.81,-25.59,-27.67,-32.39,-24.25,-18.83,-12.85,-13.23</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B170" t="str">
+        <v>[L_09_标记]</v>
+      </c>
+      <c r="C170" t="str">
+        <v>a: 29.8ms -160.3uv b: 62.7ms 712.6uv</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B171" t="str">
+        <v>[R_10_名字]</v>
+      </c>
+      <c r="C171" t="str">
+        <v>FERG(10)_dOps</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B172" t="str">
+        <v>[R_10_放大器]</v>
+      </c>
+      <c r="C172" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B173" t="str">
+        <v>[R_10_闪光]</v>
+      </c>
+      <c r="C173" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B174" t="str">
+        <v>[R_10_闪光背景]</v>
+      </c>
+      <c r="C174" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B175" t="str">
+        <v>[R_10_采样]</v>
+      </c>
+      <c r="C175" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B176" t="str">
+        <v>[R_10_分析时间]</v>
+      </c>
+      <c r="C176" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B177" t="str">
+        <v>[R_10_数据长度]</v>
+      </c>
+      <c r="C177" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B178" t="str">
+        <v>[R_10_详细数据(uv)]</v>
+      </c>
+      <c r="C178" t="str">
+        <v>-17.78,-16.15,-14.6,-12.93,-11.58,-10.52,-9.97,-10.05,-10.38,-11.45,-12.49,-13.56,-14.91,-16.08,-17.2,-17.94,-18.14,-18.55,-17.74,-17.24,-15.62,-14.73,-12.89,-11.24,-10.58,-10.34,-10.23,-10.74,-12.15,-13.65,-16.91,-19.28,-22,-24.36,-25.14,-26.7,-28.37,-27.61,-26.91,-25.59,-22.69,-19.74,-15.34,-12.93,-8.07,-7.3,-3.33,-1.72,0.38,0.42,-3.93,-7.41,-12.4,-18.29,-25.22,-31.46,-40.04,-42.31,-45.62,-47.06,-48.59,-49.31,-48.21,-39.39,-32.69,-26.77,-17.85,-9.38,-2.12,5.75,11.96,22.62,21.21,15.77,18.65,13.89,4.13,0.15,-11.96,-23.88,-32.84,-42.15,-53.55,-56.64,-62.4,-62.91,-60.76,-67.24,-59.24,-49.21,-36.14,-21.4,-9.63,4.12,16.17,33.39,39.23,34.58,36.87,32.63,41.81,32.23,19.79,10.86,-6.97,-19.1,-32.69,-42.47,-64.31,-73.55,-71.84,-71.56,-74.82,-63.46,-72,-52.02,-44.32,-32.24,-18.75,-6.32,11.21,27.19,30.58,35.55,30.69,52.77,47.7,34.39,20.66,8.23,3.91,-12.3,-25.37,-36.35,-52.18,-62.9,-76.96,-73.15,-80.23,-67.02,-70.56,-61.87,-62.12,-43.08,-33.06,-21.42,-6.79,-1.8,7.25,24.55,28.94,30.97,29.15,24.39,18.64,13.83,0.76,-8.25,-18.98,-28.87,-39.31,-44.17,-49.88,-53.84,-56.34,-59.7,-62.81,-49.86,-45.99,-40.09,-30.37,-19.93,-12.53,0,6.42,9.43,8.72,18.53,16.69,8.67,7.61,0.77,-4.67,-11.45,-17.54,-23.15,-28.28,-33.27,-39.52,-39.96,-40.32,-35.4,-33.8,-30.04,-25.47,-22.74,-17.53,-12.59,-8.55,-5.37,-2.99,-2.97,-3.36,-4.32,-6.63,-10.32,-12.09,-16.7,-19.15,-22.31,-24.66,-26.37,-26.83,-27.15,-27.2,-25.71,-23.9,-22.58,-20.61,-18.83,-18.05,-16.93,-16.32,-16.13,-16.67,-17.51,-19.24,-20.42,-22.08,-23.71,-25.16,-25.95,-26.87,-27.04,-26.55,-25.79,-24.57,-23.12,-21.51,-20.1,-18.61,-17.46,-16.85,-16.52,-16.92,-17.56,-18.64,-19.88,-21.39,-22.86,-24.22,-25.31,-25.98,-26.31,-26.03,-25.34,-24.11,-22.58,-20.72,-18.83,-16.92,-15.23,-13.85,-12.88,-12.41,-12.45,-13.01,-14.02,-15.35,-16.94,-18.64,-20.24,-21.63,-22.71,-23.35,-23.48,-23.12,-22.27,-21.02,-19.45,-17.72,-15.96,-14.33,-12.97,-12.01,-11.52,-11.56,-12.14,-13.21,-14.69,-16.46,-18.4,-20.34,-22.14,-23.65,-24.76,-25.4,-25.51,-25.12,-24.26,-23.04,-21.56,-19.97,-18.43,-17.08,-16.05,-15.45,-15.34,-15.75,-16.66,-18,-19.68,-21.56,-23.5,-25.35,-26.95,-28.18,-28.95,-29.19,-28.9,-28.1,-26.87,-25.32,-23.58,-21.8,-20.13,-18.71,-17.67,-17.09,-17.01,-17.44,-18.33,-19.61,-21.14,-22.81,-24.44,-25.9,-27.05,-27.77,-28,-27.7,-26.89,-25.61,-23.97,-22.08,-20.1,-18.18,-16.47,-15.09,-14.16,-13.73,-13.83,-14.43,-15.48,-16.87,-18.47,-20.13,-21.69,-23.03,-24,-24.53,-24.56,-24.08,-23.12,-21.77,-20.13,-18.35,-16.57,-14.94,-13.61,-12.69,-12.26,-12.36,-12.99,-14.11,-15.62,-17.41,-19.33,-21.22,-22.95,-24.37,-25.38,-25.9,-25.91,-25.41,-24.47,-23.18,-21.67,-20.08,-18.56,-17.27,-16.32,-15.81,-15.82,-16.34,-17.35,-18.78,-20.53,-22.46,-24.42,-26.25,-27.82,-29,-29.71,-29.88,-29.53,-28.68,-27.41,-25.85,-24.13,-22.39,-20.8,-19.48,-18.56,-18.11,-18.16,-18.72,-19.72,-21.09,-22.69,-24.39,-26.03,-27.47,-28.57,-29.22,-29.38,-28.99,-28.1,-26.76,-25.07,-23.16,-21.19,-19.3,-17.64,-16.33,-15.48,-15.15,-15.34,-16.02,-17.12,-18.54,-20.14,-21.77,-23.28,-24.53,-25.4,-25.81,-25.71,-25.1,-24.03,-22.58,-20.86,-19.03,-17.23,-15.61,-14.31,-13.44,-13.07,-13.24,-13.93,-15.1,-16.64,-18.43,-20.32,-22.17,-23.82,-25.15,-26.04,-26.44,-26.33,-25.73,-24.7,-23.34,-21.79,-20.19,-18.7,-17.46,-16.59,-16.18,-16.29,-16.91,-18.02,-19.54,-21.34,-23.31,-25.28,-27.09,-28.62,-29.74,-30.38,-30.48,-30.06,-29.16,-27.86,-26.29,-24.59,-22.9,-21.39,-20.18,-19.38</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B179" t="str">
+        <v>[R_10_标记]</v>
+      </c>
+      <c r="C179" t="str">
+        <v>103.9uv</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B180" t="str">
+        <v>[L_10_名字]</v>
+      </c>
+      <c r="C180" t="str">
+        <v>FERG(10)_dOps</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B181" t="str">
+        <v>[L_10_放大器]</v>
+      </c>
+      <c r="C181" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B182" t="str">
+        <v>[L_10_闪光]</v>
+      </c>
+      <c r="C182" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B183" t="str">
+        <v>[L_10_闪光背景]</v>
+      </c>
+      <c r="C183" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B184" t="str">
+        <v>[L_10_采样]</v>
+      </c>
+      <c r="C184" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B185" t="str">
+        <v>[L_10_分析时间]</v>
+      </c>
+      <c r="C185" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B186" t="str">
+        <v>[L_10_数据长度]</v>
+      </c>
+      <c r="C186" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B187" t="str">
+        <v>[L_10_详细数据(uv)]</v>
+      </c>
+      <c r="C187" t="str">
+        <v>-7.4,-3.42,1.02,5.44,8.86,10.76,11.03,9.45,6.3,2.37,-1.45,-4.87,-7.01,-7.5,-6.42,-3.63,0.18,4.27,7.91,10.42,11.38,10.58,7.79,4.1,-0.4,-4.86,-8.48,-10.44,-10.64,-8.93,-5.86,-1.5,3.18,7.32,9.83,11.22,10.8,8.21,4.21,-0.93,-5.02,-8.21,-11.62,-12.37,-11.77,-9.9,-7.23,-5.71,-3.86,-3.45,-4.54,-5.51,-10.01,-12.73,-16.27,-19.12,-19.66,-19.2,-16.17,-11.89,-3.92,0.11,8.44,11.2,13.06,16.97,11.5,10.39,2.55,-4.37,-12.53,-19.36,-23.87,-28.72,-27.49,-27.25,-22.87,-26.66,-19.81,-18.64,-14.03,-17.53,-14.12,-10.04,-8.05,-3.05,2.8,8.1,12.13,18.03,35.39,35.97,44.11,35.32,31.02,25.27,14.58,0.06,-13.99,-25.49,-35.31,-54.16,-55.93,-57.41,-55.95,-49.29,-40.27,-23.07,-16.44,-2.73,7.3,15.72,27.02,30.17,30.68,35.6,45.67,47.82,55.52,49.48,33.54,30.24,21.08,7.81,-7.77,-29.32,-41.3,-62.78,-61.62,-68.86,-92.96,-92.61,-72.55,-53.44,-49.23,-26.3,-6.82,9.94,27.94,40.51,50.33,49.13,55.17,50.23,51.83,35.97,22.76,16.77,6.24,-6.94,-16.9,-28.48,-42.94,-43.23,-63.17,-63.18,-73.68,-79.98,-65.31,-71.13,-55.71,-40.2,-25.83,-8.53,10.39,24.66,43.87,45.36,52.15,45.17,52.95,42.08,26.66,10.49,4.09,-10.6,-20.11,-27.12,-31.26,-33.96,-41.17,-29.07,-40.83,-39.23,-33.38,-26.21,-26.54,-20.19,-18.88,-12.23,-4.77,4.69,14.58,22.99,23.54,33.64,28.53,31.4,25.65,21.03,11.38,0.88,-9.53,-17.35,-24.42,-25.52,-30.25,-26.78,-22.32,-21.74,-14.14,-8.72,-5.66,-4.42,-4.34,-5.75,-7.68,-9.27,-10.56,-12.49,-8.83,-6.74,-5.63,-3.36,0.45,1.32,1.86,0.22,-3.59,-8.36,-14.37,-19.91,-24.39,-28.28,-27.83,-27.22,-25.49,-20.96,-15.99,-10.95,-7.26,-4.65,-4.07,-5.05,-8.07,-11.84,-15.22,-19,-21.02,-21.76,-20.58,-17.83,-14.17,-10,-6.32,-3.62,-2.51,-3.02,-5.28,-8.78,-12.71,-16.45,-19.33,-20.63,-20.35,-18.13,-14.52,-10.03,-5.38,-1.36,1.43,2.44,1.56,-0.84,-4.47,-8.64,-12.52,-15.35,-16.71,-16.27,-14.14,-10.7,-6.53,-2.4,0.93,2.89,3.12,1.5,-1.6,-5.71,-10.13,-14.05,-16.8,-17.95,-17.32,-15.05,-11.6,-7.63,-3.88,-1.1,0.17,-0.34,-2.61,-6.29,-10.78,-15.35,-19.23,-21.79,-22.65,-21.7,-19.18,-15.61,-11.67,-8.13,-5.68,-4.82,-5.74,-8.34,-12.19,-16.65,-20.96,-24.4,-26.38,-26.57,-24.98,-21.9,-17.92,-13.75,-10.16,-7.8,-7.09,-8.16,-10.81,-14.57,-18.75,-22.59,-25.38,-26.6,-26.01,-23.69,-20.01,-15.6,-11.22,-7.6,-5.36,-4.84,-6.1,-8.86,-12.58,-16.55,-20.01,-22.28,-22.92,-21.76,-18.95,-14.95,-10.43,-6.14,-2.82,-1.01,-0.99,-2.74,-5.89,-9.86,-13.9,-17.26,-19.32,-19.7,-18.29,-15.36,-11.39,-7.12,-3.28,-0.58,0.5,-0.25,-2.7,-6.44,-10.81,-15.07,-18.48,-20.46,-20.7,-19.19,-16.24,-12.44,-8.49,-5.18,-3.12,-2.76,-4.22,-7.28,-11.46,-16.08,-20.37,-23.62,-25.32,-25.22,-23.41,-20.26,-16.4,-12.58,-9.53,-7.87,-7.93,-9.76,-13.09,-17.35,-21.83,-25.77,-28.5,-29.57,-28.81,-26.39,-22.76,-18.58,-14.63,-11.61,-10.07,-10.3,-12.24,-15.55,-19.62,-23.71,-27.08,-29.11,-29.39,-27.87,-24.77,-20.62,-16.13,-12.06,-9.1,-7.73,-8.16,-10.25,-13.6,-17.54,-21.34,-24.25,-25.71,-25.41,-23.34,-19.84,-15.48,-10.98,-7.12,-4.53,-3.64,-4.57,-7.11,-10.77,-14.87,-18.65,-21.4,-22.61,-22.05,-19.79,-16.24,-12.02,-7.88,-4.56,-2.66,-2.53,-4.2,-7.39,-11.55,-15.96,-19.86,-22.58,-23.68,-22.98,-20.66,-17.18,-13.21,-9.5,-6.77,-5.57,-6.16,-8.5,-12.22,-16.73,-21.27,-25.1,-27.59,-28.36,-27.33,-24.75,-21.15,-17.21,-13.71,-11.32,-10.54,-11.54,-14.2,-18.1,-22.57,-26.86,-30.25,-32.15</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B188" t="str">
+        <v>[L_10_标记]</v>
+      </c>
+      <c r="C188" t="str">
+        <v>100.6uv</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B189" t="str">
+        <v>[R_11_名字]</v>
+      </c>
+      <c r="C189" t="str">
+        <v>FERG(11)_dMax</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B190" t="str">
+        <v>[R_11_放大器]</v>
+      </c>
+      <c r="C190" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B191" t="str">
+        <v>[R_11_闪光]</v>
+      </c>
+      <c r="C191" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B192" t="str">
+        <v>[R_11_闪光背景]</v>
+      </c>
+      <c r="C192" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B193" t="str">
+        <v>[R_11_采样]</v>
+      </c>
+      <c r="C193" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B194" t="str">
+        <v>[R_11_分析时间]</v>
+      </c>
+      <c r="C194" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B195" t="str">
+        <v>[R_11_数据长度]</v>
+      </c>
+      <c r="C195" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B196" t="str">
+        <v>[R_11_详细数据(uv)]</v>
+      </c>
+      <c r="C196" t="str">
+        <v>-17.65,-17.35,-17.04,-16.72,-16.37,-16.01,-15.65,-15.27,-14.88,-14.49,-14.1,-13.7,-13.31,-12.92,-12.54,-12.17,-11.81,-11.46,-11.13,-10.81,-10.52,-10.24,-9.99,-9.77,-9.56,-9.4,-9.26,-9.15,-9.06,-9.02,-9.02,-9.05,-9.09,-9.2,-9.38,-9.51,-9.78,-10.08,-10.39,-10.84,-11.05,-11.65,-12.35,-12.7,-13.74,-14.16,-14.81,-15.62,-17.71,-17.67,-18.88,-21.41,-22.86,-23.89,-24.54,-28.62,-29.29,-33.13,-35.05,-38.97,-44.38,-45.09,-47.57,-54.22,-52.04,-53.35,-69.94,-72.81,-74.47,-77.18,-74.77,-80.44,-96.22,-93.08,-88.94,-92.79,-107.84,-128.59,-115.82,-137.42,-124.14,-119.14,-142.66,-139.73,-124.6,-134.44,-130.5,-132.12,-104.68,-129.31,-122.46,-130.53,-103.55,-99.49,-87.19,-100.55,-92.11,-89.93,-42.27,-68.09,-30.78,-21.19,-0.06,-9.52,44.58,15.56,53.6,62.45,102,100.21,130.25,161.79,152.51,192.11,247.44,248.11,229.19,252.3,289.18,298.27,296.1,376.91,328.55,404.95,362.12,446.01,482.37,480.31,513.45,470.33,544.68,508.96,569.25,527.89,553.4,604.45,654.47,644.64,643.08,659.87,746.63,623.57,694.19,697.38,711.12,684.87,694.77,680.91,653.44,724.34,689.97,678.44,730.98,787.5,766.06,760.84,726.64,754.91,652.82,776.93,716.87,664.07,692.83,708.52,707.57,658.35,632.67,567.44,654.65,558.67,553.51,545.31,608.52,536.89,537.61,577.1,482.53,478.83,449.32,424.3,430.96,428.03,451.83,431.78,385.2,373.93,383.77,405.58,341.93,324.28,356.95,314.53,324.1,292.93,320.56,310.82,277.13,305.8,241.94,270.01,229.13,219.59,234.35,182.35,191.01,204.63,218.68,222.16,176.54,201.56,165.05,193.56,163.27,140.61,151.26,131.51,135.55,122.59,160.26,157,119.36,116.25,124.56,93.1,146.51,85.8,127.42,105.71,87.36,100.79,82.06,97.58,79.71,100.75,103.03,90.21,68.63,81.02,82.75,65.36,67.19,59.15,43.62,40.89,62.2,59.92,51.72,34.04,34.52,24.58,44.82,20.21,35.04,22.15,30.14,19.99,15.48,23.57,16.1,25.59,20,11.38,20.08,9.12,8.34,11.7,8.72,3.65,0.8,0.74,-2.64,-5.22,1.92,-1.25,-5.43,-2.6,-6.5,-7.85,-11.21,-11.05,-7.11,-14.2,-15.5,-9.59,-21.66,-19.94,-13.41,-25.38,-23.86,-22.11,-21.72,-29.09,-29.94,-28.02,-36.3,-30.65,-35.1,-35.67,-37.43,-41.81,-40.28,-39.46,-39.4,-37.82,-44.2,-51.36,-42.23,-49.02,-46.43,-50.8,-58.81,-45.45,-56.23,-58.69,-62.6,-65.28,-51.53,-61,-51.84,-67.35,-69.13,-60.3,-72.53,-55.27,-66.26,-64.69,-60.8,-67.9,-52.25,-67.5,-67.64,-63.38,-55.57,-75.31,-69.87,-57.78,-54.32,-75.27,-75.18,-74.03,-61.78,-73.85,-60.51,-59.66,-54.19,-66.17,-50.99,-66.08,-71.64,-81.08,-79.43,-50.24,-58.82,-68.81,-82.8,-66.53,-66.66,-63.77,-66.45,-72.88,-67.99,-78.56,-80.54,-84.54,-80.84,-78.48,-65.83,-81.27,-88.57,-89.61,-70.11,-72.56,-92,-65.94,-100.9,-100.33,-79.76,-106.32,-68,-87.7,-81.31,-103.6,-110.26,-92.2,-73.03,-87.24,-111.44,-115.11,-114.36,-102.2,-104.95,-110.81,-115.85,-107.33,-90.95,-89.36,-102.41,-96.66,-113.56,-107.97,-115.25,-100.54,-77.15,-107.78,-110.56,-96.51,-105.79,-84,-105.44,-104.44,-86.45,-105.49,-108.82,-93.32,-76.2,-70.62,-69.82,-94.53,-63.55,-91.95,-71.96,-89.68,-76.3,-61.35,-65.39,-77.72,-87.62,-73.47,-58.93,-71.69,-51.83,-54.97,-53.87,-49.5,-55.11,-54.23,-60.73,-62.18,-58.21,-44.82,-66.78,-60.3,-68.52,-40.73,-55.82,-42.74,-45.75,-52.03,-36.72,-38.82,-40.96,-49.2,-52.35,-47.35,-55.99,-44.22,-51.34,-35.97,-40.18,-38.33,-50.46,-53.93,-56.84,-35.87,-46.7,-38.01,-36.79,-35.9,-53.2,-53.88,-39.9,-41.3,-53.83,-41.5,-37.46,-48.12,-49.33,-45.42,-38.7,-42.88,-48.77,-47.56,-48.64,-43.1,-41.01,-42.77,-35.59,-39.99,-36.38,-40.01,-32.52,-28.23,-31.83,-34.45,-34.18,-25.79,-26.25,-31.71,-26.93,-26.81</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B197" t="str">
+        <v>[R_11_标记]</v>
+      </c>
+      <c r="C197" t="str">
+        <v>a: 33.6ms -186.4uv b: 69.9ms 830.0uv</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B198" t="str">
+        <v>[L_11_名字]</v>
+      </c>
+      <c r="C198" t="str">
+        <v>FERG(11)_dMax</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B199" t="str">
+        <v>[L_11_放大器]</v>
+      </c>
+      <c r="C199" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B200" t="str">
+        <v>[L_11_闪光]</v>
+      </c>
+      <c r="C200" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B201" t="str">
+        <v>[L_11_闪光背景]</v>
+      </c>
+      <c r="C201" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B202" t="str">
+        <v>[L_11_采样]</v>
+      </c>
+      <c r="C202" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B203" t="str">
+        <v>[L_11_分析时间]</v>
+      </c>
+      <c r="C203" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B204" t="str">
+        <v>[L_11_数据长度]</v>
+      </c>
+      <c r="C204" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B205" t="str">
+        <v>[L_11_详细数据(uv)]</v>
+      </c>
+      <c r="C205" t="str">
+        <v>6.71,7.66,8.57,9.43,10.24,10.99,11.69,12.33,12.91,13.44,13.89,14.29,14.62,14.89,15.09,15.23,15.3,15.31,15.25,15.13,14.96,14.72,14.42,14.07,13.66,13.2,12.69,12.13,11.53,10.89,10.2,9.49,8.73,7.95,7.14,6.31,5.45,4.58,3.69,2.79,1.88,0.97,0.07,-0.9,-1.88,-2.76,-3.7,-4.64,-5.59,-6.44,-7.6,-8.51,-9.34,-10.31,-11.43,-11.96,-13,-14.1,-15.57,-16.8,-17.99,-18.36,-20.94,-21.29,-23.97,-24.55,-29.48,-31.1,-31.46,-35.3,-34.36,-36.75,-43.98,-46.35,-49.4,-53.09,-47.03,-55.97,-61.54,-57.15,-69.61,-63.44,-80.52,-70.47,-77.87,-74.79,-81.96,-99.7,-93.56,-109.65,-89.06,-107.51,-102.08,-116.56,-93.11,-116.4,-108.71,-120.95,-119.95,-99.29,-108,-77.39,-92.74,-89.24,-60.03,-66.46,-44.84,-58.94,-38.44,-31.27,-24.69,6.58,-1.72,1.07,34.64,62.7,53.01,85.59,101.37,104.52,137.39,160.59,172.83,220.1,224.86,250,240.4,298.53,249.03,279.67,307.35,322.6,330.49,411.1,451.06,468.99,496.99,467.17,494.05,458.67,539.55,518.26,570.45,509.72,631.74,584.92,639.29,614.47,620.56,607.03,693.7,743.25,680.91,715.71,774.66,666.71,764.25,662.11,656.86,731.63,672.48,767.2,742.69,687.31,660.53,806.76,793.24,738.28,683.96,655,647.97,770.94,704.76,772.63,677.39,748.05,636.41,587.47,607.36,590.34,674.12,578.58,528.46,532.09,644.64,606.4,554.91,538.88,525.92,493.41,485.29,435.07,448.41,418.33,462.26,434.64,360.79,411.94,394.26,356.83,379.14,383.89,344.27,304.15,313.47,285.55,256.46,289.06,275.35,285.8,257.47,285.97,291.16,233.05,270.01,238.51,231.14,247.77,236.99,214.06,206.89,172.73,213.68,199.36,162.69,152.64,203.88,151.02,182.14,161.75,144.83,144.19,141.4,173.03,133.69,161.85,164.92,159.9,157.17,108.27,159.54,129.69,110.93,120.83,100.23,134.58,96.09,121.73,98.87,93.14,106.26,83.96,92.34,76.21,81.01,101.9,94.85,74.91,77.63,68.91,65.24,68.81,54.86,66.73,64.36,65.29,43.23,42.56,44.43,44.37,42.74,28.14,31.9,30.51,33.02,21.79,16.94,19.35,14.68,16.25,11.24,11.72,7.63,7.65,3.04,0.88,-11.8,-9.03,-11.04,-12.07,-13.37,-17.66,-16.67,-22.3,-24.49,-22.79,-24.68,-28.51,-32.38,-34.02,-26.64,-30.24,-34.71,-35.05,-40.23,-44.86,-33.41,-44.32,-43.94,-46.92,-44.01,-37.36,-37.04,-38.74,-47.49,-46.59,-46.96,-51.4,-43.51,-37.87,-46.4,-37.9,-39.36,-40.77,-50.46,-50.42,-38.84,-49.64,-45.78,-51.48,-42.44,-40.62,-41.79,-38.41,-39.9,-40.45,-50.92,-46.99,-31.61,-44.01,-41.36,-49.43,-37.45,-34.95,-42.9,-45.91,-35.64,-29.37,-49.13,-37.61,-28.86,-27.1,-27.21,-45.77,-29.22,-44.12,-46.86,-35.55,-47.6,-48.82,-54.99,-48.39,-40.64,-38.56,-30.43,-46.4,-35.23,-50.83,-36.33,-38.45,-65.04,-59.92,-57.19,-44.67,-59.61,-68.71,-50.07,-59.68,-50.32,-70.2,-73.95,-57.14,-59.41,-82.93,-85.49,-77.96,-66.4,-75.86,-75.77,-76.78,-92.1,-81.74,-73.46,-95.75,-65.76,-97.87,-94.74,-92.88,-89.47,-91.85,-80.21,-76.04,-98.25,-95.94,-98.66,-75.77,-84.9,-111.34,-113.61,-80.61,-94.06,-104.66,-83.28,-108.17,-91.01,-92.65,-104.45,-84.78,-108.54,-80.53,-108.25,-97.97,-93.97,-100.87,-65.25,-96.69,-100.92,-79.2,-68.54,-76.21,-87.64,-79.13,-72.49,-58.45,-84.56,-54.16,-51.33,-74.13,-52.06,-64.97,-51.02,-54.81,-52.08,-56.53,-61.07,-50.47,-44.59,-41.6,-54.29,-38.33,-32.77,-41.66,-51.56,-37.71,-40.18,-21.7,-30.6,-21.89,-45.23,-29.38,-41.35,-27.62,-37.12,-35.98,-28.02,-16.92,-31.82,-19.1,-32.21,-35.46,-13.46,-16.4,-25.37,-25.31,-31.17,-29.47,-16.86,-24.77,-22.57,-13.73,-13.36,-14.99,-20.98,-20.07,-24.17,-27.35,-22.22,-25.85,-15.41,-26.63,-18.24,-21.25,-20,-17.4,-24.16,-24.67,-15.12,-25.75,-24.58,-13.7</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B206" t="str">
+        <v>[L_11_标记]</v>
+      </c>
+      <c r="C206" t="str">
+        <v>a: 33.6ms -188.3uv b: 69.9ms 851.9uv</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B207" t="str">
+        <v>[R_12_名字]</v>
+      </c>
+      <c r="C207" t="str">
+        <v>FERG(12)_dOps</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B208" t="str">
+        <v>[R_12_放大器]</v>
+      </c>
+      <c r="C208" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B209" t="str">
+        <v>[R_12_闪光]</v>
+      </c>
+      <c r="C209" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B210" t="str">
+        <v>[R_12_闪光背景]</v>
+      </c>
+      <c r="C210" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B211" t="str">
+        <v>[R_12_采样]</v>
+      </c>
+      <c r="C211" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B212" t="str">
+        <v>[R_12_分析时间]</v>
+      </c>
+      <c r="C212" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B213" t="str">
+        <v>[R_12_数据长度]</v>
+      </c>
+      <c r="C213" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B214" t="str">
+        <v>[R_12_详细数据(uv)]</v>
+      </c>
+      <c r="C214" t="str">
+        <v>3.71,5.38,4.98,2.37,-1.78,-6.88,-12.16,-16.82,-19.86,-20.63,-19.32,-15.37,-11.33,-6.36,-2.14,0.65,1.33,-0.01,-3.08,-6.78,-10.74,-15.62,-17.66,-17.98,-17.7,-14.52,-11.7,-8.17,-5.79,-5.13,-5.81,-9.91,-14.46,-18.97,-25.6,-29.62,-31.15,-30.16,-27.9,-22.28,-15.22,-7.45,-0.79,4.46,10.67,9.92,10.14,8.61,4.11,-2.45,-5.17,-8.6,-10.68,-10.16,-10.33,-10.25,-12.18,-11.25,-14.15,-18.02,-29.11,-32.75,-31.11,-34.41,-36.23,-26.97,-20.72,-10.94,-0.49,12.94,27.33,37.48,33.7,43.79,37.89,37.23,22.96,10.11,6.96,-6.78,-13.96,-22.49,-28.51,-36.13,-39.81,-37.02,-35.15,-51.22,-46.06,-51,-42.59,-37.27,-32.22,-22.6,-9.32,9.82,23.77,38.35,53.89,49.52,46.99,47.85,41.02,34.09,14.99,-0.29,-17.86,-34.69,-43.83,-52.6,-71.99,-59.11,-68.94,-62.72,-68.96,-59.04,-52.74,-46.32,-39.22,-31.27,-19.01,-7.77,16.3,29.6,41.58,44.72,55.03,64.56,56.25,36.68,27.23,9.32,-8.31,-25.84,-44.21,-55.86,-57.97,-73.02,-65.83,-57.88,-51.75,-60.7,-49.6,-31.5,-22.52,-16.41,-8.46,-1.12,8.7,8.02,14.86,33.61,29.06,42.94,39.47,35.23,30.28,16.8,8.24,-5.81,-18.57,-29.83,-40.19,-51.67,-45.38,-48.01,-41.52,-42.49,-24.67,-21.84,-12.35,-7.09,-2.16,-0.48,1.68,2.7,1.47,2.71,0.96,3.92,3.25,7.21,7.75,6.67,1.74,-2.98,-9.58,-18.22,-26.15,-34.31,-35.96,-39.36,-38.06,-39.25,-31.89,-26.41,-18.74,-12.45,-8.32,-6.65,-7.07,-8.28,-12.8,-15.02,-20.11,-21.63,-23.15,-22,-18.18,-14.81,-12.22,-9.99,-9.17,-10.28,-13.58,-17.49,-22.1,-27.27,-30.93,-31.22,-31.41,-27.68,-23.37,-17.58,-12.07,-7.51,-4.75,-4.3,-5.82,-8.62,-12.99,-17.64,-21.06,-22.9,-22.57,-20.82,-17.04,-12.61,-8.05,-4.42,-2.35,-2.2,-4.03,-7.7,-12.14,-16.53,-20.05,-22.01,-21.85,-19.82,-16.07,-11.44,-6.81,-3.05,-0.95,-0.94,-2.96,-6.67,-11.51,-16.3,-20.41,-22.9,-23.41,-21.88,-18.68,-14.51,-10.23,-6.79,-4.91,-5.03,-7.19,-11.05,-15.92,-20.91,-25.12,-27.77,-28.42,-27.02,-23.9,-19.74,-15.44,-11.88,-9.84,-9.78,-11.78,-15.47,-20.19,-25.07,-29.19,-31.77,-32.35,-30.84,-27.57,-23.21,-18.62,-14.74,-12.31,-11.85,-13.42,-16.72,-21.09,-25.65,-29.5,-31.85,-32.21,-30.49,-26.98,-22.34,-17.45,-13.21,-10.42,-9.58,-10.8,-13.78,-17.9,-22.28,-26,-28.28,-28.61,-26.87,-23.34,-18.66,-13.69,-9.37,-6.47,-5.53,-6.68,-9.64,-13.79,-18.28,-22.18,-24.69,-25.3,-23.84,-20.59,-16.17,-11.44,-7.3,-4.58,-3.81,-5.13,-8.31,-12.73,-17.53,-21.81,-24.73,-25.76,-24.74,-21.89,-17.84,-13.41,-9.53,-7.02,-6.42,-7.92,-11.29,-15.91,-20.96,-25.51,-28.73,-30.06,-29.31,-26.7,-22.81,-18.49,-14.65,-12.11,-11.45,-12.86,-16.13,-20.68,-25.68,-30.2,-33.41,-34.74,-33.96,-31.27,-27.26,-22.74,-18.63,-15.78,-14.77,-15.81,-18.72,-22.94,-27.64,-31.91,-34.89,-36.01,-35.02,-32.1,-27.81,-22.97,-18.5,-15.25,-13.82,-14.45,-16.98,-20.87,-25.3,-29.35,-32.17,-33.17,-32.07,-29.06,-24.65,-19.66,-15.01,-11.56,-9.94,-10.39,-12.78,-16.59,-21.01,-25.13,-28.08,-29.25,-28.36,-25.54,-21.32,-16.49,-11.98,-8.64,-7.11,-7.69,-10.23,-14.24,-18.92,-23.36,-26.69,-28.26,-27.78,-25.37,-21.53,-17.03,-12.8,-9.71,-8.4,-9.18,-11.94,-16.19,-21.16,-25.92,-29.6,-31.53,-31.42,-29.33,-25.76,-21.48,-17.39,-14.38,-13.1,-13.89,-16.65,-20.92,-25.92,-30.74,-34.51,-36.53,-36.48,-34.43,-30.84,-26.46,-22.22,-18.98,-17.43,-17.92,-20.38,-24.36,-29.11,-33.71,-37.28,-39.13,-38.91,-36.65,-32.82,-28.14,-23.55,-19.92,-17.94,-18,-20.04,-23.65,-28.06,-32.39,-35.73,-37.4,-37,-34.58,-30.56,-25.68,-20.83,-16.93,-14.67,-14.45,-16.25,-19.66,-23.96,-28.23,-31.59</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B215" t="str">
+        <v>[R_12_标记]</v>
+      </c>
+      <c r="C215" t="str">
+        <v>95uv</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B216" t="str">
+        <v>[L_12_名字]</v>
+      </c>
+      <c r="C216" t="str">
+        <v>FERG(12)_dOps</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B217" t="str">
+        <v>[L_12_放大器]</v>
+      </c>
+      <c r="C217" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B218" t="str">
+        <v>[L_12_闪光]</v>
+      </c>
+      <c r="C218" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B219" t="str">
+        <v>[L_12_闪光背景]</v>
+      </c>
+      <c r="C219" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B220" t="str">
+        <v>[L_12_采样]</v>
+      </c>
+      <c r="C220" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B221" t="str">
+        <v>[L_12_分析时间]</v>
+      </c>
+      <c r="C221" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B222" t="str">
+        <v>[L_12_数据长度]</v>
+      </c>
+      <c r="C222" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B223" t="str">
+        <v>[L_12_详细数据(uv)]</v>
+      </c>
+      <c r="C223" t="str">
+        <v>-1.24,2.93,6.03,7.93,8.93,7.74,5,0.78,-3.41,-9.18,-14.63,-19.9,-24.36,-27.48,-29.35,-29.89,-29.61,-26.86,-23.6,-20.3,-14.7,-11.02,-6.69,-4.19,-2.37,-2.07,-2.58,-5.02,-6.85,-9.86,-13.79,-19.35,-20.71,-26.1,-27.48,-27.55,-27.67,-27.38,-26.06,-24.72,-22.82,-19.34,-19.6,-20.38,-17.32,-17.54,-19.7,-18.37,-19.6,-20.93,-20.46,-19.64,-18.88,-17.16,-12.83,-10.15,-4.34,2.97,3.38,5.97,7.92,10.39,8.05,4.7,-1.42,-7.78,-15.13,-25.68,-30.33,-42.67,-43.11,-41.97,-44.52,-42.07,-41.05,-30.92,-22.27,-8.96,1.04,19.31,28.04,38.3,51.33,45.93,49.55,43,36.62,25.82,11.07,-4.28,-18.88,-33.02,-48.56,-64.36,-75.85,-70.53,-70.67,-75.63,-57.3,-51.89,-39.34,-27.86,-11.5,2.99,15.63,26.58,32.31,44.62,53.01,52.57,34.4,24.73,22.95,2.38,-11.73,-23.65,-35.33,-45.7,-58.21,-64.29,-78.41,-77.88,-85.36,-71.46,-57.77,-57.28,-48.15,-36.52,-29.04,-18.23,-4.01,6.16,17.67,29.35,16.7,20.05,24.33,42.51,38.12,27.35,20.59,6.96,-5.02,-19.23,-34.46,-43.89,-56.31,-68.28,-65.66,-66.68,-69.57,-66.78,-63.25,-56.95,-38.89,-26.45,-12.61,4.22,22.81,33.05,37.07,48.88,60.81,43.51,49.99,36.33,23.64,14.35,-1.67,-16.17,-32.03,-39.5,-52.22,-62.17,-61.6,-57.31,-57.23,-54.23,-47.02,-34.39,-18.23,-7.77,3.15,10.61,19.97,26.52,25.72,26.71,21.49,9.89,3.94,-6.02,-14.08,-23.8,-29.98,-34.88,-37.85,-41.23,-38.31,-37.28,-37.66,-29.71,-27.55,-23.25,-19.83,-17.25,-17.27,-16.15,-16.5,-17.92,-19.41,-19.16,-20.54,-21.9,-23.31,-25.27,-26.1,-21.66,-20.2,-18.72,-16.41,-14.54,-13.43,-13.15,-11.84,-14.39,-16.3,-18.75,-21.04,-25.61,-27.01,-29.98,-31.82,-32.13,-31.29,-29.32,-25.44,-21.98,-16.5,-11.79,-6.89,-2.8,0.26,2.79,3.27,2.26,0.22,-3.31,-7.61,-12.4,-16.74,-21.33,-24.3,-27.02,-27.68,-26.84,-25.14,-21.65,-17.36,-12.78,-8.21,-3.96,-0.54,1.6,2.34,1.94,-0.17,-3.67,-7.92,-12.83,-17.83,-22.54,-26.47,-29.31,-30.88,-31,-29.76,-27.36,-24.11,-20.24,-16.17,-12.54,-9.59,-7.7,-7.1,-7.88,-10.01,-13.3,-17.48,-22.14,-26.89,-31.27,-34.97,-37.49,-38.7,-38.55,-36.94,-34.18,-30.46,-26.21,-21.82,-17.75,-14.36,-12.04,-10.95,-11.23,-12.82,-15.58,-19.19,-23.3,-27.48,-31.3,-34.35,-36.32,-36.97,-36.21,-34.08,-30.75,-26.51,-21.75,-16.87,-12.33,-8.52,-5.78,-4.33,-4.29,-5.6,-8.12,-11.54,-15.51,-19.59,-23.36,-26.41,-28.42,-29.15,-28.52,-26.56,-23.43,-19.43,-14.92,-10.34,-6.12,-2.66,-0.3,0.74,0.35,-1.43,-4.43,-8.37,-12.88,-17.52,-21.87,-25.53,-28.14,-29.5,-29.48,-28.13,-25.61,-22.2,-18.27,-14.24,-10.55,-7.59,-5.71,-5.12,-5.93,-8.1,-11.47,-15.75,-20.56,-25.49,-30.09,-33.96,-36.75,-38.25,-38.33,-37.04,-34.53,-31.08,-27.06,-22.9,-19.03,-15.85,-13.69,-12.79,-13.25,-15.05,-18,-21.85,-26.2,-30.65,-34.76,-38.12,-40.39,-41.34,-40.88,-39.02,-35.94,-31.91,-27.3,-22.55,-18.08,-14.3,-11.55,-10.08,-9.97,-11.22,-13.66,-17.02,-20.92,-24.95,-28.67,-31.68,-33.65,-34.34,-33.65,-31.6,-28.36,-24.22,-19.53,-14.72,-10.24,-6.49,-3.8,-2.43,-2.47,-3.9,-6.56,-10.19,-14.4,-18.78,-22.9,-26.34,-28.77,-29.95,-29.78,-28.27,-25.59,-22.01,-17.89,-13.67,-9.76,-6.59,-4.48,-3.68,-4.29,-6.28,-9.51,-13.68,-18.43,-23.34,-27.97,-31.91,-34.82,-36.45,-36.7,-35.58,-33.25,-29.97,-26.12,-22.12,-18.39,-15.34,-13.31,-12.54,-13.15,-15.09,-18.23,-22.28,-26.87,-31.59,-36,-39.68,-42.3,-43.61,-43.5,-41.99,-39.24,-35.51,-31.17,-26.65,-22.38,-18.77,-16.16,-14.79,-14.79,-16.12,-18.64,-22.09,-26.08,-30.22,-34.05,-37.18,-39.27,-40.07,-39.47,-37.49,-34.29,-30.14,-25.41</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B224" t="str">
+        <v>[L_12_标记]</v>
+      </c>
+      <c r="C224" t="str">
+        <v>103.5uv</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B225" t="str">
+        <v>[R_13_名字]</v>
+      </c>
+      <c r="C225" t="str">
+        <v>FERG(13)_dMax</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B226" t="str">
+        <v>[R_13_放大器]</v>
+      </c>
+      <c r="C226" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B227" t="str">
+        <v>[R_13_闪光]</v>
+      </c>
+      <c r="C227" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B228" t="str">
+        <v>[R_13_闪光背景]</v>
+      </c>
+      <c r="C228" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B229" t="str">
+        <v>[R_13_采样]</v>
+      </c>
+      <c r="C229" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B230" t="str">
+        <v>[R_13_分析时间]</v>
+      </c>
+      <c r="C230" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B231" t="str">
+        <v>[R_13_数据长度]</v>
+      </c>
+      <c r="C231" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B232" t="str">
+        <v>[R_13_详细数据(uv)]</v>
+      </c>
+      <c r="C232" t="str">
+        <v>-4.59,0.82,0.63,-5.22,-13.18,-18.39,-17.69,-11.65,-4.2,-0.16,-2.16,-9.03,-16.5,-19.9,-17.14,-9.98,-2.96,-0.52,-4.17,-11.6,-18.06,-19.44,-14.78,-6.96,-0.82,-0.13,-5.22,-12.74,-17.82,-17.1,-10.89,-2.94,1.88,0.71,-5.53,-12.74,-16.17,-13.48,-6.19,1.3,4.37,1.33,-5.76,-12.3,-14.06,-9.64,-1.84,4.39,5.4,0.52,-7.23,-12.75,-13.32,-7.74,0.04,3.92,2.89,-5.07,-12.97,-17.06,-15.96,-10.61,-7.02,-2.42,-9.97,-18.84,-27.29,-32.6,-35.6,-30.9,-21.94,-27.11,-35.77,-46.24,-54.91,-68.65,-59.7,-54.57,-65.26,-62.2,-86.88,-87.23,-90.78,-106.91,-100.64,-89.08,-95.25,-128.89,-109.47,-132.22,-159.79,-122.84,-150.13,-126.13,-132.17,-121.93,-157.09,-145.11,-121.29,-115.7,-96.35,-128.56,-122.26,-84.9,-74.72,-97.06,-82.3,-67.35,-35.13,-16.02,-13.21,21.3,-2.18,-2.67,49.33,75.75,121.48,132.43,116.47,165.4,145.83,216.14,201.3,267.34,245.11,263.24,325.02,296.65,324.59,409.78,434.12,373.17,493.76,442.23,472.99,529.58,575.77,541.61,536.25,574.68,663.52,626.56,650.72,615.58,692.99,703.67,699.48,734.11,801.61,843.26,729.72,692.41,865.97,832.68,814.61,860.72,763.3,758.86,739.01,760.69,860.42,760.97,745.04,877.31,767.62,727.02,708.7,770.43,767.32,803.87,812.8,691.76,770.78,692.03,730.42,747.06,710.69,614.3,679.08,593.21,644.55,600.16,586.77,605.07,601.61,564.94,510.61,540.82,450.71,453.45,449.7,440.05,397.12,386.09,401.27,393.34,360.71,360.9,373.52,309.75,328.39,345.19,286.59,319.2,279.35,241.74,270.01,245.4,265.43,283.85,235.57,234.13,201.28,194.01,215.5,220.31,218.18,215.83,192.51,196.95,192.51,191.66,169.86,214.29,154.27,209.15,155.63,155.43,178.47,167.11,166.86,183.81,159.06,169.86,137.48,155.89,110.72,134.92,95.16,141.29,127.5,123.32,102.12,91.92,68.59,64.7,101.73,86.74,111.57,83.44,77.76,48.31,65.84,54.6,63.19,78.68,64.26,45.84,51.29,33.21,36.78,23.59,37.56,42.95,30.95,14.95,5.96,7.41,8.68,10.82,15,8.15,4.01,-7.26,-15.27,-13.97,-8.16,-5.37,0.72,-4.48,-15.76,-16.77,-21.49,-28.8,-17.76,-8.13,-14.05,-15.73,-30.52,-36.58,-34.7,-27.73,-25.08,-22.36,-26.97,-22.16,-30.9,-44.04,-43.42,-36.74,-33.86,-19.27,-20.11,-29.6,-44.79,-43.77,-51.84,-32.09,-29.93,-27.25,-38.1,-46.84,-53.19,-54.03,-41.57,-51.81,-45.47,-39.55,-35.12,-42.07,-58.81,-59.34,-57.91,-52.76,-47.88,-45.88,-41.54,-66.14,-63.34,-74.01,-61.28,-40.24,-39.76,-56.11,-69.53,-67.42,-73.57,-63.12,-67.59,-52.54,-71.54,-76.48,-85.4,-85.45,-74.31,-92.36,-86.04,-55.74,-54.73,-87.53,-89.32,-91.73,-97.79,-87.7,-71.5,-89.36,-65.51,-78.43,-104.52,-90.34,-94.62,-101.07,-95.56,-101.96,-97.8,-90.11,-116.89,-85.6,-93.46,-86.89,-106.8,-101.7,-98.31,-98.12,-96.38,-117.8,-83.64,-93.16,-101.91,-89.32,-77.36,-128.96,-130.93,-115.74,-98.47,-75.06,-100.8,-111.73,-107.07,-127.76,-109.54,-111.77,-93.99,-75.41,-101.06,-75.51,-93.72,-120.95,-114.77,-119.65,-84.29,-73.24,-72.66,-112.64,-102.58,-84.79,-110.08,-120.51,-111.03,-67.32,-74.16,-94.1,-91.88,-89.57,-108.95,-74.54,-83.48,-102.41,-92.65,-101.9,-121.09,-102.73,-78.71,-88.33,-65.76,-102.6,-92.5,-88.81,-82.11,-80.99,-106.21,-101.22,-85.01,-71.64,-105.26,-98.78,-113.38,-110.36,-90.28,-79.12,-81.74,-87.16,-92.55,-77.57,-75.15,-91.2,-62.9,-64.94,-60.11,-61.69,-80.26,-80.87,-72.68,-83.74,-79.32,-67.45,-79.2,-67.54,-71.94,-71.44,-74.09,-63.05,-49.27,-63.52,-63.07,-59.33,-70.35,-69.62,-72.02,-48.66,-59.03,-61.23,-57.06,-64.33,-72.78,-66.78,-66.76,-56.57,-50.5,-32.37,-45.45,-48.94,-53.29,-58.81,-37.28,-45.24,-32.78,-36.21,-45.38,-46.5,-51.1,-37.54,-38.28,-25.04,-18.83,-34.72,-41.82,-35.58,-43.19,-33.85</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B233" t="str">
+        <v>[R_13_标记]</v>
+      </c>
+      <c r="C233" t="str">
+        <v>a: 37.3ms -228.7uv b: 77.4ms 1070.0uv</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B234" t="str">
+        <v>[L_13_名字]</v>
+      </c>
+      <c r="C234" t="str">
+        <v>FERG(13)_dMax</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B235" t="str">
+        <v>[L_13_放大器]</v>
+      </c>
+      <c r="C235" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B236" t="str">
+        <v>[L_13_闪光]</v>
+      </c>
+      <c r="C236" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B237" t="str">
+        <v>[L_13_闪光背景]</v>
+      </c>
+      <c r="C237" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B238" t="str">
+        <v>[L_13_采样]</v>
+      </c>
+      <c r="C238" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B239" t="str">
+        <v>[L_13_分析时间]</v>
+      </c>
+      <c r="C239" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B240" t="str">
+        <v>[L_13_数据长度]</v>
+      </c>
+      <c r="C240" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B241" t="str">
+        <v>[L_13_详细数据(uv)]</v>
+      </c>
+      <c r="C241" t="str">
+        <v>-35.24,-32.97,-27.18,-20.61,-16.33,-16.39,-20.88,-27.89,-34.37,-37.51,-35.98,-30.57,-23.77,-18.73,-17.76,-21.36,-27.95,-34.59,-38.33,-37.49,-32.46,-25.48,-19.69,-17.65,-20.24,-26.25,-32.92,-37.17,-37.02,-32.44,-25.4,-18.96,-15.9,-17.48,-22.87,-29.49,-34.26,-34.86,-30.89,-23.99,-17.14,-13.19,-13.86,-18.66,-25.36,-30.61,-32.15,-29.07,-22.73,-15.68,-11.41,-11.38,-15.8,-22.85,-28.67,-32.08,-29.54,-24.59,-17.92,-14.37,-13.64,-19.78,-27.23,-33.06,-38.99,-42.08,-37.74,-34.36,-29.94,-31.12,-38.53,-49.11,-59.62,-64.12,-71.32,-73.4,-60.82,-70.97,-58.05,-81.15,-85.22,-109.23,-97.1,-117.25,-115.98,-112.62,-121.35,-127.82,-131.63,-149.65,-143.38,-156.19,-140.58,-147.76,-160.39,-151.42,-155.83,-128.5,-172.11,-134.64,-144.43,-134.32,-145.4,-141.92,-106.08,-122.13,-84.58,-101.04,-75.17,-84.1,-62.65,-42.39,-41.45,3.4,28.63,6.36,66.89,87.49,78.52,129.03,98.6,166.02,178.13,190.11,246.85,216.33,234.49,235.08,327.56,301.93,381.46,361.08,419.54,402.94,494.7,498.37,527.04,481.25,562.07,497.29,601.69,543.72,669.77,601.65,649.4,604.18,611.51,674.39,736.89,723.41,798.44,710,814.36,867.65,688.84,750.39,801.37,857.8,832.93,859.18,731.07,783.18,734.65,827.41,818.01,785.04,810.99,863.61,817.05,844.19,866.49,857.44,801.9,708.34,802.33,660.17,654.83,640.01,628.9,663.86,621.71,617.54,609.03,586.46,545.37,518.29,514.96,519.38,585.16,486.01,438.66,496.86,459.23,446.18,396.83,416.26,424.32,394.86,401.23,388.85,314.33,284.31,291.42,300.18,308.55,295.84,326.87,298.94,236.22,263.55,252.57,220.99,196.73,236.18,206.13,221.64,235.18,209.85,210.41,162.46,170.91,196.52,155.64,177.74,164.63,147.07,183.56,151.21,135.38,167.78,156.69,146.58,172.13,137.77,130.16,154.4,128.52,125.24,137.81,92.15,112.01,92.88,121.47,87.56,90.59,112.44,79.59,57,63.31,90.05,58.42,55.79,88.39,82.17,79.81,62.93,59.72,36.28,45.49,34.78,51.41,39.89,45.87,41.64,30.67,16.54,6.12,-0.66,-2.91,15.93,9.95,11.33,11.28,2.47,-10.95,-21.69,-15.73,-22.27,-6.7,-6.59,-3.4,-9,-19.19,-29.17,-32.55,-37.32,-37.53,-26.79,-21.31,-20.51,-20.11,-30.98,-32.99,-47.1,-41.74,-43.15,-37.44,-29.15,-32.16,-23.13,-33.54,-41.47,-49.86,-45.18,-53.78,-51.81,-36.8,-37.69,-28.84,-35.58,-50.19,-49.85,-61.78,-53.38,-60.37,-53.34,-40.14,-39.77,-35.73,-38.85,-64.29,-70.38,-71.22,-53.52,-43.76,-50.29,-34.84,-50.24,-65.52,-67.48,-73.38,-77.74,-69.43,-55.35,-48.06,-50.66,-56.58,-55.49,-78.04,-82.47,-64.94,-77.3,-60.79,-52.91,-47,-54.99,-83.22,-83.3,-80.06,-83.64,-77.08,-92.53,-83.16,-85.43,-66,-94.05,-77.1,-75.93,-114.53,-96.62,-76.33,-77.61,-83.35,-91.33,-97.03,-82.18,-92.65,-116.14,-110.27,-104.03,-90.65,-111.55,-79.45,-79.5,-77.17,-115.49,-130.01,-121.83,-100.45,-88.84,-117.17,-86.18,-116.44,-106.47,-116.08,-115.27,-134.44,-92.06,-122.75,-88.95,-111.38,-104.08,-109.55,-124.44,-129.73,-92.61,-89.01,-118.77,-76.11,-100.32,-109.93,-102.09,-115.09,-90.42,-89.99,-112.14,-92.19,-88.37,-84,-69.64,-94.9,-111.37,-97.36,-94.87,-88.49,-98.58,-113.13,-67.39,-65.13,-107.1,-71.34,-96.02,-123.62,-115.55,-110.24,-94.39,-103.94,-94.49,-93.83,-89.97,-108.01,-106,-96.38,-109.34,-100.33,-81.57,-62.13,-69.91,-67.28,-101.16,-83.34,-83.98,-78.93,-67.02,-90.25,-82.47,-66.52,-78.67,-66.06,-96.35,-90.08,-99.33,-78.68,-78.02,-53.17,-62.36,-57.71,-63.35,-79.6,-89.11,-82.62,-83.17,-53.73,-48.59,-42.99,-69.04,-72.97,-70.61,-74.93,-62.7,-62.96,-66.5,-63.61,-37.25,-55.09,-47.27,-58.73,-71.25,-66.78,-51.97,-59.98,-40.5,-29.14,-34.93,-34.21,-54.26,-55.82,-53.64,-44.01,-41.68,-27.87,-29.56,-20.49,-36.02,-42.2,-34.72,-41.46,-34.2,-27.97,-20.93</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B242" t="str">
+        <v>[L_13_标记]</v>
+      </c>
+      <c r="C242" t="str">
+        <v>a: 37.3ms -229.5uv b: 77.6ms 1043.0uv</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B243" t="str">
+        <v>[R_14_名字]</v>
+      </c>
+      <c r="C243" t="str">
+        <v>FERG(14)_dOps</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B244" t="str">
+        <v>[R_14_放大器]</v>
+      </c>
+      <c r="C244" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B245" t="str">
+        <v>[R_14_闪光]</v>
+      </c>
+      <c r="C245" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B246" t="str">
+        <v>[R_14_闪光背景]</v>
+      </c>
+      <c r="C246" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B247" t="str">
+        <v>[R_14_采样]</v>
+      </c>
+      <c r="C247" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B248" t="str">
+        <v>[R_14_分析时间]</v>
+      </c>
+      <c r="C248" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B249" t="str">
+        <v>[R_14_数据长度]</v>
+      </c>
+      <c r="C249" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B250" t="str">
+        <v>[R_14_详细数据(uv)]</v>
+      </c>
+      <c r="C250" t="str">
+        <v>-11.84,-4.47,4.17,3.95,-5.11,-11.43,-7.26,2.12,4.81,-2.99,-11.66,-10.81,-2.27,2.99,-1.95,-12.18,-14.37,-6.18,2.62,0.56,-7.56,-11.87,-5.07,5.43,7.93,1.42,-5.01,-1.41,10.65,14.66,8.56,-0.06,-1.51,7.92,13.48,8.69,-2.77,-8.16,-4.31,2.9,-0.26,-10,-15.16,-13.36,-5.62,0.08,-6.58,-11.13,-8,4.45,14.61,13.3,5.25,5.68,15.16,25.66,24.65,14.92,10.36,14.32,17.55,14.7,1.11,-12.71,-17.93,-14.8,-15.12,-20.99,-33.15,-41.02,-28.28,-16.33,-22.13,-25.39,-21.06,-9.05,8.09,18.41,19.26,12.59,26.75,41.17,44.3,30.17,28.98,18.83,21.32,16.01,3.14,-17.36,-32.89,-31.02,-35.97,-48.99,-55.68,-69.23,-59.71,-42.42,-36.91,-31.65,-29.88,-17.75,3.31,26.15,29.26,29.75,32.39,51.95,66.46,72.7,45.48,37.85,29.4,30.72,17.56,-6.89,-30.39,-45.09,-48.95,-49.81,-55.81,-69.52,-78.22,-71.38,-52.43,-34.42,-36.6,-19.83,2.09,23.68,43.84,48.2,46.22,67.66,67.95,85.29,70.42,44.27,40.09,32.72,23.93,4.66,-22.14,-32.28,-46.1,-42.55,-62.64,-68.37,-78.5,-67.54,-50.55,-36.15,-31.82,-23.7,-9.94,14.53,30.48,31.2,38.08,45.5,58.43,58.78,45.97,33.08,19.22,23.45,14.2,4.65,-16.1,-34.14,-36.76,-32.14,-38,-42.8,-62.15,-57.58,-39.28,-32.04,-25.4,-22.72,-18.53,-1.86,13.31,16.86,16.7,13.17,23.07,26.79,34.46,21.87,4.13,4.98,8.2,7.17,-4.98,-19.26,-24.32,-19.45,-16.45,-17.59,-25.18,-28.31,-24.49,-8.42,-5.16,-10.55,-12.84,-5.31,7.71,16.24,10.25,4.54,6.42,13.41,21.27,14.06,4.57,-0.5,3.69,9.71,6.49,-4.6,-11.89,-10.64,-1.64,0.75,-5.32,-14.45,-12.23,-1.66,3.81,0.19,-7.55,-8.68,0.28,9.09,7.89,-1.5,-7.03,-1.07,7,8.47,-0.92,-9.27,-7.71,0.65,4.26,-2.74,-12.67,-14.03,-5.73,0.82,-2.73,-12.4,-16.15,-9.53,-0.85,-0.48,-9.22,-15.66,-11.75,-2.07,1.25,-5.69,-14.33,-13.86,-4.67,1.22,-3.32,-12.95,-15.58,-8.26,-0.07,-1.4,-10.59,-16.12,-11.05,-1.51,0.62,-7.01,-14.73,-12.45,-2.81,2.46,-2.82,-11.73,-12.71,-4.19,3.54,1.18,-8,-12.17,-5.77,3.5,4.3,-4.03,-10.84,-7.32,2.35,6.33,-0.14,-8.76,-8.53,0.44,7.09,3.26,-6.13,-9.2,-2.03,6.5,5.76,-3.29,-9.33,-4.82,4.55,6.98,-0.67,-8.94,-7.64,1.45,6.76,1.44,-8.09,-10.14,-2.42,5.13,2.77,-6.86,-12.03,-6.59,2.3,3.19,-5.39,-13.05,-10.56,-1.39,2.64,-3.87,-13.11,-13.86,-5.51,1.18,-2.48,-12.2,-16.1,-9.57,-1.03,-1.4,-10.43,-17.01,-13.08,-3.7,-0.74,-8.01,-16.49,-15.63,-6.54,-0.61,-5.24,-14.6,-16.92,-9.21,-1.01,-2.45,-11.58,-16.8,-11.39,-1.91,0.01,-7.8,-15.3,-12.84,-3.21,1.82,-3.73,-12.62,-13.4,-4.78,2.77,0.14,-9.07,-13.02,-6.44,2.73,3.32,-5.12,-11.75,-8.01,1.68,5.42,-1.23,-9.76,-9.3,-0.27,6.18,2.1,-7.31,-10.19,-2.88,5.5,4.48,-4.69,-10.57,-5.87,3.44,5.6,-2.23,-10.4,-8.87,0.25,5.33,-0.22,-9.72,-11.54,-3.7,3.69,1.08,-8.6,-13.56,-7.94,0.89,1.52,-7.18,-14.68,-11.95,-2.75,1.05,-5.63,-14.78,-15.27,-6.8,-0.27,-4.15,-13.85,-17.49,-10.76,-2.3,-2.9,-11.99,-18.36,-14.18,-4.79,-2.04,-9.43,-17.77,-16.63,-7.45,-1.68,-6.5,-15.8,-17.85,-9.96,-1.87,-3.53,-12.69,-17.69,-12.05,-2.6,-0.91,-8.84,-16.18,-13.46,-3.79,1.04,-4.7,-13.51,-14.05,-5.32,2.08,-0.8,-10.03,-13.76,-7.01,2.06,2.39,-6.16,-12.63,-8.68,0.98,4.47,-2.38,-10.83,-10.14,-1.05,5.18,0.85,-8.56,-11.24,-3.8,4.43,3.13,-6.13,-11.83,-6.95,2.29,4.18,-3.81,-11.88,-10.13,-0.98</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B251" t="str">
+        <v>[R_14_标记]</v>
+      </c>
+      <c r="C251" t="str">
+        <v>106uv</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B252" t="str">
+        <v>[L_14_名字]</v>
+      </c>
+      <c r="C252" t="str">
+        <v>FERG(14)_dOps</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B253" t="str">
+        <v>[L_14_放大器]</v>
+      </c>
+      <c r="C253" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B254" t="str">
+        <v>[L_14_闪光]</v>
+      </c>
+      <c r="C254" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B255" t="str">
+        <v>[L_14_闪光背景]</v>
+      </c>
+      <c r="C255" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B256" t="str">
+        <v>[L_14_采样]</v>
+      </c>
+      <c r="C256" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B257" t="str">
+        <v>[L_14_分析时间]</v>
+      </c>
+      <c r="C257" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B258" t="str">
+        <v>[L_14_数据长度]</v>
+      </c>
+      <c r="C258" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B259" t="str">
+        <v>[L_14_详细数据(uv)]</v>
+      </c>
+      <c r="C259" t="str">
+        <v>3.82,0.57,2.7,7.67,10.17,7.11,1.75,-1.5,1.55,6.56,9.41,6.72,2.02,0.03,3.52,9.5,12.94,10.49,5.95,4.36,7.89,12.79,16.08,11.93,6.95,3.83,5.9,10.13,10.98,6.65,-0.93,-2.6,-1.1,2.8,5.63,1.33,-0.95,-1.78,2.62,10.3,14.09,12.78,10.38,10.74,16.77,27.02,26.43,24.66,18.54,15.74,20.36,20.36,18.16,10.57,1.37,-6.01,-7.96,-3.73,-3.84,-11.78,-16.62,-23.83,-16.39,-5.26,0.83,-1.22,1.61,7.15,18.25,30.77,40.37,43.81,38.75,43.33,36.57,43.98,42.28,28.27,15.94,3.44,-3.03,-9.9,-15.76,-32.48,-51.25,-51.95,-51.81,-44.4,-44.14,-38.5,-29.02,-18.94,-2.3,15.8,28.84,35.2,35.85,42.77,67.61,59.26,57.91,65.83,42.85,39.37,29.67,16.82,1.06,-18.72,-37.37,-43.69,-52.77,-57.77,-54.08,-55.5,-57.81,-58.04,-35.49,-19.03,-1.87,7.86,18.5,35.17,62.96,65.2,75.69,71.75,74.56,54.57,72.09,57.56,38.35,19.76,-1.24,-12.72,-29.5,-36.23,-48.35,-58.02,-64.51,-50.78,-56.04,-30.41,-27.23,-21.99,-11.71,3.05,22.77,36.97,41.31,47.26,42.26,51.29,53.71,59.29,52.92,37.42,23.85,13.76,7.89,0.15,-14.77,-23.38,-37.35,-39.32,-33.11,-34.67,-32.44,-26.88,-28.81,-19.5,-4.23,4.73,9.11,12.22,14.03,21.53,24.25,35.67,24.47,17.67,13.13,13.36,17.53,13.07,4.6,-5.7,-10.75,-10.75,-8.81,-7.35,-10.86,-16.13,-16.61,-11.53,-4.53,-0.2,-1.3,-3.84,-2.42,4.13,11.69,13.54,10.72,7.04,4.28,7.38,12.14,12.55,7.49,1.38,-1.33,1.44,5.16,5.65,1.12,-3.86,-5.27,-1.92,4.29,5.59,2.43,-2.28,-2.19,2.79,8.41,9.53,5.6,1.29,0.78,5.16,9.9,10.53,5.75,0.48,-0.38,3.88,8.1,7.85,2.93,-2.04,-2.56,1.81,6.18,6.23,1.45,-3.32,-3.25,1.37,5.79,5.43,0.62,-3.92,-3.74,0.96,5.19,4.54,-0.48,-5.03,-4.64,0,4.07,3.23,-1.88,-6.25,-5.64,-0.82,3.19,2.22,-2.87,-7,-6.05,-1.07,2.91,1.82,-3.25,-7.15,-5.93,-0.8,3.1,1.85,-3.21,-6.91,-5.43,-0.2,3.6,2.19,-2.88,-6.39,-4.67,0.66,4.33,2.76,-2.33,-5.65,-3.71,1.68,5.2,3.43,-1.7,-4.86,-2.72,2.68,6,4,-1.18,-4.21,-1.92,3.46,6.56,4.32,-0.95,-3.86,-1.43,3.9,6.75,4.25,-1.1,-3.89,-1.35,3.91,6.51,3.75,-1.66,-4.35,-1.69,3.51,5.86,2.85,-2.62,-5.16,-2.38,2.76,4.87,1.64,-3.85,-6.23,-3.3,1.8,3.7,0.28,-5.19,-7.39,-4.28,0.79,2.5,-1.06,-6.48,-8.45,-5.14,-0.07,1.48,-2.21,-7.54,-9.25,-5.73,-0.65,0.76,-3.02,-8.24,-9.68,-5.94,-0.84,0.43,-3.43,-8.51,-9.67,-5.71,-0.6,0.53,-3.41,-8.37,-9.25,-5.09,0,0.97,-3.05,-7.89,-8.52,-4.19,0.86,1.65,-2.48,-7.21,-7.62,-3.15,1.82,2.4,-1.87,-6.52,-6.73,-2.15,2.69,3.03,-1.39,-5.98,-6.02,-1.38,3.32,3.38,-1.2,-5.75,-5.63,-0.95,3.57,3.35,-1.41,-5.91,-5.65,-0.94,3.39,2.88,-2.04,-6.49,-6.09,-1.35,2.79,2.01,-3.05,-7.43,-6.86,-2.09,1.88,0.85,-4.33,-8.61,-7.85,-3.03,0.79,-0.47,-5.72,-9.86,-8.89,-3.99,-0.3,-1.74,-7.04,-11,-9.79,-4.79,-1.21,-2.82,-8.12,-11.87,-10.4,-5.29,-1.81,-3.55,-8.83,-12.36,-10.61,-5.39,-2,-3.87,-9.12,-12.41,-10.39,-5.07,-1.78,-3.79,-9,-12.06,-9.78,-4.38,-1.21,-3.37,-8.55,-11.4,-8.89,-3.44,-0.42,-2.75,-7.93,-10.58,-7.88,-2.42,0.41,-2.11,-7.31,-9.79,-6.93,-1.5,1.12,-1.63,-6.86,-9.2,-6.2,-0.83,1.53,-1.45,-6.73,-8.94,-5.83,-0.55,1.56,-1.67,-7,-9.08,-5.88,-0.69,1.14</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B260" t="str">
+        <v>[L_14_标记]</v>
+      </c>
+      <c r="C260" t="str">
+        <v>110.1uv</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B261" t="str">
+        <v>[R_15_名字]</v>
+      </c>
+      <c r="C261" t="str">
+        <v>FERG(15)_dMax</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B262" t="str">
+        <v>[R_15_放大器]</v>
+      </c>
+      <c r="C262" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B263" t="str">
+        <v>[R_15_闪光]</v>
+      </c>
+      <c r="C263" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B264" t="str">
+        <v>[R_15_闪光背景]</v>
+      </c>
+      <c r="C264" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B265" t="str">
+        <v>[R_15_采样]</v>
+      </c>
+      <c r="C265" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B266" t="str">
+        <v>[R_15_分析时间]</v>
+      </c>
+      <c r="C266" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B267" t="str">
+        <v>[R_15_数据长度]</v>
+      </c>
+      <c r="C267" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B268" t="str">
+        <v>[R_15_详细数据(uv)]</v>
+      </c>
+      <c r="C268" t="str">
+        <v>-8.28,-24.43,-14.17,3.05,-5.92,-22.53,-13.15,4.61,-3.39,-20.45,-12.01,6.21,-0.82,-18.32,-10.87,7.71,1.63,-16.28,-9.88,8.98,3.84,-14.46,-9.16,9.9,5.69,-12.97,-8.81,10.37,7.08,-11.9,-8.9,10.33,7.97,-11.28,-9.46,9.76,8.33,-11.14,-10.5,8.67,8.17,-11.45,-11.98,7.07,7.53,-12.19,-13.89,5.02,6.41,-13.24,-16.17,2.48,4.91,-14.84,-18.96,-0.55,2.38,-17.23,-22.69,-4.68,-0.35,-19.9,-27.34,-10.75,-5.19,-26.1,-32.3,-17.35,-14.63,-31.31,-45.72,-31.11,-24.87,-45.68,-56.57,-45.15,-32.55,-60.71,-74.89,-68.96,-62.43,-87.28,-93.67,-79.59,-86.1,-89.52,-115.76,-113.71,-85.59,-104.59,-132.65,-104.32,-98.75,-126.72,-139.01,-156.21,-105.46,-155.07,-148.2,-141.33,-134.26,-147.01,-142.05,-129.51,-104.08,-105.45,-133.16,-102.11,-68.42,-39.72,-44.57,-20.59,16.52,-13.24,-5.53,13.93,60.74,59.81,72.98,100.9,102.61,144.63,123.7,161.73,190.71,231.39,236.44,241.14,275.8,296.81,297.12,285.49,389.65,350.1,403.94,398.61,425.1,433.12,453.82,442.14,581,600.14,513.62,512.79,588.58,629.77,571.72,587.08,587.52,628.49,641.94,678.83,670.8,689.02,668.62,692.81,831.03,793.17,750.52,655.54,710.72,711.79,714.44,691.34,848.77,698.17,764.88,779.92,683.16,796.38,688.24,754.33,713.27,621.55,667.16,594.99,690.31,709.48,565.63,541.56,556.63,556.63,581.78,526.4,474.96,545.6,466.27,490.14,429.33,472.44,448.18,429.41,355.83,406.52,373.07,357.35,369.02,360.49,295.64,261.16,269.74,313.88,289.45,220.42,291.38,270.71,273.52,190.9,232.68,244.46,218.78,174.39,216.13,229.15,206.86,159.81,192.63,164.6,174.68,180.66,187.3,199.73,179.81,152.43,165.01,157.8,148.68,113.5,165.09,184.18,165.84,149.05,139.68,119.34,102.89,109.94,145.04,110.4,105.89,97.1,83.18,126.35,81.02,98.34,65.47,107.49,100.3,52.07,67.34,82.22,80.49,70.29,42.9,74.35,81.3,41.32,47.99,69.75,49.81,19.55,38.84,47.72,40.87,27.93,13.75,35.3,29.91,15.14,5.72,31.92,21.01,9.76,0.6,23.26,25.64,1.79,-0.34,20.46,12.38,-6.81,-3.81,6.94,6.11,-10.6,-15.09,6.77,3.08,-8.47,-16.92,-1.24,7.95,-15.01,-23.4,-0.86,2.9,-17.78,-25.22,-8.62,3.35,-14.13,-32.59,-12.52,-3.39,-23.78,-30.16,-15.14,-15.64,-31.5,-41.85,-14.85,-19.99,-27,-49.97,-35.51,-20.22,-43.33,-46.29,-24.93,-20.99,-38.11,-50.29,-47.13,-32.52,-48.73,-55.76,-51.61,-41.32,-46.19,-55.84,-40.78,-32.41,-58.68,-59.88,-47.9,-43.63,-60.31,-71.03,-58.79,-49.01,-48.51,-69.62,-76.53,-37.02,-69.74,-66.95,-58.29,-48.17,-49.26,-70.99,-68.51,-62.04,-62.28,-95.74,-59.58,-57.71,-52.76,-83.54,-59.9,-63.44,-60.15,-68.23,-87.8,-44.23,-74.08,-87.41,-71.72,-44.03,-58.1,-85.54,-96.77,-69.67,-66.25,-98.93,-62.94,-70.38,-48.99,-87.39,-66.25,-59.26,-81.33,-78.69,-78.57,-45.95,-74.43,-91.57,-105.73,-58.17,-72.72,-85.21,-103.35,-78.58,-57.32,-83.65,-93.79,-74.53,-77.86,-77.79,-105.31,-92.97,-73.85,-77.84,-112.81,-59.63,-89.05,-69.23,-109.79,-90.28,-88.1,-89.14,-86.88,-76.01,-71.42,-101.79,-88.73,-66.97,-68.19,-93.78,-98.44,-62.5,-72.81,-107.62,-82.06,-73.01,-76.44,-82.11,-80.64,-62.49,-85.94,-88.09,-92.13,-89.19,-75.67,-87.54,-82.42,-75.1,-43.83,-84.88,-82.93,-79.76,-52.37,-60.11,-86.02,-61.71,-65.74,-51.11,-85.33,-54.8,-35.25,-56.98,-80.53,-66.93,-34.12,-54.52,-73.13,-50.31,-25.5,-63.8,-63.45,-60.11,-28.63,-35.59,-64.28,-45,-17.32,-44.03,-59.54,-53.17,-37.56,-44.85,-39.56,-47.78,-27.23,-20.22,-56.25,-32.9,-18.55,-34.88,-41.95,-42.56,-17.62,-19.62,-43.96,-42.94,-11.92,-27,-40.73,-39.38,-15.26,-16.22,-31.7,-29.47,-14.69,-17.78,-34.81,-38.49,-13.55,-8.03,-37.88,-30.16,-14.98</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B269" t="str">
+        <v>[R_15_标记]</v>
+      </c>
+      <c r="C269" t="str">
+        <v>a: 40.9ms -222.8uv b: 84.2ms 939.8uv</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B270" t="str">
+        <v>[L_15_名字]</v>
+      </c>
+      <c r="C270" t="str">
+        <v>FERG(15)_dMax</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B271" t="str">
+        <v>[L_15_放大器]</v>
+      </c>
+      <c r="C271" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B272" t="str">
+        <v>[L_15_闪光]</v>
+      </c>
+      <c r="C272" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B273" t="str">
+        <v>[L_15_闪光背景]</v>
+      </c>
+      <c r="C273" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B274" t="str">
+        <v>[L_15_采样]</v>
+      </c>
+      <c r="C274" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B275" t="str">
+        <v>[L_15_分析时间]</v>
+      </c>
+      <c r="C275" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B276" t="str">
+        <v>[L_15_数据长度]</v>
+      </c>
+      <c r="C276" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B277" t="str">
+        <v>[L_15_详细数据(uv)]</v>
+      </c>
+      <c r="C277" t="str">
+        <v>-16.59,-20.52,-6.67,1.69,-9.32,-20.46,-12.26,1.78,-1.8,-16.35,-16.47,-1.4,3.73,-9.26,-17.59,-6.43,5.76,-1.25,-14.93,-11.34,3.9,5.32,-9.02,-14.13,-0.96,8.55,-1.75,-13.74,-7.05,7.15,4.6,-10.15,-12.49,1.68,8.08,-4.88,-15.39,-5.56,5.91,-0.28,-16.62,-14.33,-0.3,-1.06,-14.93,-23.58,-14.66,-6.51,-13.54,-31.73,-27.25,-13.39,-15.17,-37.96,-47.95,-34.93,-21.61,-39.49,-60.15,-47.96,-41.28,-49.94,-77.86,-76.93,-53.63,-72.03,-89.22,-103.67,-93.01,-80.06,-90.86,-97.89,-91.28,-84.1,-84.87,-113.48,-135.97,-80.5,-93.34,-92.2,-100.6,-96.31,-104.23,-98.49,-95.2,-108.49,-87.03,-85.54,-64.1,-78.42,-46.54,-15.55,-7.61,-25.59,13.76,40.04,31.76,27.67,51.18,65.43,99.99,124.97,131.83,110.92,201.95,142.81,167.87,219.54,202.35,255.39,277.24,320.78,279.06,334.17,329.65,359.46,415.67,469.08,489.63,396.07,493.98,485.25,544.63,581.44,583.55,604.51,557.86,563.4,596.01,547.06,582.29,713.97,728.16,579.07,625.02,636.38,683.05,669.08,630.92,765.44,675.87,656.53,783.34,706.87,734.69,789.59,779.49,648.75,663.11,815.15,774.09,800.4,689.09,703.93,717.87,779.52,671.86,738.43,690.69,735.77,680.69,658.53,600.59,631.64,586.55,587.49,665.79,607.9,598.93,551.66,505.53,607.81,501.88,554.46,485.86,473.31,471.68,487.15,458.1,488.43,438.96,376.13,420.81,398.33,389.42,428.63,353.18,355.68,404.27,381.37,350.23,349.53,310.62,348.32,320.45,286.37,267.01,269.66,255.63,237.55,220.98,280.83,237.23,214.68,212.25,226.28,244.98,217.6,233.71,179.79,223.67,180.94,156.06,195.32,166.98,175.93,136.29,161.45,152.14,131.09,167.84,117.49,100.79,128.29,120.31,130.48,107.81,113.86,125.33,123.69,84.7,100.45,92.35,98.49,66.05,74.55,74.49,63.39,74.06,52.05,38.4,63.64,63.44,26.42,35.57,34.35,33.67,36.16,22.75,16.38,35.31,22.66,-5.24,-0.46,14.47,14.23,-2.53,0.07,5.47,11.42,-7.49,-12.1,-9.73,-2.46,-7.7,-23.57,-22.73,-4.3,-7.95,-15.12,-27.37,-12.21,-10.41,-18.96,-32.93,-23.79,-15.79,-12.1,-33.35,-33.78,-21.23,-19.02,-29.61,-42.55,-28.62,-11.47,-26.28,-36.51,-39.24,-28.27,-14.45,-37.74,-35.81,-27.94,-23.59,-23.09,-43.31,-38.45,-30.06,-32.6,-39.47,-42.65,-39.69,-21.59,-42.28,-61.64,-41.7,-30.56,-27.32,-57.04,-47.17,-41.65,-29.15,-48.92,-62.68,-50.11,-48.08,-41.76,-68.1,-67.3,-46.68,-51.52,-68.52,-70.32,-73.17,-58.51,-64.17,-69.18,-79.66,-68.51,-53.48,-74.19,-76,-58.08,-53.9,-85.9,-90.93,-91.88,-64.13,-84.39,-92.53,-90.34,-69.84,-70.48,-70.11,-109.83,-66.95,-66.65,-85.28,-96.5,-90.93,-65.84,-70.74,-95.85,-106.15,-77.51,-78.78,-75.11,-119.03,-94.22,-98.8,-77.9,-113.35,-102.25,-92.07,-60.01,-89.4,-102.47,-97.46,-64.96,-87.81,-118.14,-77.63,-69.72,-82.06,-82.08,-117.7,-67.54,-69.44,-96.94,-115.23,-110.98,-69.8,-72.89,-88.09,-90.9,-96.8,-84.44,-83.8,-89.6,-93.5,-97.05,-92.31,-76.53,-80.78,-71.99,-70.58,-101.74,-103.7,-100.96,-92.9,-95.26,-96.44,-101.77,-61.57,-81.27,-101.49,-81.03,-80,-73.04,-92.26,-95.72,-93.02,-73.32,-67.48,-85.37,-84.15,-82.5,-85.69,-78.03,-84.2,-83.64,-81.61,-81.13,-88.32,-86.23,-76.26,-62.13,-92.57,-75.32,-86.13,-72.87,-92.01,-96.36,-78.51,-67.74,-71.59,-87.72,-68.74,-73.05,-67.65,-84.55,-92.9,-62.83,-61.31,-74.59,-83.41,-84.2,-65.5,-44.32,-78.03,-64.01,-66.58,-53.36,-58.53,-61.59,-52.51,-43.53,-47.18,-59.5,-55.47,-54.24,-38.02,-47.21,-49.5,-55.18,-24.65,-42.7,-50.06,-56.11,-31.01,-23.51,-37.48,-53.16,-39.6,-20.74,-37.73,-48.88,-44.03,-26.63,-16.77,-42.55,-38.18,-20.87,-19.19,-26.2,-40.66,-36.22,-17.54,-16.5,-34.53,-36.94,-16.26,-11.79,-33.4,-41.66,-22.94,-17.92,-23.43,-40.22</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B278" t="str">
+        <v>[L_15_标记]</v>
+      </c>
+      <c r="C278" t="str">
+        <v>a: 40.8ms -218.6uv b: 84.3ms 923.9uv</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B279" t="str">
+        <v>[R_16_名字]</v>
+      </c>
+      <c r="C279" t="str">
+        <v>FERG(16)_dOps</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B280" t="str">
+        <v>[R_16_放大器]</v>
+      </c>
+      <c r="C280" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B281" t="str">
+        <v>[R_16_闪光]</v>
+      </c>
+      <c r="C281" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B282" t="str">
+        <v>[R_16_闪光背景]</v>
+      </c>
+      <c r="C282" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B283" t="str">
+        <v>[R_16_采样]</v>
+      </c>
+      <c r="C283" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B284" t="str">
+        <v>[R_16_分析时间]</v>
+      </c>
+      <c r="C284" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B285" t="str">
+        <v>[R_16_数据长度]</v>
+      </c>
+      <c r="C285" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B286" t="str">
+        <v>[R_16_详细数据(uv)]</v>
+      </c>
+      <c r="C286" t="str">
+        <v>-11.65,1.21,1.62,-10.95,-2.13,4.85,-8.47,-5.66,6.06,-4.48,-8.52,5.2,0.1,-9.68,2.56,4,-9.18,-1.34,6.27,-7.09,-5.88,5.96,-4.43,-10,3.1,-1.36,-12.3,-1.09,0.86,-12.79,-5.72,2.58,-10.19,-9.7,3.24,-5.67,-11.55,2.67,-0.51,-11.25,-0.3,2.95,-10.43,-5.75,2.83,-9.87,-12.17,-0.5,-10.34,-19.09,-7.64,-10.26,-24.59,-15.26,-9.67,-25.94,-18.78,-9.07,-19.24,-19.55,-3.68,-9.11,-13.88,0.84,3.9,-9.68,5.58,10.54,-3.31,-2.54,10.95,-3.89,-11.17,-1.1,-12.04,-24.99,-15.65,-19.87,-33.03,-30.13,-21.44,-40.9,-35.62,-22.27,-26.82,-23.36,-3.46,-2.81,-4.88,15.58,24.86,17.71,25.92,41.81,25.97,19.6,27.7,16.61,5.98,9.18,-6,-25.08,-27.78,-36.43,-57.74,-49.24,-36.8,-57.05,-59.56,-33.35,-36.79,-31.62,-8.4,0.11,0.15,26.62,41.52,34.87,51.6,50.39,40.42,39.33,41.48,26.55,8.33,8.87,-6.37,-33.51,-35.22,-45.79,-69.47,-70.5,-63.79,-69.4,-71.3,-57.91,-52.99,-54.08,-22.18,-9.18,-6.06,22.24,30.98,25.27,42.75,49.25,56.58,34.24,53.52,25.59,7.8,6.63,-6.75,-34.93,-43.41,-39.51,-77.02,-82.15,-75.23,-84.71,-83.92,-58.53,-50.88,-51.83,-23.27,-11.09,-12.76,7.6,25.97,27.3,38.48,40.33,40.7,36.78,42.76,20.97,6.43,7.17,0.15,-22.35,-23.65,-25.5,-42.31,-50.34,-34.64,-47.57,-52.68,-33.18,-29.89,-33.63,-15.59,-5.83,-12.26,0.99,12.89,9.9,7.52,24.2,16.75,10.9,18.61,9.6,-5.59,2.77,0.74,-17.48,-16.31,-10.41,-26.95,-29.38,-15.26,-25.26,-34.22,-19.79,-17.28,-27.62,-15.95,-8.02,-19.08,-12.4,-0.25,-10.35,-12.06,1.21,-5.82,-13.61,-2.79,-5.93,-19.8,-11.19,-7.34,-22.41,-20.31,-10.11,-23.16,-26.71,-13.85,-19.8,-28.9,-16.45,-14.31,-27.3,-17.57,-9.95,-22.68,-19.7,-7.14,-17.47,-21.53,-7.67,-12.42,-22.33,-10.43,-8.85,-22.02,-14.5,-6.74,-20,-18.8,-6.51,-16.15,-21.63,-7.67,-11.51,-22.2,-10.2,-7.15,-20.39,-13.28,-4.25,-16.76,-16.33,-3.37,-12.22,-18.42,-4.81,-7.72,-19.06,-8.09,-4.32,-17.91,-12.2,-2.68,-15.15,-16.16,-3.19,-11.48,-18.94,-5.76,-7.83,-19.96,-9.84,-5.22,-19.02,-14.51,-4.4,-16.54,-18.8,-5.73,-13.28,-21.8,-9.04,-10.18,-22.92,-13.7,-8.21,-22.07,-18.7,-7.99,-19.64,-23.01,-9.79,-16.4,-25.74,-13.32,-13.32,-26.39,-17.88,-11.32,-24.94,-22.5,-11.04,-21.88,-26.14,-12.64,-18.07,-28,-15.81,-14.5,-27.67,-19.81,-12.09,-25.26,-23.66,-11.43,-21.34,-26.39,-12.65,-16.83,-27.26,-15.38,-12.78,-25.99,-18.85,-10.08,-22.77,-22.1,-9.28,-18.28,-24.21,-10.45,-13.5,-24.51,-13.17,-9.47,-22.8,-16.63,-7.05,-19.38,-19.85,-6.72,-14.97,-21.94,-8.46,-10.57,-22.3,-11.77,-7.19,-20.76,-15.77,-5.63,-17.7,-19.47,-6.26,-13.85,-21.97,-8.97,-10.22,-22.69,-13.13,-7.77,-21.55,-17.82,-7.21,-18.94,-22.01,-8.8,-15.64,-24.8,-12.3,-12.63,-25.67,-17.04,-10.82,-24.59,-22,-10.84,-22.01,-26.17,-12.87,-18.75,-28.69,-16.59,-15.78,-29.1,-21.25,-14,-27.47,-25.84,-13.98,-24.32,-29.35,-15.85,-20.53,-31.01,-19.21,-17.1,-30.47,-23.29,-14.93,-27.88,-27.1,-14.54,-23.88,-29.68,-16,-19.41,-30.34,-18.9,-15.51,-28.84,-22.42,-13.04,-25.45,-25.6,-12.49,-20.88,-27.52,-13.88,-16.13,-27.58,-16.73,-12.24,-25.63,-20.19,-10.04,-22.02,-23.3,-9.94,-17.52,-25.17,-11.86,-13.15,-25.26,-15.26,-9.91,-23.47,-19.24,-8.56,-20.21,-22.79,-9.41,-16.3,-25.04,-12.28,-12.71,-25.5,-16.52,-10.41,-24.11,-21.16,-10.07,-21.34,-25.19,-11.88,-18,-27.75,-15.56,-15.06,-28.37,-20.36,-13.44,-27.07,-25.29,-13.7,-24.37,-29.31,-15.97,-21.1,-31.6,-19.88,-18.26,-31.79,-24.61,-16.7,-29.98,-29.17,-16.96,-26.74,-32.53</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B287" t="str">
+        <v>[R_16_标记]</v>
+      </c>
+      <c r="C287" t="str">
+        <v>103.3uv</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B288" t="str">
+        <v>[L_16_名字]</v>
+      </c>
+      <c r="C288" t="str">
+        <v>FERG(16)_dOps</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B289" t="str">
+        <v>[L_16_放大器]</v>
+      </c>
+      <c r="C289" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B290" t="str">
+        <v>[L_16_闪光]</v>
+      </c>
+      <c r="C290" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B291" t="str">
+        <v>[L_16_闪光背景]</v>
+      </c>
+      <c r="C291" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B292" t="str">
+        <v>[L_16_采样]</v>
+      </c>
+      <c r="C292" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B293" t="str">
+        <v>[L_16_分析时间]</v>
+      </c>
+      <c r="C293" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B294" t="str">
+        <v>[L_16_数据长度]</v>
+      </c>
+      <c r="C294" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B295" t="str">
+        <v>[L_16_详细数据(uv)]</v>
+      </c>
+      <c r="C295" t="str">
+        <v>5.21,-13.57,-13.46,6.64,-0.63,-16.05,-0.56,9.4,-9.96,-10.47,9.55,1.34,-14.9,-0.09,9.07,-10.73,-12.19,7.28,-0.44,-17.3,-1.75,8.09,-11.21,-12.6,8,1.35,-14.14,1.69,12.41,-5.33,-5.68,14.82,7.88,-8.88,4.61,14.62,-6.01,-8.94,8.37,-1.21,-20.08,-8.77,-0.79,-23.41,-24.97,-6.67,-17.41,-31.81,-17.14,-6.33,-24.59,-23.58,-0.12,-4.31,-16.27,0.3,14.01,-0.89,-4.61,14.33,8.51,-5.44,1.37,10.37,-14.65,-21.14,-7.51,-18.6,-44.45,-35.01,-29.4,-52.69,-52.84,-31.93,-32,-49.89,-27.93,-13.06,-22.46,-15.58,11.92,16.16,1.75,30.72,44.27,20.27,15.27,35.91,29.91,6.26,9.72,11.27,-18.12,-33.89,-24.55,-40.24,-58.26,-56.71,-43.49,-56.71,-61.04,-31.21,-36.53,-40.24,-11.41,13.06,5.58,16.04,42.92,60.78,50.78,57.27,81.74,41.41,42.01,43.25,24.66,-3.95,-6.36,-10.64,-42.67,-61.31,-58.51,-52.84,-95.7,-64.62,-68.52,-64.88,-59.5,-23.35,-15.58,-20.29,10.52,31.98,24.72,26.95,71.5,49.06,48.21,56.33,54.04,29.6,13.25,16.26,-7.12,-42.97,-41.75,-39.1,-65.13,-74.88,-57.3,-59.5,-89.56,-64.99,-37.36,-53.79,-43.83,-8.53,0.76,-3.65,16.51,43.34,27.7,30.26,36.55,46.35,15.49,19.64,24.91,-3.91,-19.03,-9.63,-21.54,-51.94,-39.61,-33.04,-55.48,-61.16,-40.51,-34.57,-49.25,-28.2,-6.85,-16.59,-14.54,11.32,16.19,0.71,18.12,37.28,15.67,13.39,27,20.43,-2.6,2.12,10.81,-12.03,-22.01,-5.11,-15.19,-31.15,-21.63,-11.87,-24.07,-32.88,-8.62,-9.66,-24.47,-9.98,6.65,-7.63,-12.9,8.34,6.89,-9.59,0.15,11.5,-5.54,-13.26,3.15,-1.63,-22.33,-13.29,-1.75,-20.16,-28.1,-9.7,-12.22,-31.64,-21.37,-7.13,-23.43,-28.99,-8.72,-10.46,-28.68,-17.39,-2.54,-19.46,-26.01,-5.74,-8.15,-27.16,-16.44,-3.18,-20.39,-27.24,-7.95,-10.23,-29.54,-19.35,-4.76,-21.56,-28.56,-8.47,-9.93,-28.63,-17.81,-2.68,-18.84,-25.33,-4.93,-6.06,-24.61,-13.98,1.08,-15.08,-22.01,-1.9,-2.94,-21.86,-11.58,3.44,-12.84,-20.06,-0.04,-1.14,-20.14,-10.13,4.93,-11.26,-18.73,1.2,0.18,-18.96,-9.24,5.8,-10.46,-18.27,1.43,0.4,-19.03,-9.7,5.24,-11.14,-19.34,0.09,-0.96,-20.63,-11.64,3.25,-13.19,-21.69,-2.42,-3.41,-23.23,-14.48,0.45,-15.95,-24.66,-5.45,-6.28,-26.16,-17.56,-2.51,-18.76,-27.59,-8.37,-8.96,-28.79,-20.26,-4.99,-21.02,-29.88,-10.56,-10.82,-30.53,-22,-6.44,-22.17,-31.01,-11.53,-11.41,-30.97,-22.39,-6.52,-21.93,-30.73,-11.1,-10.61,-30.01,-21.41,-5.25,-20.38,-29.18,-9.44,-8.62,-27.93,-19.37,-2.99,-17.9,-26.78,-7.01,-5.94,-25.24,-16.82,-0.31,-15.1,-24.15,-4.45,-3.25,-22.63,-14.44,2.1,-12.67,-21.98,-2.44,-1.19,-20.74,-12.87,3.62,-11.2,-20.84,-1.54,-0.29,-20.07,-12.55,3.83,-11.06,-21.06,-2.01,-0.79,-20.79,-13.63,2.66,-12.3,-22.63,-3.81,-2.57,-22.75,-15.91,0.35,-14.61,-25.22,-6.55,-5.22,-25.5,-18.9,-2.58,-17.46,-28.24,-9.63,-8.12,-28.41,-21.93,-5.47,-20.16,-31.02,-12.38,-10.58,-30.78,-24.35,-7.65,-22.07,-32.92,-14.18,-12.03,-32.07,-25.62,-8.64,-22.73,-33.54,-14.65,-12.13,-31.98,-25.5,-8.23,-22,-32.76,-13.76,-10.87,-30.56,-24.09,-6.57,-20.06,-30.83,-11.76,-8.58,-28.18,-21.79,-4.09,-17.39,-28.26,-9.21,-5.82,-25.43,-19.21,-1.45,-14.64,-25.7,-6.78,-3.29,-23,-17.05,0.69,-12.49,-23.84,-5.13,-1.61,-21.5,-15.89,1.76,-11.47,-23.15,-4.71,-1.21,-21.3,-16.07,1.46,-11.83,-23.86,-5.68,-2.21,-22.49,-17.62,-0.17,-13.5,-25.83,-7.88,-4.37,-24.79,-20.21,-2.79,-16.08,-28.64,-10.83,-7.2,-27.67,-23.29,-5.8,-18.96,-31.64,-13.88,-10.03,-30.44,-26.17,-8.52,-21.44,-34.16</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B296" t="str">
+        <v>[L_16_标记]</v>
+      </c>
+      <c r="C296" t="str">
+        <v>107.8uv</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B297" t="str">
+        <v>[R_17_名字]</v>
+      </c>
+      <c r="C297" t="str">
+        <v>FERG(17)_dMax</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B298" t="str">
+        <v>[R_17_放大器]</v>
+      </c>
+      <c r="C298" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B299" t="str">
+        <v>[R_17_闪光]</v>
+      </c>
+      <c r="C299" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B300" t="str">
+        <v>[R_17_闪光背景]</v>
+      </c>
+      <c r="C300" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B301" t="str">
+        <v>[R_17_采样]</v>
+      </c>
+      <c r="C301" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B302" t="str">
+        <v>[R_17_分析时间]</v>
+      </c>
+      <c r="C302" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B303" t="str">
+        <v>[R_17_数据长度]</v>
+      </c>
+      <c r="C303" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B304" t="str">
+        <v>[R_17_详细数据(uv)]</v>
+      </c>
+      <c r="C304" t="str">
+        <v>2.78,-6.17,-1.07,1.09,-6.93,1.48,-1.8,-6.02,2.66,-4.89,-3.83,2,-7.15,-1.21,-0.36,-7.89,0.78,-3.73,-6.94,1.25,-7,-4.91,-0.16,-9.27,-2.51,-3.07,-9.98,-1.3,-7.03,-9.01,-1.34,-10.14,-7.07,-3.53,-13.13,-5.61,-7.73,-13.73,-4.92,-12.42,-14.05,-6.7,-17.93,-14.12,-10.93,-19.07,-12.09,-18.09,-22.39,-13.37,-20.86,-26.27,-23.24,-31.01,-25.71,-29.33,-40.06,-26.28,-40.02,-43.18,-36.22,-53.62,-44.35,-45.93,-54.08,-47.54,-52.66,-53.99,-65.19,-74.79,-61.57,-52.65,-66.79,-83.72,-80.67,-64.12,-68.31,-81.57,-76.79,-84.62,-64.34,-75.28,-77.74,-90.06,-64.97,-52.78,-81.47,-45,-49.3,-35.46,-27.94,-27.91,-56.88,3.06,-25.72,32.4,36.62,42.56,37.97,70.26,39.07,76.57,76.39,100.1,141.48,113.88,164.92,182.65,175.45,198.96,242.38,232.11,244.67,235.62,288.16,341.17,365.76,383.79,372.68,419.87,464.65,421.99,400.77,474.57,437.48,566.39,520.04,498.8,522.39,551.09,625.67,559.9,622.38,645.17,718.25,602.39,678.87,715.93,660.23,652.18,692.37,661.14,651.81,752.37,735.59,836.08,695.18,768.57,697.09,845.01,799.71,689.19,694.28,738.53,810.44,822.82,772.79,692.62,760.92,771.78,773.31,822.06,730.92,757.42,809.9,715.94,753.96,654.86,729.21,741.62,738.33,685.49,604.89,607.1,695.19,642.21,621.74,656.17,646.83,642.74,559.91,532.84,625.57,547.41,586.26,543.32,492.07,448.03,523.27,464,447.97,463.51,455.66,459.76,388.91,429.67,399.41,389.58,386.71,325.34,350.61,325.49,370.3,360.37,295.28,358.26,338.45,280.97,320.05,298.08,245.22,240.8,227.08,231.52,260.94,246.11,213.23,244.11,228.06,204.29,166.29,190.73,188.16,180.71,186.15,153.95,146.76,169.36,150.16,157.97,162.58,147.18,130.05,101.51,115.08,101.54,94.98,114.63,111.01,108.95,84.66,99.54,78.39,69.95,75.49,56.35,67.69,52.62,60.32,40.11,33.97,50.41,44.95,39.37,45.8,21.2,30.89,20.96,13.7,15.3,20.38,0.03,14.8,12.35,-6.35,7.2,-3.32,-2.24,-1.49,-7.53,-2.66,-4.58,-12.35,-9.41,-10.62,-19.71,-13.8,-22.98,-21.03,-19.36,-22.48,-23.1,-19.54,-33.86,-23.79,-30.23,-34.23,-28.31,-31.81,-30.82,-30.78,-40.32,-30.2,-29.67,-47.06,-30.22,-33.18,-37.22,-31.12,-53.04,-49.83,-40.9,-56.29,-51.69,-41.5,-46.64,-48.49,-50.42,-59.82,-56.29,-59.99,-51.55,-53.68,-52.32,-64.19,-46.08,-69.34,-47.82,-63.78,-61.96,-66.33,-69.57,-74.36,-52.59,-70.27,-53.03,-59.03,-82.56,-68.89,-65.73,-82.6,-65.78,-79.33,-60.57,-68.71,-69.8,-73.68,-65.49,-89.15,-59.24,-67.82,-85.8,-69.67,-90.32,-62.76,-89.81,-99.06,-65,-74.81,-81.25,-66.15,-85.62,-93.07,-77.95,-87.76,-86.66,-82.74,-91.41,-81.36,-75.28,-78.91,-92.39,-75.48,-88.87,-70.61,-86.92,-82.66,-92.45,-103.01,-93.7,-99.74,-89.24,-96.14,-103.92,-117.51,-83.89,-120.67,-104.78,-104.3,-85.39,-100.31,-117.71,-115.75,-113.83,-99.34,-80.52,-114.53,-112.65,-93.53,-82.79,-113.22,-110.45,-86.9,-112.9,-105.15,-122.78,-79.71,-84.81,-127.53,-77.46,-125.73,-110.24,-105.34,-97.69,-91.53,-77.65,-111.49,-97.16,-90.45,-112.6,-113.58,-102.26,-116.73,-111.27,-83.37,-107.02,-98.8,-117.3,-93.99,-86.75,-98.38,-86.59,-83.97,-92,-78.29,-77.38,-101.9,-80.33,-107.6,-73.82,-77.22,-88.45,-93.65,-70.54,-99.28,-92.42,-82.55,-69.96,-85.91,-85.19,-81.01,-75.32,-82.31,-74.03,-91.45,-70,-62.18,-64.17,-73.93,-56.46,-60.47,-61.54,-80.76,-66.79,-73.61,-72.81,-60.47,-54.75,-72.69,-58.84,-51.52,-68.79,-49.38,-70.14,-60.17,-58.84,-66.01,-64.9,-52.37,-58.56,-47.4,-61.12,-63.62,-49.96,-47.47,-49.28,-46.94,-61.02,-43.89,-56.22,-60.16,-41.29,-55.24,-45.85,-46.07,-49.92,-50.37,-48.68,-45.39,-39.07,-41.69,-47.48,-34.09,-45.25,-46.47,-37.39,-47.02,-37.19,-40.48,-41.7</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B305" t="str">
+        <v>[R_17_标记]</v>
+      </c>
+      <c r="C305" t="str">
+        <v>a: 43.1ms -230.6uv b: 91.2ms 1092.1uv</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B306" t="str">
+        <v>[L_17_名字]</v>
+      </c>
+      <c r="C306" t="str">
+        <v>FERG(17)_dMax</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B307" t="str">
+        <v>[L_17_放大器]</v>
+      </c>
+      <c r="C307" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B308" t="str">
+        <v>[L_17_闪光]</v>
+      </c>
+      <c r="C308" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B309" t="str">
+        <v>[L_17_闪光背景]</v>
+      </c>
+      <c r="C309" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B310" t="str">
+        <v>[L_17_采样]</v>
+      </c>
+      <c r="C310" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B311" t="str">
+        <v>[L_17_分析时间]</v>
+      </c>
+      <c r="C311" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B312" t="str">
+        <v>[L_17_数据长度]</v>
+      </c>
+      <c r="C312" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B313" t="str">
+        <v>[L_17_详细数据(uv)]</v>
+      </c>
+      <c r="C313" t="str">
+        <v>-3.85,-3.04,-16.22,-1.83,-4.33,-15.58,-0.22,-5.92,-14.75,0.92,-7.73,-13.75,1.54,-9.68,-12.64,1.63,-11.69,-11.45,1.16,-13.66,-10.24,0.18,-15.51,-9.05,-1.28,-17.15,-7.93,-3.15,-18.52,-6.94,-5.34,-19.54,-6.11,-7.77,-20.18,-5.47,-10.33,-20.41,-5.06,-12.91,-20.23,-4.92,-15.44,-19.73,-5.06,-17.84,-18.79,-5.65,-19.97,-17.71,-6.52,-21.86,-16.64,-8.09,-23.75,-15.83,-10.53,-26.45,-14.88,-12.24,-28.82,-16.68,-17.81,-31.36,-17.43,-21.04,-36.07,-21.38,-31.14,-41.93,-25.16,-37.14,-47.61,-37.37,-42.22,-47.97,-39.26,-61.75,-54.88,-58.48,-63.78,-73.4,-63.78,-95.97,-76.61,-76.32,-111.92,-81.52,-108.47,-109.38,-111.81,-87.73,-112.59,-109.92,-94.5,-121.06,-116.28,-100.92,-109.07,-103.25,-138.18,-129.79,-100.82,-106.85,-102.38,-66.8,-78.5,-75.22,-46.6,-32.57,-45.3,-18.96,-37.08,-19.65,24.33,18.63,56.3,68.28,79.84,107.69,108.97,128.78,133.04,180.08,213.53,254.37,206.24,230.62,321.78,297.07,282.18,388.84,358.12,344.47,422.6,452.72,465.48,433.36,492.58,524.76,479.63,565.73,516.76,591.62,560.63,661.55,571.78,578.55,592.69,661.86,661.86,646.6,636.23,741.39,778.11,775.16,784.5,804.91,711.86,697.63,837.45,677.93,744.86,820.72,760.77,758.96,724.73,691.57,714.97,842.21,657.17,698.14,814.46,728.88,682.84,755.79,662.2,644.5,643.02,615.09,693.49,577.57,569.22,599.35,604.62,611.48,575.6,587.01,542.93,529.17,496.27,449.52,454.8,484.71,471.94,399.57,415.1,402.29,425.55,379.48,318.13,368.22,338.21,339.98,354.56,329.54,288.98,292.34,292.86,281.34,237.66,228.8,277.84,275.24,186.62,253.68,185.63,200.49,208.12,219.93,219.42,169,194.51,182.41,207.24,178.64,135.2,177.36,185.9,179.24,140.02,167.21,169.89,141.04,146.75,100.61,157.25,122.68,121.73,99.79,79,126.85,109.36,95.53,80.43,105.26,72.85,75.73,70.66,55.74,99.55,85.27,60.79,68.87,44.65,37.26,51.45,59.23,53.77,56.02,40.74,34.01,37.47,20.91,43.81,38.71,27.28,31.37,39.04,19.36,31.76,24.05,15.76,19.16,17.88,-6.74,20.42,9.06,-2.28,10.79,1.22,-15.99,7.89,-11.87,-18.67,-1.37,-11.45,-10.44,-6.02,-20.77,-13.54,-2.48,-27.26,-19.82,-10.43,-31.47,-19.53,-16.31,-32.92,-29.75,-28.48,-39.34,-32.97,-28.74,-35.96,-25,-30.37,-47.29,-36.84,-32.15,-48.77,-28.66,-39.52,-40.62,-38.08,-44.2,-49.87,-32.06,-54.47,-57.23,-38.59,-58.36,-49.32,-34.74,-51.74,-50.91,-50.66,-59.61,-55.22,-50.33,-67.36,-52.82,-62.91,-62.58,-50.06,-43.44,-70.07,-52.93,-63.31,-77.84,-42.51,-63.21,-81.13,-64.87,-60.4,-68.51,-60.83,-69.74,-56.08,-60.01,-73.87,-55.19,-43.43,-67.13,-69.12,-75.32,-83.39,-80.38,-73.82,-97.39,-52.6,-51.44,-66.03,-74.97,-88.62,-74.76,-54.53,-83.8,-81.4,-86.85,-85.77,-84.36,-61.86,-73.35,-103.09,-83.5,-90.87,-96.34,-82.29,-87.47,-106.4,-95.33,-107.28,-107.74,-67.08,-98.02,-105.19,-82.95,-115.11,-76.87,-74.71,-120.98,-81.21,-69.97,-93.52,-96.95,-108.19,-107.74,-94.46,-87.66,-115.24,-77.71,-90.61,-96.11,-74.35,-91.01,-122.13,-103.26,-92.43,-98.36,-65.78,-99.06,-87.17,-83.2,-92.58,-99.75,-79.25,-90.78,-95.35,-81.32,-86.75,-81.92,-97.72,-110.36,-72.03,-82.53,-106.18,-62.52,-83.2,-107.61,-88.82,-96.3,-90.28,-59.54,-71.75,-80.75,-55.69,-96.96,-72.86,-61.36,-82.21,-84.65,-78.51,-66.79,-69.98,-64.78,-69.58,-59.21,-55.38,-77.8,-67.08,-64.22,-58.27,-65.45,-68.81,-58.12,-52.57,-57.94,-56.1,-42.52,-60.14,-65.89,-57.02,-45.61,-63.27,-50.92,-62.12,-50.65,-54.35,-64.32,-58.58,-36.93,-53.89,-47.05,-33.32,-55.08,-37.17,-36.2,-63.66,-39.92,-33.14,-51.71,-38.31,-40.81,-58.04,-39.99,-45.41,-51.14,-32.48,-31.99,-42.69,-36.65,-35.52,-51.9,-32.19,-43.34,-35.71,-22.12,-32.88,-41.66</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B314" t="str">
+        <v>[L_17_标记]</v>
+      </c>
+      <c r="C314" t="str">
+        <v>a: 43.2ms -227.9uv b: 91.3ms 1057.4uv</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B315" t="str">
+        <v>[R_18_名字]</v>
+      </c>
+      <c r="C315" t="str">
+        <v>FERG(18)_dOps</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B316" t="str">
+        <v>[R_18_放大器]</v>
+      </c>
+      <c r="C316" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B317" t="str">
+        <v>[R_18_闪光]</v>
+      </c>
+      <c r="C317" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B318" t="str">
+        <v>[R_18_闪光背景]</v>
+      </c>
+      <c r="C318" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B319" t="str">
+        <v>[R_18_采样]</v>
+      </c>
+      <c r="C319" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B320" t="str">
+        <v>[R_18_分析时间]</v>
+      </c>
+      <c r="C320" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B321" t="str">
+        <v>[R_18_数据长度]</v>
+      </c>
+      <c r="C321" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B322" t="str">
+        <v>[R_18_详细数据(uv)]</v>
+      </c>
+      <c r="C322" t="str">
+        <v>18.63,1.87,11.33,10.42,2.11,16.94,-3.22,14.68,-0.39,4.9,6.74,-5.44,10.39,-10.41,7.38,-5.83,-1.88,3.8,-10.74,8.8,-9.89,6.97,-0.26,0.28,10.76,-3.47,16.29,-2.66,12.3,6.3,2.08,14.17,-5.26,12.38,-7.26,0.95,-3.61,-14.21,-0.69,-22.08,-3.45,-17.18,-11.88,-7.75,-18.8,0.95,-15.56,6.68,-1.37,8.14,16.26,8.63,30.49,13.51,27.42,21.03,22.3,25.21,8.27,22.54,0.28,8.51,-4.41,-13.29,-9.62,-25.02,-14.47,-29.43,-17.7,-20.65,-24.38,-3.72,-15.18,10.6,3.71,22.33,30.36,26.55,55.41,31.53,53.31,48.48,40.76,47.88,27.98,37.05,8.26,12.78,-9.19,-22.16,-17.58,-46.42,-33.91,-61.01,-42.59,-44.41,-47.62,-25.35,-32.24,-1.17,-5.5,22.06,33.38,38.38,55.15,38.85,75.8,46.45,73,56.45,42.59,45.41,8.72,10.21,-16.92,-32.42,-34.63,-58.78,-54.28,-80.36,-71.42,-74.12,-64.6,-49.87,-51.41,-13.11,-15.85,14.77,23.45,44.06,64.71,52.57,66.79,59.61,74.85,64.62,50.97,52.02,12.31,17.08,-16.27,-18.48,-39.07,-51.67,-38,-70.44,-51.57,-58.65,-55.86,-44.39,-43,-4.31,-14.3,19.45,25.43,41.39,55.93,45.8,71.34,44.49,60.02,54.2,43.72,47.49,17.41,25.66,-5.72,-0.73,-24.05,-37.11,-27.51,-46.88,-31.2,-42.78,-32.06,-31.76,-26.63,-2.12,-14.05,16.17,10.31,22.73,34.37,22.07,43.08,21.94,46.45,31.89,32.87,27.15,5.56,19.16,-8.81,-0.49,-16.6,-22.2,-16.53,-34.6,-17.92,-37.15,-16.11,-21.64,-17.82,-3.14,-16.29,7.33,-5.4,9.56,8.59,7.93,20.48,4.29,19.72,4.38,12.39,9.64,-2.09,10.98,-11.5,4.3,-10.96,-7.66,-6.36,-16.41,-1.5,-18.39,-1.7,-10.96,-7.29,3.01,-10.47,10.87,-6.17,10.27,4.74,3.82,15.32,-0.51,19.26,0.59,12.6,8.29,2.44,14.69,-4.6,14.23,-2.54,6.24,5.43,-3.42,12.29,-6.25,11.98,-1.32,5.39,8.52,-2.3,15.65,-3.7,14.06,2.97,5.75,11.99,-2.16,16.29,-3.2,12.11,3.29,2.04,11.14,-5.82,13.25,-5.64,7.11,1.51,-2.99,9.23,-9.35,10.11,-6.99,3.04,1.29,-6.48,8.35,-11.05,7.83,-7.13,-0.15,1.6,-9.34,7.53,-12.32,5.36,-7.04,-3.39,1.93,-11.72,6.75,-12.85,3.27,-5.97,-5.69,3.12,-12.65,6.87,-11.73,2.31,-3.51,-6.56,5.41,-12.04,7.89,-9.21,2.24,-0.03,-6.41,8.27,-10.38,9.23,-5.87,2.54,3.84,-5.72,11.15,-8.14,10.46,-2.2,2.84,7.62,-4.87,13.59,-5.79,11.15,1.26,2.72,10.75,-4.32,15.07,-3.83,10.84,4,1.78,12.76,-4.45,15.21,-2.62,9.29,5.69,-0.15,13.43,-5.38,13.93,-2.26,6.52,6.3,-2.95,12.81,-6.95,11.42,-2.57,2.83,6.05,-6.26,11.21,-8.8,8.08,-3.19,-1.27,5.33,-9.58,9.12,-10.44,4.48,-3.64,-5.21,4.65,-12.33,7.07,-11.35,1.2,-3.46,-8.4,4.43,-14,5.5,-11.13,-1.32,-2.33,-10.46,4.98,-14.3,4.71,-9.59,-2.84,-0.16,-11.2,6.32,-13.18,4.69,-6.84,-3.37,2.88,-10.76,8.25,-10.9,5.23,-3.2,-3.19,6.38,-9.49,10.35,-7.89,5.91,0.78,-2.73,9.78,-7.86,12.09,-4.72,6.23,4.5,-2.49,12.5,-6.41,12.95,-1.95,5.75,7.43,-2.85,14.08,-5.53,12.57,0.04,4.21,9.21,-4.05,14.27,-5.42,10.84,1.07,1.58,9.76,-6.06,13.07,-6.04,7.89,1.23,-1.9,9.22,-8.58,10.8,-7.07,4.12,0.84,-5.77,8.01,-11.15,7.91,-8.07,0.09,0.36,-9.45,6.61,-13.22,4.97,-8.54,-3.61,0.27,-12.36,5.51,-14.3,2.5,-8.07,-6.47,0.93,-14.08,5.07,-14.05,0.83,-6.42,-8.21,2.49,-14.41,5.4,-12.42,0.06,-3.66,-8.78,4.85,-13.42,6.37,-9.6,0.04,-0.08,-8.42,7.66,-11.45,7.64,-6.03,0.39</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B323" t="str">
+        <v>[R_18_标记]</v>
+      </c>
+      <c r="C323" t="str">
+        <v>102.3uv</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B324" t="str">
+        <v>[L_18_名字]</v>
+      </c>
+      <c r="C324" t="str">
+        <v>FERG(18)_dOps</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B325" t="str">
+        <v>[L_18_放大器]</v>
+      </c>
+      <c r="C325" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B326" t="str">
+        <v>[L_18_闪光]</v>
+      </c>
+      <c r="C326" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B327" t="str">
+        <v>[L_18_闪光背景]</v>
+      </c>
+      <c r="C327" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B328" t="str">
+        <v>[L_18_采样]</v>
+      </c>
+      <c r="C328" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B329" t="str">
+        <v>[L_18_分析时间]</v>
+      </c>
+      <c r="C329" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B330" t="str">
+        <v>[L_18_数据长度]</v>
+      </c>
+      <c r="C330" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B331" t="str">
+        <v>[L_18_详细数据(uv)]</v>
+      </c>
+      <c r="C331" t="str">
+        <v>-20.26,-25.65,-11.02,-29.91,-13.81,-21.61,-25.16,-11.99,-30.76,-13.91,-23.7,-25.64,-14.19,-32.78,-15.48,-27.21,-27.25,-17.44,-35.56,-17.57,-30.49,-28.79,-20.16,-36.79,-18.32,-32.01,-27.53,-20.22,-35.38,-16.07,-31.24,-23.84,-18.72,-33.72,-14.72,-31.24,-22.94,-21.08,-34.93,-17.7,-36.11,-27.52,-27.15,-41.36,-23.87,-41.62,-32.78,-31.16,-43.26,-22.92,-40.29,-25.87,-25.92,-31.5,-12.3,-27.21,-9.37,-14.16,-18.92,-2.14,-18.61,-4.63,-8.31,-18.76,-4.66,-28.39,-15.8,-28.67,-35.3,-26.51,-50.61,-33.55,-48.84,-47.42,-38.16,-48.48,-28.98,-33.61,-27.99,-10.1,-18.88,4.59,-2.63,12.94,23.74,4.79,32.21,10.43,13.85,15.37,-6.74,0.78,-25.39,-29.09,-37.34,-59.51,-47.06,-68.92,-73.73,-69.95,-71.94,-50.31,-70.63,-41.44,-34.65,-32.15,0.32,-10.21,12.08,22.63,28.32,44.38,30.14,37.44,26.7,18.52,19.81,-12.34,-16.15,-35.89,-55.64,-59.05,-89.02,-92.33,-87.41,-93.47,-84.61,-87.55,-74.61,-67.18,-50.26,-23.17,-26.34,6.56,6.76,22.81,45.27,34.95,50.53,45.47,23.36,29.91,-3.1,11.15,-21.07,-32.24,-35.19,-69.55,-66.12,-86.39,-73.91,-65.94,-91.48,-69.71,-70.14,-50.35,-36.5,-36.74,-4.63,-10.58,9.14,16.31,11.78,31.64,27.77,26.05,28.66,9.7,25,-9.27,-4.23,-16.71,-33.85,-28.87,-48.67,-39.16,-54.07,-59.29,-36.81,-53.15,-37.82,-36.7,-38.2,-15.94,-27.47,-6.11,-5.51,-4.84,8.71,-8.33,7.76,0.31,-6.76,4.97,-18.57,-6.43,-20.75,-25.09,-18.63,-38.73,-24.41,-39.7,-40.83,-27.84,-45.46,-26.14,-40.68,-33.03,-23.41,-37.42,-16.17,-29.06,-21.33,-13.66,-28.2,-8.21,-24.05,-18.26,-13.78,-27.98,-11.78,-29.66,-20.97,-20.28,-33.55,-16.22,-33.72,-23.91,-24.08,-34.58,-16.39,-33.38,-20.76,-21.92,-30,-12.24,-30.12,-15.51,-18.69,-25.46,-8.76,-27.46,-11.84,-17.36,-22.89,-7.81,-26.62,-10.47,-18.01,-21.68,-8.1,-26.64,-9.57,-18.85,-20.42,-8.23,-26.19,-8.36,-19.19,-18.8,-8.13,-25.69,-7.31,-19.74,-17.58,-8.7,-25.61,-7.02,-21.05,-17.1,-10.16,-26.23,-7.63,-23.01,-17.31,-12.29,-27.27,-8.76,-25.25,-17.78,-14.66,-28.34,-10.07,-27.46,-18.26,-17.04,-29.28,-11.42,-29.51,-18.64,-19.34,-29.96,-12.68,-31.25,-18.81,-21.38,-30.26,-13.71,-32.54,-18.64,-23.02,-30.03,-14.37,-33.23,-17.99,-24.13,-29.18,-14.56,-33.25,-16.84,-24.68,-27.73,-14.31,-32.64,-15.25,-24.7,-25.73,-13.69,-31.49,-13.31,-24.31,-23.34,-12.82,-29.92,-11.19,-23.66,-20.72,-11.87,-28.14,-9.09,-22.91,-18.09,-11.04,-26.32,-7.19,-22.27,-15.63,-10.49,-24.67,-5.68,-21.89,-13.54,-10.39,-23.33,-4.72,-21.9,-11.95,-10.83,-22.42,-4.4,-22.37,-10.93,-11.87,-21.97,-4.73,-23.3,-10.49,-13.46,-21.97,-5.67,-24.63,-10.56,-15.53,-22.32,-7.12,-26.24,-11.04,-17.9,-22.88,-8.91,-27.95,-11.74,-20.4,-23.48,-10.85,-29.57,-12.5,-22.82,-23.93,-12.73,-30.91,-13.11,-24.96,-24.05,-14.38,-31.79,-13.43,-26.66,-23.72,-15.66,-32.09,-13.35,-27.79,-22.84,-16.47,-31.74,-12.81,-28.31,-21.41,-16.79,-30.75,-11.84,-28.25,-19.47,-16.67,-29.18,-10.51,-27.67,-17.14,-16.21,-27.17,-8.98,-26.74,-14.59,-15.58,-24.9,-7.4,-25.61,-12.02,-14.95,-22.57,-5.99,-24.49,-9.63,-14.5,-20.38,-4.93,-23.54,-7.61,-14.4,-18.49,-4.36,-22.92,-6.1,-14.76,-17.05,-4.4,-22.73,-5.21,-15.65,-16.11,-5.08,-22.98,-4.95,-17.06,-15.68,-6.38,-23.64,-5.27,-18.91,-15.68,-8.19,-24.61,-6.08,-21.07,-16,-10.37,-25.74,-7.21,-23.35,-16.47,-12.71,-26.84,-8.47,-25.56,-16.9,-15.03,-27.72,-9.67,-27.5,-17.11,-17.11,-28.21,-10.64,-28.98,-16.96,-18.81,-28.17,-11.25,-29.9,-16.34,-20.01,-27.52,-11.42,-30.16,-15.22,-20.67,-26.25,-11.14,-29.79,-13.63,-20.81,-24.41,-10.48,-28.85,-11.67,-20.51,-22.13,-9.55,-27.48</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B332" t="str">
+        <v>[L_18_标记]</v>
+      </c>
+      <c r="C332" t="str">
+        <v>101.7uv</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B333" t="str">
+        <v>[R_19_名字]</v>
+      </c>
+      <c r="C333" t="str">
+        <v>FERG(19)_lCone</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B334" t="str">
+        <v>[R_19_放大器]</v>
+      </c>
+      <c r="C334" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B335" t="str">
+        <v>[R_19_闪光]</v>
+      </c>
+      <c r="C335" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B336" t="str">
+        <v>[R_19_闪光背景]</v>
+      </c>
+      <c r="C336" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B337" t="str">
+        <v>[R_19_采样]</v>
+      </c>
+      <c r="C337" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B338" t="str">
+        <v>[R_19_分析时间]</v>
+      </c>
+      <c r="C338" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B339" t="str">
+        <v>[R_19_数据长度]</v>
+      </c>
+      <c r="C339" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B340" t="str">
+        <v>[R_19_详细数据(uv)]</v>
+      </c>
+      <c r="C340" t="str">
+        <v>-10.83,-8.96,-12.07,-8.22,-13.23,-7.56,-14.24,-7.01,-15.07,-6.6,-15.7,-6.35,-16.09,-6.27,-16.22,-6.36,-16.1,-6.62,-15.72,-7.05,-15.11,-7.61,-14.28,-8.28,-13.27,-9.03,-12.11,-9.81,-10.86,-10.59,-9.56,-11.34,-8.25,-11.99,-6.99,-12.53,-5.83,-12.91,-4.79,-13.12,-3.93,-13.12,-3.26,-12.92,-2.81,-12.51,-2.58,-11.9,-2.58,-11.1,-2.8,-10.14,-3.22,-9.07,-3.84,-7.92,-4.59,-6.74,-5.43,-5.64,-6.38,-4.56,-7.37,-3.64,-8.57,-2.92,-9.67,-2.42,-10.41,-2.64,-11.68,-2.98,-13.16,-3.58,-13.86,-4.53,-14.36,-6.19,-16.65,-7.93,-16.34,-10.54,-20.63,-13.38,-22.45,-19.95,-24.21,-25.28,-28.09,-28.83,-27.67,-28.37,-27.06,-33.14,-29.28,-38.49,-33.64,-44.03,-46.9,-46.3,-40.5,-47.78,-54.59,-62.86,-43.85,-64.86,-52.76,-56.8,-59.96,-57.74,-41.66,-57.12,-48.77,-49.36,-50.52,-42.9,-52.8,-43.73,-41.71,-41,-36.48,-32.12,-33.01,-12.12,-16.91,-8.2,-18.67,-6.4,9.65,9.55,14.63,19.44,28.41,31.33,26.78,46.21,44.95,57.46,50.52,70.78,74.1,75.51,72.04,90.85,109.16,104.69,104.41,107.21,132.88,142.19,144.55,126.21,150.74,151.27,158.73,171.44,170.77,184.15,200.9,158.33,222.94,210.58,225.44,225.64,216.52,220.91,217.72,192.66,264.4,230.38,230.68,258.16,285.3,280.89,259.49,221.74,239.69,290.02,267.52,277.64,241.32,238.72,245.69,251.88,289.46,235.91,236.57,230.67,242.87,226.22,266.25,276.81,267.06,214.98,206.47,232.1,248.29,204.55,208.31,189.62,180.99,199.19,221.19,186.19,185.4,210.1,205.61,186.14,156.33,176.14,164.14,154.91,172.39,156.55,153.31,132.41,114.51,120.87,111.49,98.01,96.45,88.79,116.1,88.88,87.9,75.53,92.28,77.62,75.29,58.85,75.14,57.74,53.49,48.5,46.19,40.02,45.5,45.38,41.85,37.45,28.63,27.33,24.14,30.47,22.11,25.06,19.47,23.67,13.94,18.9,7.37,16.09,4.74,14.36,3.3,12.11,3.22,11.01,-1.62,8.15,-1.12,4.53,-2.25,3.89,-2.54,-0.6,-4.35,-2.7,-5.84,-3.6,-5.09,-7.63,-5.45,-7.41,-5.8,-10.7,-4.5,-13.37,-3.32,-14.36,-4.82,-14.51,-5.36,-14.63,-6.76,-15.16,-4.48,-16.3,-9.89,-15.86,-5.88,-16.97,-8.06,-18.6,-13.52,-13.29,-14.14,-12.6,-14.91,-16.44,-13.69,-14.47,-17.81,-12.14,-19.69,-11.75,-19.34,-15.89,-17.94,-16.58,-17.03,-8.38,-27.01,-8.62,-19.45,-12.16,-18.93,-10.45,-29.71,-18.72,-26.47,-14.95,-17.9,-21.52,-26.69,-16.11,-20.68,-18.3,-30.96,-19.47,-19.09,-29.55,-17.08,-20.45,-19.06,-32.34,-16.43,-28.38,-22.9,-28.39,-21.37,-35.18,-23.39,-38.78,-19.94,-34.98,-25.47,-43.57,-30.22,-33.62,-38.54,-34.8,-29.06,-29.5,-31.08,-39.84,-37.37,-46.44,-35.17,-32.26,-43.02,-38.47,-35.14,-38.26,-39.03,-50.19,-45.37,-39.68,-41.26,-27.4,-40.28,-34.75,-38.71,-34.9,-49.38,-37.21,-59.58,-40.43,-58.56,-39.18,-44.97,-52.24,-47.89,-32.67,-55.29,-35.9,-53.55,-42.67,-54.78,-49.04,-40.89,-39,-31.15,-51.38,-40.26,-35.66,-40.36,-43.43,-43.04,-42.28,-41.47,-51.74,-39.21,-41.01,-39.48,-36.41,-40.53,-37.6,-29.09,-30.04,-36.68,-34.01,-36.79,-39.17,-24.34,-41.78,-31.48,-42.75,-22.91,-33.48,-37.21,-33.34,-37.8,-29.82,-30.29,-24.57,-26.89,-20.97,-36.8,-16.74,-40.39,-14.43,-30.4,-29.57,-25.39,-22.74,-30.81,-24.13,-27.12,-22.81,-34.47,-22.78,-32.17,-23.23,-20.6,-23.2,-25.83,-25.93,-16.76,-23.68,-15.18,-16.9,-21.18,-22.02,-11.62,-23.8,-19.31,-24.01,-9.87,-22.27,-13.74,-16.47,-7.79,-20.25,-12.35,-18.97,-3.92,-15.28,-10.45,-17.54,-8.71,-16.68,-7.99,-11.39,-7.7,-7.43,-3.19,-9.56,-3.36,-9.11,-4.06,-3.45,-8.28,-5.08,-4.57,1.9,-5.77,0.2,-5.06,4.1,-6.65,2.62,-4.75,6.97,-4.79,6.96,-1.71,8.11,-3.63,7.59</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B341" t="str">
+        <v>[R_19_标记]</v>
+      </c>
+      <c r="C341" t="str">
+        <v>a: 47.1ms -55.8uv b: 99.2ms 200.9uv</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B342" t="str">
+        <v>[L_19_名字]</v>
+      </c>
+      <c r="C342" t="str">
+        <v>FERG(19)_lCone</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B343" t="str">
+        <v>[L_19_放大器]</v>
+      </c>
+      <c r="C343" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B344" t="str">
+        <v>[L_19_闪光]</v>
+      </c>
+      <c r="C344" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B345" t="str">
+        <v>[L_19_闪光背景]</v>
+      </c>
+      <c r="C345" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B346" t="str">
+        <v>[L_19_采样]</v>
+      </c>
+      <c r="C346" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B347" t="str">
+        <v>[L_19_分析时间]</v>
+      </c>
+      <c r="C347" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B348" t="str">
+        <v>[L_19_数据长度]</v>
+      </c>
+      <c r="C348" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B349" t="str">
+        <v>[L_19_详细数据(uv)]</v>
+      </c>
+      <c r="C349" t="str">
+        <v>-13.37,-23.86,-14.49,-22.76,-16.61,-20.85,-19.3,-18.61,-22.03,-16.58,-24.24,-15.26,-25.49,-15,-25.54,-15.89,-24.43,-17.76,-22.42,-20.23,-19.98,-22.76,-17.67,-24.81,-16,-25.91,-15.33,-25.81,-15.8,-24.51,-17.28,-22.28,-19.41,-19.56,-21.67,-16.92,-23.52,-14.9,-24.47,-13.86,-24.29,-14.03,-22.93,-15.24,-20.67,-17.21,-17.96,-19.52,-15.4,-21.5,-13.26,-22.91,-12.53,-23.15,-13.26,-22.51,-14.8,-20.95,-18.08,-19.24,-20.13,-17.04,-24.62,-17.37,-26.38,-16.66,-29.24,-20.74,-29.47,-24.05,-30.07,-31.39,-34.99,-33.54,-32.76,-39.04,-33.38,-42.17,-39.37,-56.08,-45.64,-54.54,-51.97,-50.82,-54.62,-57.39,-55.63,-56.58,-67.43,-54.11,-68.82,-64.26,-77.01,-66.85,-79.03,-59.87,-56.95,-53.82,-61.98,-49.8,-48.21,-56.88,-43.66,-48.6,-41.42,-42.57,-29.55,-35.33,-30.18,-27.64,-25.96,-8.27,-16.23,-6.53,-2.47,16.61,5.62,30.68,21.47,38.93,21.46,52.65,51.67,64.18,53.59,62.2,78.45,88.47,82.6,96.45,91.45,111.54,117.65,103.07,144.48,133.04,140.19,142.6,134.93,168.95,168.57,173.99,143.71,202.45,175.08,200.12,212.26,200.97,215.95,203.03,208.57,216.23,214.14,247,232.86,235.07,270.34,201.43,252.86,276.7,235.22,265.6,224.18,219.42,277.06,215.99,251.96,278.17,243.96,255.73,208.58,289.98,249.6,271.11,229.97,227.53,255.4,244.87,207.88,225.16,216.95,209.51,191.45,186.6,176.4,166,202.56,206.67,187.32,190.15,193.21,138.2,148.42,153.7,131.46,155,148.63,135.81,107.27,129.24,124.32,113.27,111.54,100.25,91.04,72.32,68.55,83.92,79.3,55.81,62.84,50.87,54.94,43.18,41.33,45.83,34.76,28.86,29.68,31.68,23.07,32.32,12.98,26.09,16.09,23.29,12.47,17.31,9,11.74,7.59,5.37,2.96,-0.15,7.08,-3.68,1.67,-5.09,1.94,-10.38,-1.33,-9.03,-3.39,-7.41,-7.69,-8.1,-10.25,-6.2,-14.47,-4.87,-16.76,-7.1,-16.53,-8.62,-17.11,-11.77,-16.35,-13.75,-15.3,-18.91,-13.06,-18.47,-12.06,-21.49,-13.23,-23.56,-15.82,-22.17,-14.84,-22.19,-17.71,-21.16,-23.27,-18.4,-25.76,-18.77,-30.53,-18.14,-32.46,-20.58,-27.28,-20.31,-29.05,-26,-27.47,-26.21,-27.58,-36.01,-22.92,-37.46,-24.28,-30.55,-29.69,-38.78,-25.53,-31.24,-28.95,-34.8,-29.61,-28.74,-40.37,-34.67,-43.29,-23.66,-36.88,-30.3,-44.84,-27.68,-42.98,-29.75,-35.81,-38.45,-39.45,-46.79,-34.03,-44.8,-28.33,-40.54,-30.93,-49.48,-31.51,-38.46,-29.48,-45.69,-49.57,-42.6,-48.59,-41.29,-44.97,-38.37,-56.33,-34.37,-46.99,-47.09,-44.77,-35.97,-42.58,-51.42,-52.29,-54.43,-39.16,-49.85,-36.28,-55.69,-32.55,-43.34,-37.71,-50.77,-44.58,-40.07,-51.89,-46.68,-56.25,-42.04,-64.85,-55.11,-53.32,-40.53,-62.1,-47.32,-47.19,-59.08,-56.77,-57.26,-51.71,-59.74,-53.06,-55.01,-53.81,-61.62,-60.41,-72.51,-51.45,-62.65,-64.47,-52.39,-48.92,-66.19,-50.53,-52.08,-59.26,-61.34,-68.35,-47.04,-47.75,-46.08,-56.18,-53.03,-55.21,-53.04,-60.73,-44.53,-38.23,-48.33,-42.62,-56.05,-35.9,-48.24,-54.18,-56.8,-42.55,-45.64,-54.04,-43.21,-42.19,-41.35,-44.29,-40.86,-43.58,-34.77,-43.72,-36.27,-44.39,-36.98,-36.41,-34.82,-30.45,-30.82,-28.59,-36.42,-28.15,-43.69,-30.93,-38.51,-24.33,-43.84,-27.31,-27.33,-35.08,-28.77,-35.76,-26.2,-36.52,-20.4,-32.17,-27.82,-31.97,-24.12,-28.46,-28.43,-25.41,-28.92,-27.91,-22.34,-19.61,-32.42,-20.38,-32.1,-14.97,-29.61,-19.41,-25.17,-15.59,-24.5,-23,-20.01,-18.92,-21.31,-21.49,-19.29,-26.81,-12.37,-24.27,-13.63,-25.87,-14.24,-22.96,-14.66,-18.44,-19.72,-15.56,-17.39,-10.47,-22.16,-11.89,-18.42,-10.46,-20.84,-7.76,-17.17,-9.25,-15.54,-13.42,-12.09,-13.32,-7.7,-14.4,-4.05,-15.38,-3.42,-14.22,-3.24,-11.72,-4.09,-9.92,-6.57,-6.8,-8.66,-2.48,-10.64</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B350" t="str">
+        <v>[L_19_标记]</v>
+      </c>
+      <c r="C350" t="str">
+        <v>a: 47.2ms -58.1uv b: 99.2ms 190.2uv</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B351" t="str">
+        <v>[R_20_名字]</v>
+      </c>
+      <c r="C351" t="str">
+        <v>FERG(20)_lFlicker</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B352" t="str">
+        <v>[R_20_放大器]</v>
+      </c>
+      <c r="C352" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B353" t="str">
+        <v>[R_20_闪光]</v>
+      </c>
+      <c r="C353" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B354" t="str">
+        <v>[R_20_闪光背景]</v>
+      </c>
+      <c r="C354" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B355" t="str">
+        <v>[R_20_采样]</v>
+      </c>
+      <c r="C355" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B356" t="str">
+        <v>[R_20_分析时间]</v>
+      </c>
+      <c r="C356" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B357" t="str">
+        <v>[R_20_数据长度]</v>
+      </c>
+      <c r="C357" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B358" t="str">
+        <v>[R_20_详细数据(uv)]</v>
+      </c>
+      <c r="C358" t="str">
+        <v>-65.24,-49.54,-55.3,-51.82,-49.67,-38.88,-47.26,-47.53,-35.85,-39.77,-45.73,-43.12,-27.98,-48.46,-28.14,-34.22,-20.82,-30.21,-25.34,-28.08,-21.07,-21,-28.61,-14.88,-29.74,-13.73,-27.3,-10.42,-22.41,-6.97,-15.56,-10.18,-9.1,-4.68,-4.63,-12.88,2.7,-2.88,11.2,1.16,15.97,5.32,16.35,13.04,22.48,34.02,20.33,40.93,24.23,40.69,28.67,56.94,46.99,58.24,54.95,53.06,60.65,58.88,76.89,65.8,68.52,54.62,77.67,63.67,81.88,75.41,80.66,75.16,76.37,76.65,66.34,74.27,65.43,78.05,55.05,69.94,60.97,55.39,52.57,46,51.01,38.73,42.32,27.54,35.24,15.74,27.91,8.58,13.42,-0.83,1.46,-8.57,-12.94,-14.35,-26.89,-17.55,-40.36,-26.05,-47.03,-36.26,-52.96,-40.28,-50.74,-56.82,-54.41,-66.06,-56.46,-74.99,-63.39,-81.07,-61.48,-73.06,-63.97,-69.08,-63.98,-62.77,-64.35,-59.42,-66.72,-50.83,-74.15,-57.06,-64.62,-57.05,-65.23,-56.9,-54.07,-59.1,-54.68,-55.7,-30.95,-49.28,-34.8,-54.88,-33.5,-35.22,-32.73,-39.95,-36.51,-24.01,-38.42,-20.98,-34.37,-20.85,-33.85,-19.77,-34.24,-14.41,-26.61,-20.22,-22.55,-19.53,-15.99,-22.86,-11.77,-24.52,-7.58,-20.67,-2.58,-14.29,-1.49,-7.11,-5.09,1.88,-1.71,11.66,-6.82,13.09,5.7,19.55,-0.15,24.02,13.52,32.03,30.1,34.86,43.39,33.59,47.1,37.89,48.46,41.92,53.27,42.47,65.61,57,61.78,61.46,68.43,69.9,51.05,79.25,60.1,78.81,60.13,67.26,58.62,67.71,71.62,57.1,66.34,45.79,56.44,44.77,60.26,34.06,52.82,32.32,30.05,26.61,24.24,17.71,10.64,15.1,-1.98,6.56,-12.54,-4.09,-20.91,-14.82,-29.54,-30.3,-33.96,-43.84,-33.05,-52.98,-38.38,-60.35,-45.39,-63.24,-51.05,-70.42,-58.49,-71.53,-61.38,-61.49,-76.81,-56.63,-71.44,-63.25,-78.69,-57.06,-67.93,-61.75,-68.35,-60.65,-68.24,-68.84,-57.27,-65.5,-55.76,-60.57,-45.4,-62.17,-42.97,-64.4,-46.83,-57.27,-58.19,-40.22,-46.85,-34.77,-48.3,-40.6,-44.12,-35.82,-46.43,-37.66,-39.45,-36.69,-36.29,-34.61,-26.75,-42.21,-24.48,-38.14,-22.6,-32.34,-21.09,-28.88,-21.7,-19.14,-22.1,-13.83,-23.63,-10.76,-17.82,-1.62,-16.54,4.54,-2.5,6.61,6.61,5.83,14,9.29,18.79,17.1,25.43,20.93,37.13,30.03,39.26,31.21,44.05,45.21,48.15,63.51,58.96,72.8,52.72,73.98,53.26,73.84,63.29,64.89,73.8,72.34,73.06,65.91,81.01,65.55,81.57,60.6,64.25,52.76,59.68,53.58,50.29,47.19,32.19,41.66,21.41,33.57,16.03,22.89,2.33,10.02,-4.3,-0.91,-9,-18.56,-14.48,-30.43,-22.7,-40.77,-35.45,-50,-43.79,-53.49,-57.94,-58.38,-69.65,-62.03,-72.35,-63.31,-75.1,-70.86,-79.33,-69.69,-80.88,-78.71,-77.82,-75.45,-72.87,-84.84,-78.58,-88.94,-75.72,-89.03,-63.39,-70.42,-73.47,-81.72,-58.39,-61.38,-68.25,-60.88,-59.2,-52.72,-61.51,-49.98,-56.01,-36.04,-48.58,-42.1,-42.86,-44.2,-33.76,-48.6,-34.11,-42.78,-29.97,-41.19,-23.51,-42.06,-27.78,-37.1,-29.82,-30.07,-30.07,-22.98,-32.89,-19.23,-29.68,-12.45,-28.3,-10.86,-23.1,-11.58,-14.24,-11.03,-10.11,-15.05,-1.34,-7.58,9.79,3.15,11.35,3.17,24.91,12.8,19.59,23.66,15.75,37.62,19.43,38.04,33.78,40.71,40.37,44.32,46.58,45.94,44.86,55.66,60.98,47.57,63.19,52.94,67.19,44.4,63.32,53.47,64.22,61.37,59.81,48.31,44.04,49.43,37.89,57.4,28.92,45.32,23.5,34.21,19.88,28.26,14.58,12.05,9.33,-1.33,6.76,-15.46,-2.55,-24.48,-15.08,-32.64,-27.61,-38.67,-38.61,-44.38,-51.1,-42.82,-58.67,-48.63,-62.63,-55.38,-75.63,-63.43,-73.28,-69.12,-72.36,-84.32,-68.41,-79.66,-71.77,-79.13,-73.4,-87.5,-70.19,-76.9,-68.64,-71.64,-79.84,-63.69,-67.76,-73.21,-69.95,-48.8</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B359" t="str">
+        <v>[R_20_标记]</v>
+      </c>
+      <c r="C359" t="str">
+        <v>幅值: 61.1uv 相位: 35.6°</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B360" t="str">
+        <v>[L_20_名字]</v>
+      </c>
+      <c r="C360" t="str">
+        <v>FERG(20)_lFlicker</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B361" t="str">
+        <v>[L_20_放大器]</v>
+      </c>
+      <c r="C361" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B362" t="str">
+        <v>[L_20_闪光]</v>
+      </c>
+      <c r="C362" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B363" t="str">
+        <v>[L_20_闪光背景]</v>
+      </c>
+      <c r="C363" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B364" t="str">
+        <v>[L_20_采样]</v>
+      </c>
+      <c r="C364" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B365" t="str">
+        <v>[L_20_分析时间]</v>
+      </c>
+      <c r="C365" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B366" t="str">
+        <v>[L_20_数据长度]</v>
+      </c>
+      <c r="C366" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B367" t="str">
+        <v>[L_20_详细数据(uv)]</v>
+      </c>
+      <c r="C367" t="str">
+        <v>-83.72,-62.31,-71.11,-57.9,-80.93,-76.2,-78.55,-67.31,-66.24,-79.5,-64.24,-81.39,-69.12,-79.39,-59.2,-80.52,-56.05,-75.28,-57.56,-70.28,-54.52,-73.41,-47.11,-66.4,-47.24,-54.86,-45.35,-46.48,-35.55,-38.08,-28.68,-26.35,-27.98,-14.47,-15.94,-3.85,-14.07,3.76,-5.2,17.97,3.04,24.29,12.35,38.43,21.13,45.54,28.79,48.4,41.05,55.85,52.69,58.87,54.53,60.34,66.42,64.77,56.55,56.11,63.66,58.32,79.23,56.28,65.02,51.37,75.7,54.5,63.53,53.93,51.94,40.84,45.83,26.6,47.34,23.17,32.33,15.53,20.21,7.77,14.83,4.71,-3.78,-3.27,-9.28,-8.98,-24.41,-12.23,-33.01,-20.17,-39.72,-25.79,-50.76,-34.55,-56.14,-38.24,-52.83,-44.74,-60.77,-51.84,-62.9,-53.32,-61,-61.97,-59.03,-56.42,-58.54,-66.3,-59.85,-70.58,-60.85,-69.27,-53.93,-68.17,-56.65,-61.12,-44.43,-71.6,-55.1,-68.06,-47.74,-64.14,-53.34,-60.72,-55.79,-64.58,-64.52,-62.28,-58.31,-52.5,-64.44,-56.08,-70.79,-53.23,-61.15,-53.88,-67.52,-48.43,-64.63,-48.77,-68.54,-51.98,-62.78,-54.97,-62.85,-51.87,-59.22,-45.78,-52.05,-40.85,-43.81,-44.43,-37.56,-36,-29.62,-32.22,-21.48,-29.87,-13.6,-21.17,-2.13,-11.25,6.62,-4.29,14.81,3.76,20.82,12.67,25.64,17.98,30.77,23.79,41.42,43.05,51.29,55.71,44.91,48.67,55.76,62.03,61.84,69.17,62.85,75.38,63.68,70.95,52.85,68.49,54.01,69.77,47.21,61.52,54.63,59.52,43.43,56.43,49.5,41.82,38.9,31.63,32.87,22.89,33.03,12.22,24.2,3.96,18.87,2.2,12.67,-5.05,2.06,-15.72,-6.53,-28.55,-14.89,-30.7,-22.73,-33.19,-27.22,-36.46,-30.73,-42.89,-39.84,-42.16,-43.87,-42.7,-51.32,-38.71,-50.34,-43.25,-55.16,-38.5,-51.09,-43.09,-62.99,-40.46,-57.89,-44.61,-63.88,-38.14,-53.44,-42.53,-55.75,-42.22,-43.86,-49.7,-47.9,-55.88,-56.68,-52.96,-47.95,-57.64,-56.26,-69.91,-43.24,-58.67,-56.58,-70.12,-45.25,-60.71,-56.25,-72.39,-54.57,-61.2,-57.44,-59.02,-50.58,-59.55,-57.17,-57.43,-56.84,-55.78,-55.24,-49.62,-48.17,-39.5,-49.28,-37.71,-44.47,-23.3,-38.29,-15.38,-28.63,-9.88,-26.32,-3.25,-13.52,5.54,-5.79,10.06,4.36,18.95,18.19,24.34,34.82,31.18,37.07,44.2,54.07,54.98,63.91,58.85,74.12,57.37,81.3,66.42,77.98,60.93,71.51,76.96,84.13,71.34,74.77,71.19,75.44,74.92,78.46,71.81,67.16,67.87,66.51,65.61,49.96,53.41,46.52,45.34,37.71,39.14,20.75,32.54,15.57,20.42,5.27,19.16,-7.03,7.03,-15.23,-0.1,-14.24,-15.66,-21.33,-24.56,-23.12,-33.34,-30.75,-40.04,-32.07,-42.89,-34.07,-50.55,-38.97,-49.85,-37.7,-55.96,-43.17,-55.92,-45.65,-63.97,-47.15,-54.42,-41.13,-60.08,-52.09,-47.52,-58.86,-44.65,-51.18,-47.11,-58.99,-51.04,-58.92,-47.07,-60.73,-41.71,-61.3,-40.54,-62.55,-44.92,-52.3,-43.98,-62.87,-41.95,-57.5,-48.69,-62.26,-53,-61.97,-49.9,-54.37,-50.33,-51.62,-52.98,-44.47,-54.44,-45.94,-46.84,-42.64,-46.41,-27.51,-44.01,-25.62,-39.79,-20.3,-30.33,-13.76,-28.49,-6.33,-15.62,3.71,-5.42,4.54,5.65,10.78,17.27,22.19,30.43,25.32,41.3,28.27,48.18,35.96,62.67,44.65,72.36,45.56,73.09,57.55,77.4,68,75.15,71.28,77.47,64.98,79.32,71.58,84.64,87.25,83.8,80.95,77.56,76.79,66.69,73.14,66.26,61.92,56.98,56.86,36.93,60.21,41.35,51.31,32.26,35.13,23.66,24.22,11.8,20.73,1.6,5.57,2.6,0.65,-3.34,-11.89,-12.34,-22.9,-10.61,-30.26,-22.07,-35.68,-21.55,-38.96,-23.13,-40.17,-29.85,-45.78,-29.5,-46.1,-34.66,-47.55,-35.15,-40.36,-38.65,-40.62,-41.15,-37.08,-39.39,-30.3,-38.22,-43.54,-35.37,-32.39,-43.65,-25.99,-48.7,-30.6,-45.78,-32.73,-50.63,-23.69,-42.18,-37.93,-55.34</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B368" t="str">
+        <v>[L_20_标记]</v>
+      </c>
+      <c r="C368" t="str">
+        <v>幅值: 64.2uv 相位: 36°</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B369" t="str">
+        <v>[R_21_名字]</v>
+      </c>
+      <c r="C369" t="str">
+        <v>FERG(21)_lCone</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B370" t="str">
+        <v>[R_21_放大器]</v>
+      </c>
+      <c r="C370" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B371" t="str">
+        <v>[R_21_闪光]</v>
+      </c>
+      <c r="C371" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B372" t="str">
+        <v>[R_21_闪光背景]</v>
+      </c>
+      <c r="C372" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B373" t="str">
+        <v>[R_21_采样]</v>
+      </c>
+      <c r="C373" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B374" t="str">
+        <v>[R_21_分析时间]</v>
+      </c>
+      <c r="C374" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B375" t="str">
+        <v>[R_21_数据长度]</v>
+      </c>
+      <c r="C375" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B376" t="str">
+        <v>[R_21_详细数据(uv)]</v>
+      </c>
+      <c r="C376" t="str">
+        <v>1.48,10.16,1.01,7.54,6.69,2.07,10.92,1.88,8.19,7.7,2.82,11.82,2.88,8.93,8.8,3.63,12.75,3.9,9.68,9.88,4.42,13.62,4.86,10.33,10.84,5.08,14.35,5.66,10.81,11.61,5.54,14.84,6.24,11.04,12.13,5.75,15.06,6.55,10.99,12.37,5.69,15,6.58,10.67,12.33,5.36,14.67,6.37,10.11,12.06,4.82,14.13,5.97,9.36,11.61,4.13,13.44,5.45,8.5,11.06,3.37,12.65,4.85,7.55,10.45,2.51,11.78,4.16,6.57,9.67,1.49,10.61,3.02,5.01,8.12,0.07,9.24,1.52,2.16,6.26,-2.27,4.86,-1.77,-1.51,2.21,-8.66,1.79,-9.59,-8.66,-3.03,-14.19,-8.32,-17.32,-16.74,-11.39,-25.46,-19.64,-28.06,-31.29,-21.91,-34.26,-27.49,-43.78,-32.23,-27.15,-36.69,-41.48,-50.66,-51.14,-46.39,-52.97,-35.92,-49.09,-37.21,-36.11,-42.55,-26.73,-41.35,-21.87,-15.52,-33.29,-14.57,-22.85,-15.67,-8.82,-10.2,6.36,1.58,12.74,18.31,8.97,29.97,32.67,33.56,44.65,34.81,50.05,50.45,65.64,72.11,61.69,71.86,92.95,90.94,106.66,99.96,118.73,122.95,107.63,126.05,113.84,132.39,131.9,134.03,155.76,136.18,182.21,176.62,195.43,182.25,186.25,204.99,230.75,192.64,228.48,243.77,221.05,246.54,263.92,254.45,206.87,242.97,222.89,227.42,283.19,291.23,257.5,301.24,281.64,252.16,234.15,241.76,254.31,292.75,266.7,298.61,277.21,240.89,252.48,253.8,249.32,224.01,265.84,225.95,277.37,258.74,206.26,217.71,207.45,205.1,208.77,199.02,187.01,181.51,193.8,167.65,190.42,181.16,154.25,179.63,148.76,157.52,137.98,148.52,123.46,124.93,122.5,123.82,116.14,111.89,87.23,99.58,101.33,79.09,80.04,64.34,73.44,74.29,52.38,59.79,50.12,49.24,50.68,39.19,44.6,41.25,36.97,37.68,29.83,36.06,28.51,26.36,27.85,21.68,26.72,19.47,19.36,22.47,13.14,20.68,14.54,15.89,18.24,9.42,18.19,10.11,12.23,15.33,5.33,14.5,7.55,10.2,14.01,4.88,12.35,6.91,8.31,11.63,4.49,13.65,4.82,7.9,11.88,4.37,11.61,5.33,5.26,10.96,3.86,12.47,4.62,3.84,10.61,0.79,11.95,4.35,3.35,8.77,0.62,11.76,3.39,4.01,7.91,-1.7,7.88,0.69,2.78,5.64,1.52,6.82,5.75,4.49,7.14,0.85,4.96,3.53,1.48,5.89,-1.44,-0.43,-4.26,-2.5,1.76,-7.49,0.56,0.25,-2.3,-1.82,-12.17,-0.29,-12.31,-12.91,-6.82,-16.1,-2,-10.19,-13.71,-11.4,-18.27,-4.85,-17.68,-22.44,-6.53,-18.41,-15.65,-12.42,-26.19,-5.25,-20.29,-9.21,-25.13,-25.08,-14.27,-15.4,-22.72,-26.85,-26.49,-14.07,-18.17,-22.7,-15.04,-24.3,-10.64,-30.97,-31.33,-25.57,-34.11,-19.45,-18.48,-24.21,-19.82,-21.02,-20.6,-35.85,-13.02,-20.47,-26.51,-28.39,-34.75,-35.44,-14.6,-22.24,-13.2,-32.72,-20.01,-27.37,-34.07,-26.29,-29.57,-16.06,-27.82,-20.04,-17.09,-36.32,-24.2,-27.38,-23.4,-23.02,-33.47,-21.11,-11.41,-37.29,-13.81,-22.38,-24.2,-20.95,-36.17,-17.66,-17.71,-24.53,-11.02,-19.58,-23.53,-27.09,-24.5,-32.59,-38.91,-26.12,-35.72,-21.6,-23.32,-34.61,-27.61,-28.98,-17.45,-28.48,-17.05,-22.6,-31.5,-19.8,-17.87,-20.15,-7.74,-15.2,-17.12,-9.95,-16.99,-17.79,-12.66,-13.76,-11.88,-17.1,-11.26,-17.13,-15.1,-13.1,-16.4,-11.64,-10.9,-21.3,-0.66,-13.69,-6.86,-14.32,-12.43,-11.23,-14.39,-3.46,-5.65,-7.28,-3.57,-6.45,3.24,-7.34,-0.27,1.84,-2.62,3.89,0.13,-0.32,2.64,-4,4.09,2.36,-1.33,12.57,-1.11,4.39,5.13,5.22,6.86,3.11,13.93,5.03,7.25,14.28,7.59,13.96,10.95,7.53,14.16,5.62,14.95,13.9,11.71,18.38,8.27,17.25,11.8,10.97,19.64,6.93,15.1,12.78,11.04,19.61,10.84,18.27,12.92,10.75</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B377" t="str">
+        <v>[R_21_标记]</v>
+      </c>
+      <c r="C377" t="str">
+        <v>a: 51.4ms -46.8uv b: 106.5ms 214.4uv</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B378" t="str">
+        <v>[L_21_名字]</v>
+      </c>
+      <c r="C378" t="str">
+        <v>FERG(21)_lCone</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B379" t="str">
+        <v>[L_21_放大器]</v>
+      </c>
+      <c r="C379" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B380" t="str">
+        <v>[L_21_闪光]</v>
+      </c>
+      <c r="C380" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B381" t="str">
+        <v>[L_21_闪光背景]</v>
+      </c>
+      <c r="C381" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B382" t="str">
+        <v>[L_21_采样]</v>
+      </c>
+      <c r="C382" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B383" t="str">
+        <v>[L_21_分析时间]</v>
+      </c>
+      <c r="C383" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B384" t="str">
+        <v>[L_21_数据长度]</v>
+      </c>
+      <c r="C384" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B385" t="str">
+        <v>[L_21_详细数据(uv)]</v>
+      </c>
+      <c r="C385" t="str">
+        <v>15.63,-6.24,10.98,3.22,0.25,13.96,-6.28,16.39,-2.13,8.71,9.33,-1.43,18.04,-4.05,16.52,3.91,6.84,15.72,-1.36,21.14,0.22,15.81,10.81,5.38,21.26,0.17,22.54,5.66,14.07,17.32,4.26,24.86,2.65,21.71,11.2,11.13,22.24,3.31,25.76,5.27,18.42,15.49,7.2,24.43,2.01,23.31,7.32,12.48,17.33,1.53,23.02,-0.77,16.19,7.3,4.42,16.05,-5.5,15.41,-4.96,7.04,5.89,-8.57,8.12,-15.49,7.36,-12.32,-6.9,-4.45,-18.14,-0.43,-26.2,-13.23,-21.67,-21.4,-16.19,-29.06,-19.73,-32.9,-19.9,-20.27,-38.85,-24.52,-47.92,-27,-33.04,-28.94,-20.23,-52.98,-12.26,-38.14,-37.41,-34.31,-29.48,-20.39,-35.32,-10.31,-32.47,-21.31,-2.87,-19.57,11.89,-9.01,-1.61,3.69,-5.19,20.42,7.17,36.77,20.55,30.32,38.41,37.84,53.88,41.27,66.34,66.68,82.65,83.16,74.97,107.65,86.86,102.96,101.06,101.39,146.21,111.41,140.75,136.28,146.84,167.62,165.27,195.57,168.15,175.64,204.92,163.65,225.92,188.77,230.83,195.99,218.86,207.05,219.97,234.35,202.5,266.81,234.8,274.95,252.25,215.22,292.78,272.72,285.47,224.61,248.21,265.85,243.39,277.35,256.96,249.55,303.37,245.3,272.19,284.71,281.97,252.98,293.78,260.05,271.93,296.67,270.18,300.78,277.31,233.91,234.11,275.5,250.52,244.14,255.88,217.09,233.19,230.71,210.25,208.99,206.17,213.93,208.59,205.15,216.45,187.71,200.52,217.33,201.97,219.79,184.74,206.84,179.16,172.8,179.97,138.59,169.64,137.84,143.93,121.2,134.83,132.07,120.69,123.24,116.97,121.83,102.77,88.09,122.74,89.01,100.78,80.18,97.81,86.46,73.09,91.64,58.49,81.66,61.22,62.33,67.1,52.32,72.84,41.69,48.21,55.31,42.11,54.56,32.53,47.96,34.89,30.08,42.79,23.84,42.33,15.86,28.67,23.55,17.53,32.91,5.69,30.29,9.86,17.59,20.61,1.88,22.24,-1.55,17.54,7.04,5.94,16.03,-4.9,17.73,-3.5,9.42,5.33,-4.99,14.07,-9.3,11.09,-2.19,0.73,8.11,-10.58,13.16,-9.75,8.2,-0.15,-7.35,6.72,-10.12,6.61,-11.84,1.33,2.74,-7.23,8.69,-9.7,3.61,-9.09,-4.83,4.63,-10.84,13.18,-15.52,-0.19,-2.74,-3.76,11.1,-11.61,9.22,-6.29,-0.48,-3.43,-16.8,12.27,-18.96,5.5,-6.88,-11.52,2.68,-14.52,4.42,-16.32,-2.27,0.32,-12.1,-1.24,-26.81,4.72,-12.91,-15.38,-5.92,-25.12,-8.91,-24.54,-14.86,-20.32,-25.09,-17.79,-25.91,-14.48,-27.41,-16.2,-25.67,-22.97,-16.29,-41.37,-20.09,-37.83,-26.93,-21.56,-36.28,-22.9,-46.14,-23.89,-26.8,-28.37,-22.41,-44.38,-22.75,-41.26,-38.18,-35.24,-44.26,-15.31,-35.14,-25.05,-46.85,-37.93,-28.46,-36.53,-29.84,-46.04,-38.98,-28.69,-46.46,-22.74,-40.46,-16.91,-30.77,-29.64,-24.12,-44.92,-20.04,-32.13,-16.42,-33.91,-39.16,-30.29,-30.81,-30.43,-29.45,-22.86,-20.3,-27.13,-20.68,-39.54,-13.54,-24.39,-26.58,-22.65,-26.76,-9.6,-23.41,-28.27,-13.39,-34.14,-18.76,-29.62,-15.85,-33.32,-14.49,-19.05,-36.36,-16.14,-35.31,-15.77,-24.4,-17.41,-18.33,-23.17,-10.55,-18.89,-17.98,-20.77,-24.95,1.81,-37.07,-16,-27.35,-12.72,-8.06,-33.46,-1.71,-25.33,-15.32,-11.79,-16.9,-6.68,-30.56,-7.81,-27.74,-11.85,-17,-24.99,-5.2,-30.31,-8.44,-15.04,-14.98,-8.67,-26.41,3.4,-26.1,-2.75,-9.78,-13.44,-3.04,-20.81,2.54,-16.88,-8.7,-0.85,-12.39,10.47,-16.55,1,-2.5,-3.61,7.27,-11.7,14.42,-6.17,8.72,6.54,-0.3,16.74,-6.86,17.99,-2.26,4.93,11.4,-3.45,21.42,0.18,16.67,9.94,9.1,20.98,-0.04,23.79,6.37,15.7,16.26,4.69,25.84,2.5,22.89,10.82,14.91,23.23,6.11,26.51,6.59,21.99,15.34,11.17,25.92,4.5,25.19,8.47,15.38,17.54,4.4</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B386" t="str">
+        <v>[L_21_标记]</v>
+      </c>
+      <c r="C386" t="str">
+        <v>a: 51.4ms -49.3uv b: 106.5ms 191.6uv</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B387" t="str">
+        <v>[R_22_名字]</v>
+      </c>
+      <c r="C387" t="str">
+        <v>FERG(22)_lFlicker</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B388" t="str">
+        <v>[R_22_放大器]</v>
+      </c>
+      <c r="C388" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B389" t="str">
+        <v>[R_22_闪光]</v>
+      </c>
+      <c r="C389" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B390" t="str">
+        <v>[R_22_闪光背景]</v>
+      </c>
+      <c r="C390" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B391" t="str">
+        <v>[R_22_采样]</v>
+      </c>
+      <c r="C391" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B392" t="str">
+        <v>[R_22_分析时间]</v>
+      </c>
+      <c r="C392" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B393" t="str">
+        <v>[R_22_数据长度]</v>
+      </c>
+      <c r="C393" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B394" t="str">
+        <v>[R_22_详细数据(uv)]</v>
+      </c>
+      <c r="C394" t="str">
+        <v>-54.24,-54.73,-51.57,-45.11,-58.75,-43.57,-50.28,-51.24,-39.3,-42.13,-50.53,-33.63,-42.04,-44.92,-33.23,-41.5,-36.26,-24.02,-33.46,-27.89,-15.7,-27.43,-21.19,-4.17,-17.11,-12.54,2.28,-2.51,2.26,15.65,-0.54,13.5,21,16.63,18.72,32.27,30.47,30.43,44.03,34.43,53.59,51.56,46.52,62.27,63.35,51.57,64.07,73.74,60.28,69.4,62.41,63.55,72,58.36,50.61,70.4,64.49,50.94,58.99,49.19,50.52,51.7,38.9,30.36,36.38,27.09,23.4,23.51,9.19,3.74,15.97,0.36,-7.11,0.14,-18.91,-18.01,-14.18,-28.25,-30.79,-25.79,-39.5,-40.72,-39.5,-49.98,-49.14,-47.4,-59.16,-55.57,-58.23,-71.59,-62.72,-63.25,-77.29,-64.95,-67.75,-74.25,-67.87,-60.24,-68.46,-56.44,-68.22,-74.85,-51.84,-56.49,-78.12,-59.45,-60.9,-73.06,-60.66,-64.25,-66.17,-46.72,-59.53,-68.54,-56.98,-61.63,-56.41,-40.64,-52.42,-54.04,-44.47,-55.91,-51.81,-43.22,-61.56,-53.39,-42.66,-59.95,-49.81,-35.29,-56.16,-45.92,-41.18,-55,-43.02,-39.93,-48.96,-43.01,-34.58,-47.05,-35.61,-28.17,-42.08,-25.74,-24.42,-31.64,-19.31,-18.16,-22.31,-12.38,-14.81,-14.43,4.88,4.38,-3.05,7.78,10.75,9.36,26.79,20.07,24.4,41.29,37.43,30.1,53.23,42.03,41.29,55.3,55.2,42.27,68.67,58.14,58.05,67.69,51.88,65.92,77.04,64.4,65.19,67.4,51.67,68.37,64.9,46.99,63.86,52.31,43.93,50.4,56.22,28.37,39.9,41.5,25.19,26.13,27.91,6.65,11.57,5.38,-2.97,0.8,-6.4,-23.27,-14.47,-17.44,-32.07,-23.36,-31.77,-47.94,-36.71,-50.05,-55.62,-44.59,-57.98,-65.63,-50.61,-66.68,-65.81,-55.31,-60.88,-71.87,-64.07,-70.56,-70.27,-59.92,-68.3,-64.4,-64.1,-77.26,-66.07,-61.79,-67.01,-67.84,-57.89,-61.92,-55.83,-47.1,-75.87,-49.86,-51.75,-65.83,-48.7,-49.2,-60.68,-65.03,-48.85,-55.45,-56.78,-53.14,-62.02,-48.3,-50.73,-51.06,-49.65,-50.22,-55.56,-42.49,-46.78,-57.79,-36.15,-45.84,-49.46,-38.24,-39.78,-46.76,-31.71,-34.36,-40.06,-21.9,-26.85,-25.8,-9.72,-21.72,-16.45,-4.02,-9.75,-7.3,10.84,-4.04,2.26,13.69,10.08,12.07,36.64,16.68,27.72,46.19,26,47.95,55.85,49.3,47.25,60.58,51.35,61.79,63.35,64.96,70.43,77.07,56.94,68.53,76.01,68.3,80.33,77.42,55.8,63.09,63.67,50.62,62.59,54.79,52.96,60.01,49.94,32.49,40.88,37.18,26.3,33.79,17.44,6.34,13.14,2.41,-6.24,3.8,-11.06,-18.03,-13.67,-32.49,-30.31,-27.35,-44.6,-38.78,-38.54,-54.16,-52.99,-45.91,-60.72,-60.67,-50.03,-66.14,-58.72,-62.41,-72.3,-70.48,-57.4,-70.35,-67.81,-58.83,-76.43,-63.13,-61.07,-77.51,-54.2,-55.77,-62.75,-60.4,-60.55,-64.98,-49.86,-50.21,-68.83,-55.18,-65.19,-65.49,-41.56,-46.98,-48.16,-32.12,-60.42,-50.81,-39.95,-53.36,-54.77,-38.05,-47.43,-50.47,-40.86,-49.46,-40.43,-38.75,-45.91,-41.97,-32.64,-42.96,-41.03,-28.6,-45.81,-36,-24.66,-43.21,-31.49,-20.62,-30.23,-25.48,-13.8,-26.1,-11.9,-8.52,-17.69,-3.31,-1.9,-10.27,2.84,10.26,2.64,14.12,24.03,17,38.01,31.45,28.84,45.23,31.47,29.7,48.81,41.58,54.78,66.36,54.58,49.23,71.52,51.72,67.4,76.43,60.35,54.63,69.91,67.27,70.78,68.07,62.7,59.85,61.63,57.34,52.74,64.95,46.72,49.47,48.78,30.22,39.22,37.26,18.52,27.6,25.96,1.7,12.85,9.73,-8.89,0.03,-3.62,-18,-10.29,-21.78,-30.25,-23.18,-31.14,-48.68,-33.1,-44.82,-54.08,-45.67,-50.06,-57.15,-47.71,-59.73,-59.86,-49.81,-65.45,-61.63,-58.1,-61.41,-65.23,-56.65,-69.2,-67.22,-47.84,-58.15,-56.3,-57.45,-69.85,-54.09,-57.25,-55.66,-51.4,-42.48,-53.33,-49.07,-49.18,-57.52,-53.7,-41.51,-57.56,-38.41,-46.56,-60.42,-48.05,-45.96,-65.25,-48.61</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B395" t="str">
+        <v>[R_22_标记]</v>
+      </c>
+      <c r="C395" t="str">
+        <v>幅值: 63.5uv 相位: 36.6°</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B396" t="str">
+        <v>[L_22_名字]</v>
+      </c>
+      <c r="C396" t="str">
+        <v>FERG(22)_lFlicker</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B397" t="str">
+        <v>[L_22_放大器]</v>
+      </c>
+      <c r="C397" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B398" t="str">
+        <v>[L_22_闪光]</v>
+      </c>
+      <c r="C398" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B399" t="str">
+        <v>[L_22_闪光背景]</v>
+      </c>
+      <c r="C399" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B400" t="str">
+        <v>[L_22_采样]</v>
+      </c>
+      <c r="C400" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B401" t="str">
+        <v>[L_22_分析时间]</v>
+      </c>
+      <c r="C401" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B402" t="str">
+        <v>[L_22_数据长度]</v>
+      </c>
+      <c r="C402" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B403" t="str">
+        <v>[L_22_详细数据(uv)]</v>
+      </c>
+      <c r="C403" t="str">
+        <v>-45.81,-35,-41.98,-25.24,-27.12,-21.53,-11.51,-15.72,-10.92,0.94,-6.57,6.98,13.14,10,24.85,23.7,27.45,38.62,39.08,44.17,54.43,50.68,64.34,61.1,61.97,70.52,75.63,66.03,87.11,79.69,74.15,91.88,73.55,76.77,85.15,68.88,80.7,89.6,77.08,94.7,78.49,74.32,80.6,68.77,70.86,73.27,63.75,65.08,57.74,49.33,63.25,59.33,44.84,53.72,50.98,40.96,45.52,26.16,31.37,31.68,20.09,28.46,24.69,18.01,19.57,18.75,11.09,22.86,8.07,9.46,15.44,1.01,7.11,6.59,0,7.43,0.85,-1.92,6.41,-5.96,-0.91,1.5,-5.54,-1.79,-8.39,-15.28,-5.12,-7.99,-23.18,-9.73,-25.18,-13.52,-15.3,-28.64,-22.22,-15.17,-32.77,-24.75,-30.7,-31.8,-20.84,-46.32,-39.45,-44.3,-47.4,-40.36,-40.23,-48.34,-52.64,-53.66,-60.63,-41.63,-47.28,-65.31,-48.88,-62.09,-46.5,-47.02,-56.35,-52.31,-49.72,-56.91,-39.17,-47.15,-45.36,-28.02,-37.13,-32.23,-19.15,-29.48,-19.58,-13.98,-20.18,-6.01,-4.23,-4.67,9.26,7.1,11.53,23.24,19.68,27.11,38.14,32.15,43.2,51.87,46.41,58.54,62.91,62.01,77.02,65.37,67.62,73.27,66.93,71.53,79.08,74.18,85.67,88.34,73.02,76.69,80.97,76.56,79.71,69,76.05,76.47,60.04,75.54,63.48,59.72,75.14,55.97,57.03,67.05,41.42,59.7,53.06,44.98,47.33,38.14,36.39,38.68,30.38,24.21,34.86,22.23,22.02,26.01,18,15.62,14.53,8.74,20.43,10.43,7.21,13.86,6.41,5.87,11.43,0.2,5.37,7.34,-2.76,3.18,3.72,-10.51,1.18,-6.73,-9.66,-8.41,-6.72,-12.87,-6.35,-24.13,-12.18,-16.63,-24.21,-16.57,-26.95,-28.43,-23.4,-39.95,-29.75,-38.44,-51.71,-33.32,-40.4,-58.24,-38.44,-47.92,-48.39,-41.64,-56.67,-55.83,-56.51,-68.47,-57.37,-56.34,-70.47,-52.39,-63.87,-56.43,-52.99,-49.87,-61.43,-41.15,-49.95,-43.48,-35.09,-49.83,-29.2,-32.25,-30.69,-21.28,-18.28,-22,-5.38,-9.18,-1.53,7.53,3.17,16.27,20.73,18.77,33.4,35.63,34.77,45.49,43.9,47.29,62.18,55.78,60.68,74.24,70.87,73.28,76.27,73.94,86.2,84.08,77.95,96.54,78.14,84.62,87.01,84.16,85.06,88.9,73.05,78.5,75.28,78.28,81.4,74.31,69.85,74.39,64.85,71.21,63.63,50.2,56.25,51.53,38.12,43.57,40.27,41.47,37.17,28.08,24.67,26.45,22.85,26.32,17.85,8.48,17.25,13.69,7.3,12.09,4.41,6.89,10.58,-1.05,5.12,2.71,-5.76,3.15,-4.89,-8.25,-0.97,-12.85,-4.89,-3.4,-12.27,-4.27,-10.21,-16.37,-14.54,-22.82,-22.83,-14.12,-22.23,-22.24,-19.47,-43.66,-39.44,-33.81,-40.21,-40.47,-39.28,-39.18,-39.13,-49.39,-42.78,-37.04,-56.55,-48.56,-49.93,-63.03,-58.79,-58.06,-69.55,-47.02,-62.65,-53.73,-50.21,-52.02,-53.46,-54.93,-52.81,-44.49,-45.22,-51.9,-37.86,-39.99,-40.83,-26.67,-32.54,-23.51,-15.76,-24.59,-12.76,-4.67,-6.69,5.83,8.3,7.65,22.14,18.19,23.47,37.47,33.15,40.17,48.56,41.78,56.63,56.47,57.83,61.96,64.52,71.18,82.25,72.49,81.91,76.75,70.49,82.95,74.3,70.69,77.36,85.23,77.96,81.72,80.57,66.21,81.04,66.95,72.43,71.19,62.66,61.04,59.14,52.44,57.9,48.84,44.77,55.44,40.49,48.47,42.23,32.73,30.37,30.77,16.65,30.09,27.48,21.03,31.51,14.11,9.11,16.09,4.47,14.09,12.14,0.3,9.48,4.42,-0.23,8.89,-0.68,0.61,5.83,-3.46,3.23,0.48,-5.07,-3.63,-1.29,-4.68,-9.52,-13.92,-8.06,-12.62,-19.76,-8.95,-5.86,-28.86,-26.54,-22.17,-32.69,-23.45,-31.32,-30.32,-31.25,-48.83,-39.2,-43.77,-41.34,-42.5,-45.53,-61.96,-41.23,-53.99,-52.49,-46.81,-59,-64.36,-62.73,-61.64,-51.08,-51.41,-55.05,-61.95,-46.94,-55.22,-45.02,-50.56,-53.29,-40.52</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B404" t="str">
+        <v>[L_22_标记]</v>
+      </c>
+      <c r="C404" t="str">
+        <v>幅值: 61.6uv 相位: 36.3°</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B405" t="str">
+        <v>[R_23_名字]</v>
+      </c>
+      <c r="C405" t="str">
+        <v>FERG(23)_lCone</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B406" t="str">
+        <v>[R_23_放大器]</v>
+      </c>
+      <c r="C406" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B407" t="str">
+        <v>[R_23_闪光]</v>
+      </c>
+      <c r="C407" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B408" t="str">
+        <v>[R_23_闪光背景]</v>
+      </c>
+      <c r="C408" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B409" t="str">
+        <v>[R_23_采样]</v>
+      </c>
+      <c r="C409" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B410" t="str">
+        <v>[R_23_分析时间]</v>
+      </c>
+      <c r="C410" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B411" t="str">
+        <v>[R_23_数据长度]</v>
+      </c>
+      <c r="C411" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B412" t="str">
+        <v>[R_23_详细数据(uv)]</v>
+      </c>
+      <c r="C412" t="str">
+        <v>-16.19,-6.73,-12.64,-19.6,-10.82,-7.13,-17.25,-16.94,-6.91,-11.12,-19.55,-12.16,-6.7,-16.36,-18.25,-8.07,-10.38,-19.94,-14.23,-7.22,-16.01,-19.99,-10.06,-10.36,-20.62,-16.8,-8.5,-16.03,-21.91,-12.6,-10.84,-21.34,-19.54,-10.25,-16.17,-23.67,-15.33,-11.56,-21.82,-22.08,-12.19,-16.25,-25.05,-18.02,-12.41,-21.97,-24.26,-14.28,-16.39,-25.95,-20.55,-13.48,-22.3,-26.56,-16.79,-17.24,-27.66,-23.97,-15.81,-24.53,-31.3,-22.47,-19.15,-30.86,-32.06,-21.34,-30.86,-37.43,-31.34,-26.19,-40.96,-41.4,-30.16,-35.01,-47.91,-42.29,-34.72,-47.11,-52.82,-49.14,-56.62,-63.15,-60.7,-51.4,-69.14,-62.52,-66.3,-68.24,-65.84,-64.48,-63.56,-56.22,-60.47,-70.05,-46.63,-67.07,-64.41,-53.43,-49.41,-63.21,-42.48,-44.72,-41.61,-42.05,-32.82,-24.34,-31.48,-14.97,-11.94,-10.25,-10.3,10.97,6.66,5.16,13.2,25.29,22.28,17.59,32.61,44.11,50.83,62.15,64.39,73.12,65.56,97.03,84.82,103.54,102.92,104.09,128.6,105.96,110.26,123.5,137.8,144.88,136.11,136.57,129.75,144.1,190.26,150.03,159.29,203.7,231.37,209.43,236.67,214.87,246.62,201.75,225.67,247.73,248.5,265.31,254.4,273.76,230.72,231,266.09,224.32,287.75,282.38,297.8,227.91,284.08,262.3,243.6,252.86,296.06,234.75,230.6,242.15,265.9,217.13,258.27,253.37,235.81,253.16,225.36,252.19,190.62,217.17,235.05,192.82,169.93,177.62,186.65,173.69,156.81,148.61,155.47,159.86,140.89,123.15,131.76,133.85,125.36,106.75,103.29,82.9,87.69,94.37,93.03,90.37,79.71,78.18,70.91,58.58,50.5,36.48,51.95,42.84,32.67,35.46,36.45,29.25,19.27,23.57,29.07,16.36,9.54,12.4,14.86,2.98,3.09,6.52,1.89,-5.82,-0.98,2.31,-8.45,-13.52,-1.68,-5.73,-16.64,-14.04,-5.37,-15.43,-19.25,-12.27,-10.94,-20.59,-18.3,-9.68,-16.49,-23.9,-15.29,-13.79,-23.34,-20.91,-13.53,-18.61,-25.55,-16.52,-13.21,-23.92,-24.76,-14.77,-16.86,-29.06,-22.06,-15.27,-25.02,-26.47,-14.6,-19.34,-27.17,-23.11,-14.9,-26.38,-26.92,-20.51,-19.13,-30.94,-27.85,-18.25,-28.51,-31.82,-23.75,-17.39,-33.29,-28.6,-24.73,-27.32,-36.8,-24.02,-25.84,-35.98,-38.53,-26.54,-30.75,-39.61,-32.63,-33.15,-34.73,-38.52,-37.45,-37.76,-47.75,-37.9,-27.92,-44.74,-53.35,-34.83,-33.57,-50.26,-47.85,-31.52,-47.32,-58.15,-41.01,-35.2,-49.58,-57.39,-44.01,-53.63,-59.43,-49.01,-36.15,-52.93,-48.07,-40.75,-45.59,-65.64,-55.37,-38.62,-54.46,-52.39,-51.98,-54.52,-64.38,-60.7,-39.66,-64.8,-54.29,-54.88,-46.47,-67.35,-67.97,-41.86,-46.29,-58.85,-50.86,-57.4,-69.24,-50.81,-41.22,-53.55,-70.77,-58.82,-53.09,-63.87,-59.38,-47.16,-46.52,-55.11,-59.16,-64.34,-50.17,-77.31,-51.18,-50.08,-72.36,-58.75,-54.95,-59.87,-65.21,-51.49,-60.07,-58.94,-62.76,-57.24,-66.71,-76.72,-67.17,-64.28,-70.66,-66.4,-43.93,-54.5,-70.06,-54.15,-55.12,-74.65,-77.22,-50.95,-57.88,-66.35,-66.41,-55.08,-62.3,-72.33,-48.5,-56.95,-61.26,-71.25,-47.12,-69.59,-74.19,-61.55,-62.79,-53.56,-60.26,-45.44,-60.97,-66.91,-47.06,-46.12,-56.61,-58.72,-53.33,-45.46,-60.89,-42.54,-50.75,-58.02,-57.4,-50.54,-41.83,-55.16,-46.18,-32.31,-54.54,-57.24,-36.7,-43.68,-54.98,-51.3,-29.67,-34.74,-49.16,-43.34,-29.67,-41.89,-38.58,-34.03,-32.02,-46.22,-28.59,-33.4,-36.76,-34.74,-24.88,-29.93,-34.19,-34.93,-23.14,-28.24,-31.88,-24.88,-22.06,-30.88,-26.58,-24.16,-24.91,-32.81,-26.13,-18.32,-33.49,-27.13,-20.19,-22.86,-33.41,-19.75,-19.95,-28.62,-27.22,-16.33,-21.11,-32.65,-24.42,-16.87,-28.79,-28.04,-17.3,-22.94,-29.39,-22.7,-15.68,-27.85,-29.49,-18.93,-19.48,-27.88,-24.78,-17.81,-23.96,-28.58,-20.27,-18.56,-27.67,-25.42,-15.61,-21.93,-29.8,-20.11,-16.95,-26.4,-25.51,-15.83</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B413" t="str">
+        <v>[R_23_标记]</v>
+      </c>
+      <c r="C413" t="str">
+        <v>a: 55.5ms -51.5uv b: 112.9ms 190.4uv</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B414" t="str">
+        <v>[L_23_名字]</v>
+      </c>
+      <c r="C414" t="str">
+        <v>FERG(23)_lCone</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B415" t="str">
+        <v>[L_23_放大器]</v>
+      </c>
+      <c r="C415" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B416" t="str">
+        <v>[L_23_闪光]</v>
+      </c>
+      <c r="C416" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B417" t="str">
+        <v>[L_23_闪光背景]</v>
+      </c>
+      <c r="C417" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B418" t="str">
+        <v>[L_23_采样]</v>
+      </c>
+      <c r="C418" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B419" t="str">
+        <v>[L_23_分析时间]</v>
+      </c>
+      <c r="C419" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B420" t="str">
+        <v>[L_23_数据长度]</v>
+      </c>
+      <c r="C420" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B421" t="str">
+        <v>[L_23_详细数据(uv)]</v>
+      </c>
+      <c r="C421" t="str">
+        <v>-0.12,-2.83,15.19,6.92,-5.16,11.45,13.31,-4.07,5.66,17.08,0.24,-0.13,17.07,6.39,-3.93,13.33,12.37,-4.47,7.08,16.14,-1.66,0.32,16.33,3.46,-4.87,12.71,8.99,-6.94,6.27,12.85,-5.45,-1.1,13.5,-1.19,-7.24,10.42,4.14,-10.4,4.33,8.45,-9.84,-3.05,9.99,-6.07,-9.56,7.97,-0.63,-13.31,2.75,4.44,-13.41,-4.24,7.06,-9.97,-10.75,6.25,-4.35,-15.34,2.01,0.73,-16.36,-5.26,3.79,-14.15,-13.39,3.58,-9.41,-18.39,-2.45,-4.9,-22.41,-12.45,-5.74,-25.56,-18.29,-10.11,-25.08,-28.59,-14.28,-25.09,-34.59,-23.44,-17.83,-44.07,-40.03,-26.31,-40.91,-43.78,-29.39,-43.78,-61.82,-43.96,-31.94,-60.11,-57.92,-34.42,-47.19,-62.88,-38.36,-47.4,-62.81,-31.71,-36.33,-43.49,-26.73,-15.18,-32.13,-37.21,-15.24,-23.09,-15.06,-6.66,-2.21,-8,16.6,23.1,4.12,18.41,37.12,30.83,24.35,59.89,42.85,33.11,57.88,71.6,67.1,70.58,89.96,82.5,82.46,100.92,90.9,82.89,137,147.88,112.21,152.15,134.99,150.02,138.47,177.94,142.68,162.2,163.63,179.73,163.99,172.25,192.43,176.54,209.32,247.02,215.7,252,251.46,267.34,215.71,283.93,245.24,235.05,240.22,291.96,251.85,224.99,317.42,240.88,238.71,302.68,266.83,248.31,277.93,284.23,255.5,241.46,272.37,278.82,260.72,293.93,249.27,265.65,221.36,257.31,223.84,226.65,207.02,248.45,208.68,225.03,237.48,213.36,216.4,189.48,189.66,150.48,184.2,141.52,135.08,163.59,130.6,123.32,125.31,127.69,109.22,100.6,118.23,96.47,85.14,85.8,90.61,74.89,82.27,80.94,57.22,58.27,59.04,40.34,43.48,47.57,41.98,22.3,42.66,39.21,16.09,23.73,32.19,14.12,10.22,26.68,11.65,2.13,15.51,13.79,-2.58,7.39,15.05,-2.65,-1.85,12.07,1.02,-10.63,6.81,5.75,-12.64,0.33,7.73,-10.17,-6.82,9.26,-4.98,-12.41,6.4,0.88,-14.36,-0.97,4.45,-12.84,-6.92,7.16,-8.62,-11.63,7.19,-0.14,-13.81,2.53,5.93,-12.15,-3.2,7.11,-7.12,-10.98,7.94,-2.66,-15.29,0.24,4.53,-12.81,-3.86,3.3,-14.49,-8.31,4.34,-8.36,-16.9,2.74,-3.78,-22.7,-7.04,-2.27,-14.73,-11.18,0.05,-12.7,-21.66,-5.26,-7.96,-25.6,-8.28,-11.62,-31.37,-23.26,-7.45,-18.44,-32.82,-12.78,-22.4,-40,-25.24,-20.53,-41.24,-34.06,-9.55,-28.7,-30.94,-19.76,-32.99,-44.62,-30.45,-29.07,-45.83,-35.32,-20.47,-46.18,-39.43,-24.98,-39.26,-43.33,-38.22,-39.65,-54.42,-35.06,-30.21,-49.94,-37.92,-35.36,-35.36,-42.11,-25.62,-36.36,-42.78,-28.88,-26.38,-55.49,-40.41,-25.84,-41.46,-48.87,-39.65,-46.11,-58.33,-35.84,-33.12,-58.39,-45.17,-30.33,-41.74,-41.67,-18.25,-31.66,-55.11,-36.07,-30.42,-49.76,-41.07,-40.43,-55.27,-37.61,-29.68,-34.86,-50.62,-29.7,-32.82,-42.95,-33.04,-39.36,-51.66,-46.75,-19.83,-47.44,-58.41,-35.64,-31.32,-62.85,-45.08,-45.12,-58.71,-50.02,-21.01,-43.74,-46.11,-33.95,-39.44,-42.62,-28.51,-30.12,-56.11,-50.67,-34.65,-55.77,-48.65,-25.94,-45,-45.38,-41.18,-33.11,-57.52,-45.38,-25.31,-46.88,-55.15,-29.99,-48.85,-49.06,-23.38,-37.33,-42.13,-35.23,-23.92,-36.77,-43.26,-31.29,-31.04,-41.03,-16.88,-24.14,-47.53,-32.3,-19.19,-43.58,-36.24,-19.24,-23.81,-28.31,-18.64,-15.77,-28.2,-16.71,-15.8,-32.96,-20.36,-8.4,-25.39,-30.1,-8.45,-17.02,-21.28,-13.91,-11.06,-19.28,-11.91,2.02,-19.34,-14.37,3.85,-10.71,-23.93,-2.85,-6.02,-17.37,-9.18,1.05,-15.77,-14.65,7.48,-7.28,-14.1,3.52,-0.22,-15.45,-4.46,2.45,-14.49,-8.17,6.2,-8.54,-14.17,3.99,-4.06,-16.57,-0.15,0.33,-17.69,-10.47,4.43,-13.3,-15.25,4.45,-5.13,-18.88,-0.9,1.3,-16.89,-8.53,3.39,-13.95,-13.28,2.89,-7.55,-17.98,-0.15,-1.07</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B422" t="str">
+        <v>[L_23_标记]</v>
+      </c>
+      <c r="C422" t="str">
+        <v>a: 55.3ms -50.4uv b: 112.9ms 216.2uv</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B423" t="str">
+        <v>[R_24_名字]</v>
+      </c>
+      <c r="C423" t="str">
+        <v>FERG(24)_lFlicker</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B424" t="str">
+        <v>[R_24_放大器]</v>
+      </c>
+      <c r="C424" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B425" t="str">
+        <v>[R_24_闪光]</v>
+      </c>
+      <c r="C425" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B426" t="str">
+        <v>[R_24_闪光背景]</v>
+      </c>
+      <c r="C426" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B427" t="str">
+        <v>[R_24_采样]</v>
+      </c>
+      <c r="C427" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B428" t="str">
+        <v>[R_24_分析时间]</v>
+      </c>
+      <c r="C428" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B429" t="str">
+        <v>[R_24_数据长度]</v>
+      </c>
+      <c r="C429" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B430" t="str">
+        <v>[R_24_详细数据(uv)]</v>
+      </c>
+      <c r="C430" t="str">
+        <v>-11.28,-3.58,-17.25,-22,-9.08,7.07,1.22,-4.44,-6.14,11,20.06,15.72,7.68,18.69,36.74,37.43,30.8,24.9,44.55,61.97,46.49,40.63,59.67,76.13,77.02,53.73,53.26,81.3,85.73,78.04,69.47,74.38,89.99,90.12,88.92,78.46,82.56,97.65,82.88,71.03,85.01,93.61,86.81,70.73,68.42,74.13,84.12,69.94,48.37,50.09,61.82,54.52,37.48,37.6,44.57,39.03,24.9,19.02,13.32,23.59,15.68,3.63,-8.75,1.11,13.72,-8.58,-14.62,-11.52,-1.2,-9.3,-22.74,-35.84,-24.99,-14.18,-23.32,-34.07,-29.54,-18.86,-28.66,-37.73,-46.04,-30.96,-19.64,-35.6,-38.97,-41.73,-30.27,-23.87,-34.94,-48.79,-33.75,-31.29,-28.72,-44.19,-46.76,-29.32,-30.55,-52.03,-45.12,-32.43,-26.13,-26.99,-48.47,-45.08,-34.53,-26.73,-36.95,-48.8,-39.52,-23.51,-37.96,-41.82,-38.06,-26.63,-29.54,-50.5,-46.55,-35.29,-26.06,-40.49,-50.4,-39.28,-24.41,-24.27,-35.5,-39.22,-21.33,-14.76,-21.21,-29.1,-14.77,-0.65,0.35,-14.06,-9.24,10.22,24.16,14.03,5.41,17.87,36.33,39.13,24.33,33.56,44.93,60.81,55.26,46.69,63.54,72.64,71.69,61.99,76.62,81.05,100.72,93.91,83.47,88.47,98.07,101.49,89.08,81.07,101.26,109.7,93.35,73.99,79.74,89.37,85.65,82.92,71.93,72.58,82.11,69.86,58.6,59.73,63.84,60.39,40.86,28.68,42.02,47.62,24.87,12.29,12.33,23.14,14.27,0.14,-12.46,-0.52,1.46,-11.73,-27.03,-24.02,-13.93,-16.28,-33.05,-42.89,-28.87,-23.43,-32.04,-48.6,-43.53,-35.06,-32,-53.71,-55.06,-40.9,-29.56,-44.52,-54.71,-55.85,-31.43,-30.32,-56.83,-56.1,-32.63,-42.67,-45.08,-48.98,-46.4,-28.09,-37.63,-45.05,-50.97,-33.55,-25.61,-38.47,-57.86,-37.04,-27.28,-28.73,-47.85,-46.52,-32.55,-33.76,-40.49,-45.49,-45.08,-28.36,-26.45,-46.13,-41.55,-26.93,-21.11,-32.27,-36.97,-32.5,-14.23,-18.9,-26.15,-30.48,-12.81,-3.47,-9.44,-17.69,-3.69,6.86,11.9,3.79,4.27,22.23,28.95,25.45,22.07,23.78,41.24,53.74,39.07,40.79,51.22,63.27,66.95,51.42,63.38,85.52,74.59,73.66,78.88,77.26,94.37,87.5,71.93,81.68,100.41,94.07,83.49,85.58,83.08,88.96,77.97,68.54,75.98,77.32,81.03,70.64,54.61,61.67,72.7,48.49,43.33,34.63,49.2,45.3,22.89,19.95,21.63,30.64,9.41,-1.29,-5.41,11.45,3.45,-13.6,-19.54,-10.9,-5.16,-21.44,-30.63,-27.19,-15.97,-23.86,-35.41,-39.58,-33.34,-28.66,-32.91,-48.12,-39.84,-35.01,-32.45,-43.95,-51.3,-38.08,-33.66,-40.8,-50,-35.03,-31.7,-32.08,-32.68,-44.57,-34.27,-25.93,-40.87,-44.58,-37.17,-34.41,-25.06,-37.44,-43.81,-34.04,-27.47,-40.36,-52.28,-36.96,-21.9,-25.1,-38.49,-47.4,-38.81,-21.43,-33.72,-43.6,-39.63,-29.73,-27.83,-45.49,-43.51,-29.49,-23.18,-30.29,-41.33,-34.08,-18.26,-15.34,-31.12,-34.14,-16.43,-9.61,-17.3,-22.89,-10.34,7.76,6.81,0.25,1.21,13.43,31.62,17.93,15.61,26.25,40.04,49.3,40.37,41.95,47,65.36,55.53,45.77,57.5,72.72,78.21,71.38,71.71,84.52,85.47,88.06,75.05,72.16,98.71,87.93,74.52,67.75,91.97,89.89,74.97,66.43,66.01,84.68,85.56,59.2,55.1,59,62.84,55.62,40.89,44.45,45.1,44.46,28.62,21.67,25.85,30.51,13.28,0.15,2.82,15.18,5.72,-9.57,-20.79,-11.95,-8.79,-16.15,-31.7,-32.28,-17.56,-20.81,-39.21,-47.01,-27.8,-26.06,-34.73,-48.17,-45.5,-37.95,-33.56,-52.12,-59.44,-48.6,-37.37,-46.54,-56.9,-40.13,-41.78,-42.32,-48.67,-51.54,-39.93,-38.1,-48.64,-50.56,-50.87,-34.85,-34.09,-46.44,-61.92,-46.5,-41.83,-46.07,-53.53,-49.61,-28.02,-45.28,-57.71,-48.49,-39.96,-39.12,-38.02,-48.9,-44.4,-29.37,-35.96,-47.85,-51.18,-32.91,-25.2,-28.35,-36.5,-34.39</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B431" t="str">
+        <v>[R_24_标记]</v>
+      </c>
+      <c r="C431" t="str">
+        <v>幅值: 64.3uv 相位: 37.4°</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B432" t="str">
+        <v>[L_24_名字]</v>
+      </c>
+      <c r="C432" t="str">
+        <v>FERG(24)_lFlicker</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B433" t="str">
+        <v>[L_24_放大器]</v>
+      </c>
+      <c r="C433" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B434" t="str">
+        <v>[L_24_闪光]</v>
+      </c>
+      <c r="C434" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B435" t="str">
+        <v>[L_24_闪光背景]</v>
+      </c>
+      <c r="C435" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B436" t="str">
+        <v>[L_24_采样]</v>
+      </c>
+      <c r="C436" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B437" t="str">
+        <v>[L_24_分析时间]</v>
+      </c>
+      <c r="C437" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B438" t="str">
+        <v>[L_24_数据长度]</v>
+      </c>
+      <c r="C438" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B439" t="str">
+        <v>[L_24_详细数据(uv)]</v>
+      </c>
+      <c r="C439" t="str">
+        <v>-13.99,-12.8,-24.94,-17.69,-5.12,-6.38,-18.26,-10.84,-0.34,4.04,-8.35,-8.93,8.96,19.91,5.49,6.69,26.37,30.77,15.33,18.5,31.54,46.01,35.88,33.74,44.32,60.93,47.99,52.66,62.9,74.01,62.49,65.82,62.55,92.47,78.47,67.17,81.31,90.84,85,71.37,79.8,87.82,84.03,71.02,76.87,91.75,91.09,74.01,73.65,75.31,83.04,57,54.96,72.61,67.68,46.79,38.08,47.6,46.62,34.05,26.37,28.32,35.31,21.33,7.43,14.78,18.6,3.9,-8.24,-6.43,-1.42,-5.73,-19.47,-19.32,-13.16,-22.72,-34.95,-36.57,-21.36,-27.43,-44.94,-43.52,-35.52,-31.95,-40.85,-50.56,-30.02,-27.49,-43.88,-43.87,-33.97,-28.56,-40.76,-45.4,-32.68,-33.36,-49.09,-53.53,-30.29,-23.69,-42.16,-48.88,-40.7,-25.59,-33.15,-39.86,-35.04,-17.39,-42.08,-41,-37.67,-16.48,-23.52,-41.56,-31.44,-21.18,-25.84,-42.32,-36.53,-18.24,-23.42,-36.77,-36.45,-23.9,-20.9,-31.98,-36.58,-23.63,-16.2,-25.91,-27.82,-17.34,-3.84,-13.88,-19.32,-9.29,7.31,-4.35,-9.72,10.55,17.84,14.45,7.47,18.43,36.12,32.94,27.99,36.28,54.72,54.07,47.2,44.49,68.24,68.32,65.73,69.81,78.68,81.53,71.64,76.02,99.21,95.43,81.44,82.69,104.51,91.36,96.8,83.86,90.88,97.53,82.76,76.97,90.88,92.3,68.76,67.39,74.94,74.69,71.59,58.75,52.71,67.58,52.78,31.85,37.47,43.68,33.03,18.4,14.22,26.13,17.2,-2.55,-1.93,1.88,-1.67,-18.78,-25.65,-13.34,-15.49,-31.2,-33.84,-32.47,-28.3,-40.01,-48.5,-34.17,-34.68,-43.96,-51.26,-43.89,-35.75,-53.42,-54.57,-53.62,-38.64,-49.16,-62.77,-48.74,-41.43,-48.09,-57.77,-57.21,-26.69,-43.46,-46.9,-42.98,-37.32,-34.12,-53.88,-45.61,-19.8,-23.21,-44.04,-46.87,-23.4,-32.04,-38.42,-33.93,-23.11,-21.07,-42.92,-35.8,-20.52,-20.53,-27.66,-34.9,-19.63,-13.49,-23.92,-30.34,-20.82,-10.03,-17.51,-26.06,-14.99,-0.9,-9.89,-17.62,-9.78,6.43,1.92,-3.71,3.5,17.4,14.18,11.44,19.38,32.88,31.34,26.4,25.13,47.11,49.54,39.4,45.32,66.68,59.51,56.02,61.83,70.94,85.9,75.45,68.49,85.24,83.93,72.31,69.1,84.05,85.72,77.91,77.42,92.9,92.17,78.62,63.72,81,93.72,82.8,71.67,77.78,70.31,71.13,56.37,49.53,56.88,47.74,35.98,30.85,40.79,38.15,19.62,11.93,21.58,17.94,3.37,-3.6,5.15,2.17,-14.89,-24.62,-12.06,-13.92,-24.71,-32.13,-22.2,-26.75,-31.1,-41.86,-40.17,-34.82,-38.12,-48.41,-50.8,-29.25,-37.51,-51.58,-41.96,-39.12,-40.08,-46.04,-51.31,-33.71,-40.68,-45.8,-41.61,-31.03,-29.37,-48.17,-35.22,-34.67,-23.46,-39.4,-39.1,-21,-21.7,-29.32,-41.65,-22.31,-17.72,-31.71,-33.23,-20.99,-26.71,-32.74,-42.42,-32.4,-17.19,-29.58,-37.14,-25.01,-21.42,-29.07,-37.91,-29.72,-17.86,-19.82,-30.22,-26.44,-14.77,-13,-25.61,-19.92,-8.69,-5.08,-15.73,-10.66,4.05,6.03,-8.66,-2.04,11.46,20.37,13.96,10.03,28.46,41.96,27.36,28.06,39.83,50.04,40.57,42.17,62.26,74.02,62.69,59.01,66.1,78.32,80.28,65.71,87.09,82.24,82.23,69.99,70.38,94.09,96.45,70.96,73.41,82.26,85.2,70.65,65.54,86.4,79.81,67.62,64.14,72.64,72.14,57.04,45.59,49.35,56.23,32.87,27.9,37.2,39.44,22.4,8.38,14.85,20.41,3.11,-12.62,-4.67,-0.2,-8.52,-24.17,-18.03,-17.94,-28.67,-42.48,-31.88,-31.99,-30.78,-46.3,-49.56,-37.77,-36.93,-53.12,-46.86,-43.85,-45.65,-48.64,-48.51,-36.24,-43.24,-54.25,-60.86,-45.47,-45.25,-54.29,-58.39,-37.46,-32.03,-51.01,-61.72,-33.36,-36.95,-39.29,-56.12,-36.49,-38.33,-43.73,-47.44,-44.51,-29.26,-42.96,-40.53,-44.5,-29.22,-37.9,-46.53,-44.05,-27.3,-28.21,-39.74,-40.77,-24.63,-24.55,-36.27</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B440" t="str">
+        <v>[L_24_标记]</v>
+      </c>
+      <c r="C440" t="str">
+        <v>幅值: 63.1uv 相位: 37.2°</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C440"/>
   </ignoredErrors>
 </worksheet>
 </file>